--- a/style_analysis.xlsx
+++ b/style_analysis.xlsx
@@ -156,11 +156,11 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -812,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M130"/>
+  <dimension ref="A1:M132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1127,7 +1127,7 @@
       <c r="G10" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="16" t="inlineStr"/>
+      <c r="H10" s="17" t="inlineStr"/>
       <c r="I10" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="J14" s="12" t="n">
-        <v>0</v>
+        <v>21.6</v>
       </c>
       <c r="K14" s="15" t="inlineStr"/>
       <c r="L14" s="15" t="inlineStr"/>
@@ -1606,7 +1606,9 @@
         <v>0</v>
       </c>
       <c r="K21" s="15" t="inlineStr"/>
-      <c r="L21" s="15" t="inlineStr"/>
+      <c r="L21" s="16" t="n">
+        <v>6</v>
+      </c>
       <c r="M21" s="14" t="inlineStr">
         <is>
           <t>Global Partners LP</t>
@@ -1809,17 +1811,19 @@
       <c r="G26" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="16" t="inlineStr"/>
+      <c r="H26" s="13" t="n">
+        <v>32850</v>
+      </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K26" s="15" t="inlineStr"/>
-      <c r="L26" s="17" t="n">
+      <c r="L26" s="16" t="n">
         <v>136.6</v>
       </c>
       <c r="M26" s="14" t="inlineStr">
@@ -1938,10 +1942,12 @@
       <c r="G29" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="16" t="inlineStr"/>
+      <c r="H29" s="13" t="n">
+        <v>6203.27562275</v>
+      </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J29" s="12" t="n">
@@ -2034,7 +2040,9 @@
         <v>0</v>
       </c>
       <c r="K31" s="15" t="inlineStr"/>
-      <c r="L31" s="15" t="inlineStr"/>
+      <c r="L31" s="16" t="n">
+        <v>0.2</v>
+      </c>
       <c r="M31" s="14" t="inlineStr">
         <is>
           <t>Humana Inc.</t>
@@ -2108,10 +2116,12 @@
       <c r="G33" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="16" t="inlineStr"/>
+      <c r="H33" s="13" t="n">
+        <v>79009.1575</v>
+      </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J33" s="12" t="n">
@@ -2161,7 +2171,9 @@
         <v>0</v>
       </c>
       <c r="K34" s="15" t="inlineStr"/>
-      <c r="L34" s="15" t="inlineStr"/>
+      <c r="L34" s="16" t="n">
+        <v>1.5</v>
+      </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
           <t>Ally Financial Inc.</t>
@@ -2192,10 +2204,12 @@
       <c r="G35" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="16" t="inlineStr"/>
+      <c r="H35" s="13" t="n">
+        <v>4197.27353648</v>
+      </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J35" s="12" t="n">
@@ -2348,7 +2362,7 @@
         </is>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
@@ -2371,7 +2385,7 @@
       <c r="D43" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E43" s="16" t="inlineStr"/>
+      <c r="E43" s="17" t="inlineStr"/>
       <c r="F43" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -2497,10 +2511,12 @@
       <c r="D47" s="12" t="n">
         <v>0.4</v>
       </c>
-      <c r="E47" s="16" t="inlineStr"/>
+      <c r="E47" s="13" t="n">
+        <v>11838.6424</v>
+      </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G47" s="12" t="n">
@@ -2568,7 +2584,7 @@
         </is>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
@@ -2591,7 +2607,7 @@
       <c r="D50" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E50" s="16" t="inlineStr"/>
+      <c r="E50" s="17" t="inlineStr"/>
       <c r="F50" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -2621,7 +2637,7 @@
       <c r="D51" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="16" t="inlineStr"/>
+      <c r="E51" s="17" t="inlineStr"/>
       <c r="F51" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -2651,7 +2667,7 @@
       <c r="D52" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="16" t="inlineStr"/>
+      <c r="E52" s="17" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -2750,7 +2766,7 @@
         </is>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="H55" s="14" t="inlineStr">
         <is>
@@ -2846,7 +2862,7 @@
         </is>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
@@ -2961,7 +2977,7 @@
         </is>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
@@ -2984,10 +3000,12 @@
       <c r="D65" s="12" t="n">
         <v>7.7</v>
       </c>
-      <c r="E65" s="16" t="inlineStr"/>
+      <c r="E65" s="13" t="n">
+        <v>54313.77967512</v>
+      </c>
       <c r="F65" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G65" s="12" t="n">
@@ -3046,10 +3064,12 @@
       <c r="D67" s="12" t="n">
         <v>2.8</v>
       </c>
-      <c r="E67" s="16" t="inlineStr"/>
+      <c r="E67" s="13" t="n">
+        <v>40786.32640656</v>
+      </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G67" s="12" t="n">
@@ -3268,10 +3288,12 @@
       <c r="D74" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="E74" s="16" t="inlineStr"/>
+      <c r="E74" s="13" t="n">
+        <v>1462675.48</v>
+      </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G74" s="12" t="n">
@@ -3403,7 +3425,7 @@
         </is>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
@@ -3490,10 +3512,12 @@
       <c r="D81" s="12" t="n">
         <v>17.5</v>
       </c>
-      <c r="E81" s="16" t="inlineStr"/>
+      <c r="E81" s="13" t="n">
+        <v>32850</v>
+      </c>
       <c r="F81" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G81" s="12" t="n">
@@ -3600,7 +3624,7 @@
       <c r="D87" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="E87" s="16" t="inlineStr"/>
+      <c r="E87" s="17" t="inlineStr"/>
       <c r="F87" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -3621,7 +3645,7 @@
       <c r="D88" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E88" s="16" t="inlineStr"/>
+      <c r="E88" s="17" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr"/>
       <c r="G88" s="14" t="inlineStr"/>
     </row>
@@ -3638,7 +3662,7 @@
       <c r="D89" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E89" s="16" t="inlineStr"/>
+      <c r="E89" s="17" t="inlineStr"/>
       <c r="F89" s="14" t="inlineStr"/>
       <c r="G89" s="14" t="inlineStr"/>
     </row>
@@ -3872,7 +3896,7 @@
       <c r="D97" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E97" s="16" t="inlineStr"/>
+      <c r="E97" s="17" t="inlineStr"/>
       <c r="F97" s="14" t="inlineStr"/>
       <c r="G97" s="14" t="inlineStr"/>
     </row>
@@ -4253,22 +4277,22 @@
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>SRL</t>
+          <t>SVACW</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>15.2</v>
+        <v>0</v>
       </c>
       <c r="E112" s="13" t="n">
-        <v>90.786287375</v>
+        <v>12.500000625</v>
       </c>
       <c r="F112" s="11" t="n">
         <v>0</v>
@@ -4281,7 +4305,7 @@
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>Scully Royalty Ltd.</t>
+          <t xml:space="preserve">Spring Valley Acquisition Corp. </t>
         </is>
       </c>
     </row>
@@ -4293,17 +4317,17 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>THRY</t>
+          <t>SRL</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>0.7</v>
+        <v>15.2</v>
       </c>
       <c r="E113" s="13" t="n">
-        <v>155.224251</v>
+        <v>90.786287375</v>
       </c>
       <c r="F113" s="11" t="n">
         <v>0</v>
@@ -4312,11 +4336,11 @@
         <v>0</v>
       </c>
       <c r="H113" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
-          <t>Thryv Holdings, Inc.</t>
+          <t>Scully Royalty Ltd.</t>
         </is>
       </c>
     </row>
@@ -4328,17 +4352,17 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>OWL</t>
+          <t>THRY</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="E114" s="13" t="n">
-        <v>65.51875</v>
+        <v>155.224251</v>
       </c>
       <c r="F114" s="11" t="n">
         <v>0</v>
@@ -4347,11 +4371,11 @@
         <v>0</v>
       </c>
       <c r="H114" s="12" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>Blue Owl Capital Inc.</t>
+          <t>Thryv Holdings, Inc.</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4387,7 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>OWL</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
@@ -4373,7 +4397,7 @@
         <v>0.2</v>
       </c>
       <c r="E115" s="13" t="n">
-        <v>295.7383494</v>
+        <v>65.51875</v>
       </c>
       <c r="F115" s="11" t="n">
         <v>0</v>
@@ -4386,64 +4410,64 @@
       </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
-          <t>Citizens, Inc.</t>
+          <t>Blue Owl Capital Inc.</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>OPTU</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>11.1</v>
+        <v>0.2</v>
       </c>
       <c r="E116" s="13" t="n">
-        <v>547.94303805</v>
+        <v>295.7383494</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G116" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H116" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>Optimum Communications, Inc.</t>
+          <t>Citizens, Inc.</t>
         </is>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>BHC</t>
+          <t>BRCB</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D117" s="12" t="n">
-        <v>12.7</v>
+        <v>0</v>
       </c>
       <c r="E117" s="13" t="n">
-        <v>1781.47882188</v>
+        <v>135.58094828</v>
       </c>
       <c r="F117" s="11" t="n">
         <v>0</v>
@@ -4456,7 +4480,7 @@
       </c>
       <c r="I117" s="14" t="inlineStr">
         <is>
-          <t>Bausch Health Companies Inc.</t>
+          <t>Black Rock Coffee Bar, Inc.</t>
         </is>
       </c>
     </row>
@@ -4468,30 +4492,30 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>THM</t>
+          <t>OPTU</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>7.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" s="13" t="n">
-        <v>432.90702351</v>
+        <v>547.94303805</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G118" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>International Tower Hill Mines L</t>
+          <t>Optimum Communications, Inc.</t>
         </is>
       </c>
     </row>
@@ -4503,17 +4527,17 @@
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>GLP</t>
+          <t>BHC</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D119" s="12" t="n">
-        <v>2.4</v>
+        <v>12.7</v>
       </c>
       <c r="E119" s="13" t="n">
-        <v>1447.53107254</v>
+        <v>1781.47882188</v>
       </c>
       <c r="F119" s="11" t="n">
         <v>0</v>
@@ -4522,11 +4546,11 @@
         <v>0</v>
       </c>
       <c r="H119" s="12" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="I119" s="14" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Bausch Health Companies Inc.</t>
         </is>
       </c>
     </row>
@@ -4538,17 +4562,17 @@
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>THM</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>0.1</v>
+        <v>7.4</v>
       </c>
       <c r="E120" s="13" t="n">
-        <v>1573.512885</v>
+        <v>432.90702351</v>
       </c>
       <c r="F120" s="11" t="n">
         <v>0</v>
@@ -4557,33 +4581,33 @@
         <v>0</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>0</v>
+        <v>38.1</v>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>PureCycle Technologies, Inc.</t>
+          <t>International Tower Hill Mines L</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>small</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>GLP</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D121" s="12" t="n">
-        <v>39.4</v>
+        <v>2.4</v>
       </c>
       <c r="E121" s="13" t="n">
-        <v>2480.42355102</v>
+        <v>1447.53107254</v>
       </c>
       <c r="F121" s="11" t="n">
         <v>0</v>
@@ -4596,29 +4620,29 @@
       </c>
       <c r="I121" s="14" t="inlineStr">
         <is>
-          <t>NextNav Inc.</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>small</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>PPTA</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>29.2</v>
+        <v>0.1</v>
       </c>
       <c r="E122" s="13" t="n">
-        <v>3042.29831296</v>
+        <v>1573.512885</v>
       </c>
       <c r="F122" s="11" t="n">
         <v>0</v>
@@ -4631,7 +4655,7 @@
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>Perpetua Resources Corp.</t>
+          <t>PureCycle Technologies, Inc.</t>
         </is>
       </c>
     </row>
@@ -4643,17 +4667,17 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>AAMI</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>13.5</v>
+        <v>39.4</v>
       </c>
       <c r="E123" s="13" t="n">
-        <v>2677.5184482</v>
+        <v>2480.42355102</v>
       </c>
       <c r="F123" s="11" t="n">
         <v>0</v>
@@ -4666,7 +4690,7 @@
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
-          <t>Acadian Asset Management Inc.</t>
+          <t>NextNav Inc.</t>
         </is>
       </c>
     </row>
@@ -4678,17 +4702,17 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>PPTA</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>7.9</v>
+        <v>29.2</v>
       </c>
       <c r="E124" s="13" t="n">
-        <v>3422.4887892</v>
+        <v>3042.29831296</v>
       </c>
       <c r="F124" s="11" t="n">
         <v>0</v>
@@ -4697,11 +4721,11 @@
         <v>0</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>9.6</v>
+        <v>31.2</v>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>NovaGold Resources Inc.</t>
+          <t>Perpetua Resources Corp.</t>
         </is>
       </c>
     </row>
@@ -4713,17 +4737,17 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>AAMI</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>1.8</v>
+        <v>13.5</v>
       </c>
       <c r="E125" s="13" t="n">
-        <v>2116.46378184</v>
+        <v>2677.5184482</v>
       </c>
       <c r="F125" s="11" t="n">
         <v>0</v>
@@ -4732,33 +4756,33 @@
         <v>0</v>
       </c>
       <c r="H125" s="12" t="n">
-        <v>0</v>
+        <v>21.6</v>
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
-          <t>Huntsman Corporation</t>
+          <t>Acadian Asset Management Inc.</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>46.7</v>
+        <v>7.9</v>
       </c>
       <c r="E126" s="13" t="n">
-        <v>251547.5764068</v>
+        <v>3422.4887892</v>
       </c>
       <c r="F126" s="11" t="n">
         <v>0</v>
@@ -4767,33 +4791,33 @@
         <v>0</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Company</t>
+          <t>NovaGold Resources Inc.</t>
         </is>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="14" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>40.5</v>
+        <v>1.8</v>
       </c>
       <c r="E127" s="13" t="n">
-        <v>398828.3945862001</v>
+        <v>2116.46378184</v>
       </c>
       <c r="F127" s="11" t="n">
         <v>0</v>
@@ -4806,7 +4830,7 @@
       </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
-          <t>Bank of America Corporation</t>
+          <t>Huntsman Corporation</t>
         </is>
       </c>
     </row>
@@ -4818,17 +4842,17 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>PCG-PX</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>28.2</v>
+        <v>46.7</v>
       </c>
       <c r="E128" s="13" t="n">
-        <v>110602.29248386</v>
+        <v>251547.5764068</v>
       </c>
       <c r="F128" s="11" t="n">
         <v>0</v>
@@ -4841,7 +4865,7 @@
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>PG&amp;E Corp</t>
+          <t>Wells Fargo &amp; Company</t>
         </is>
       </c>
     </row>
@@ -4853,17 +4877,17 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>MDGL</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D129" s="12" t="n">
-        <v>23.4</v>
+        <v>40.5</v>
       </c>
       <c r="E129" s="13" t="n">
-        <v>11660.39953925</v>
+        <v>398828.3945862001</v>
       </c>
       <c r="F129" s="11" t="n">
         <v>0</v>
@@ -4872,11 +4896,11 @@
         <v>0</v>
       </c>
       <c r="H129" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>Madrigal Pharmaceuticals, Inc.</t>
+          <t>Bank of America Corporation</t>
         </is>
       </c>
     </row>
@@ -4888,28 +4912,98 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
+          <t>PCG-PX</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D130" s="12" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E130" s="13" t="n">
+        <v>110602.29248386</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" s="14" t="inlineStr">
+        <is>
+          <t>PG&amp;E Corp</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="14" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="B131" s="10" t="inlineStr">
+        <is>
+          <t>MDGL</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" s="12" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E131" s="13" t="n">
+        <v>11660.39953925</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I131" s="14" t="inlineStr">
+        <is>
+          <t>Madrigal Pharmaceuticals, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="14" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
           <t>NTRA</t>
         </is>
       </c>
-      <c r="C130" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D130" s="12" t="n">
+      <c r="C132" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" s="12" t="n">
         <v>18.1</v>
       </c>
-      <c r="E130" s="13" t="n">
+      <c r="E132" s="13" t="n">
         <v>33141.47154862</v>
       </c>
-      <c r="F130" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" s="14" t="inlineStr">
+      <c r="F132" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="14" t="inlineStr">
         <is>
           <t>Natera, Inc.</t>
         </is>
@@ -4942,7 +5036,7 @@
     <col width="33.5" customWidth="1" min="2" max="2"/>
     <col width="9.5" customWidth="1" min="3" max="3"/>
     <col width="9.5" customWidth="1" min="4" max="4"/>
-    <col width="23.5" customWidth="1" min="5" max="5"/>
+    <col width="22.5" customWidth="1" min="5" max="5"/>
     <col width="9.5" customWidth="1" min="6" max="6"/>
     <col width="34.5" customWidth="1" min="7" max="7"/>
     <col width="40.5" customWidth="1" min="8" max="8"/>
@@ -5594,7 +5688,7 @@
       <c r="G18" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="16" t="inlineStr"/>
+      <c r="H18" s="17" t="inlineStr"/>
       <c r="I18" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -5776,7 +5870,9 @@
         <v>0</v>
       </c>
       <c r="K22" s="15" t="inlineStr"/>
-      <c r="L22" s="15" t="inlineStr"/>
+      <c r="L22" s="16" t="n">
+        <v>0.2</v>
+      </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
           <t>TeraWulf Inc.</t>
@@ -6065,17 +6161,21 @@
       <c r="G29" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="16" t="inlineStr"/>
+      <c r="H29" s="13" t="n">
+        <v>20211.75389</v>
+      </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K29" s="15" t="inlineStr"/>
-      <c r="L29" s="15" t="inlineStr"/>
+      <c r="L29" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="M29" s="14" t="inlineStr">
         <is>
           <t>Strategy Inc</t>
@@ -6406,7 +6506,7 @@
       <c r="D40" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="16" t="inlineStr"/>
+      <c r="E40" s="17" t="inlineStr"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -6436,7 +6536,7 @@
       <c r="D41" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="16" t="inlineStr"/>
+      <c r="E41" s="17" t="inlineStr"/>
       <c r="F41" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -6658,7 +6758,7 @@
       <c r="D48" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="16" t="inlineStr"/>
+      <c r="E48" s="17" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -7219,10 +7319,12 @@
       <c r="D68" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="E68" s="16" t="inlineStr"/>
+      <c r="E68" s="13" t="n">
+        <v>1462675.48</v>
+      </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G68" s="12" t="n">
@@ -7409,10 +7511,12 @@
       <c r="D74" s="12" t="n">
         <v>2.3</v>
       </c>
-      <c r="E74" s="16" t="inlineStr"/>
+      <c r="E74" s="13" t="n">
+        <v>21722.76832</v>
+      </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G74" s="12" t="n">
@@ -7439,10 +7543,12 @@
       <c r="D75" s="12" t="n">
         <v>5.2</v>
       </c>
-      <c r="E75" s="16" t="inlineStr"/>
+      <c r="E75" s="13" t="n">
+        <v>141870.5045849</v>
+      </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G75" s="12" t="n">
@@ -8188,7 +8294,7 @@
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>SPG</t>
+          <t>SEI</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
@@ -8198,7 +8304,7 @@
         <v>0.1</v>
       </c>
       <c r="E104" s="13" t="n">
-        <v>1.69064</v>
+        <v>2.47595712</v>
       </c>
       <c r="F104" s="11" t="n">
         <v>0</v>
@@ -8207,11 +8313,11 @@
         <v>0</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>Simon Property Group, Inc.</t>
+          <t>Solaris Energy Infrastructure, I</t>
         </is>
       </c>
     </row>
@@ -8223,17 +8329,17 @@
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>WMG</t>
+          <t>SPG</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D105" s="12" t="n">
         <v>0.1</v>
       </c>
       <c r="E105" s="13" t="n">
-        <v>0.03011373000000001</v>
+        <v>1.69064</v>
       </c>
       <c r="F105" s="11" t="n">
         <v>0</v>
@@ -8246,7 +8352,7 @@
       </c>
       <c r="I105" s="14" t="inlineStr">
         <is>
-          <t>Warner Music Group Corp.</t>
+          <t>Simon Property Group, Inc.</t>
         </is>
       </c>
     </row>
@@ -8258,17 +8364,17 @@
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>GLXY</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D106" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E106" s="13" t="n">
-        <v>0.00342</v>
+        <v>0.56213788</v>
       </c>
       <c r="F106" s="11" t="n">
         <v>0</v>
@@ -8281,7 +8387,7 @@
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>Galaxy Digital</t>
+          <t>Erie Indemnity Company</t>
         </is>
       </c>
     </row>
@@ -8293,17 +8399,17 @@
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>WMG</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
         <v>10</v>
       </c>
       <c r="D107" s="12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E107" s="13" t="n">
-        <v>36.04991760000001</v>
+        <v>0.03011373000000001</v>
       </c>
       <c r="F107" s="11" t="n">
         <v>0</v>
@@ -8316,7 +8422,7 @@
       </c>
       <c r="I107" s="14" t="inlineStr">
         <is>
-          <t>C3.ai, Inc.</t>
+          <t>Warner Music Group Corp.</t>
         </is>
       </c>
     </row>
@@ -8783,17 +8889,17 @@
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>JHG</t>
+          <t>PTON</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D121" s="12" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="E121" s="13" t="n">
-        <v>7993.44254304</v>
+        <v>2429.47701593</v>
       </c>
       <c r="F121" s="11" t="n">
         <v>0</v>
@@ -8806,7 +8912,7 @@
       </c>
       <c r="I121" s="14" t="inlineStr">
         <is>
-          <t>Janus Henderson Group plc</t>
+          <t>Peloton Interactive, Inc.</t>
         </is>
       </c>
     </row>
@@ -8818,17 +8924,17 @@
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>GS-PD</t>
+          <t>JHG</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E122" s="13" t="n">
-        <v>5652.342186360001</v>
+        <v>7993.44254304</v>
       </c>
       <c r="F122" s="11" t="n">
         <v>0</v>
@@ -8837,11 +8943,11 @@
         <v>0</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>The Goldman Sachs Group, Inc.</t>
+          <t>Janus Henderson Group plc</t>
         </is>
       </c>
     </row>
@@ -9278,7 +9384,7 @@
         </is>
       </c>
       <c r="J8" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K8" s="15" t="inlineStr"/>
       <c r="L8" s="15" t="inlineStr"/>
@@ -9450,7 +9556,7 @@
         </is>
       </c>
       <c r="J12" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K12" s="15" t="inlineStr"/>
       <c r="L12" s="15" t="inlineStr"/>
@@ -9665,7 +9771,7 @@
         </is>
       </c>
       <c r="J17" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K17" s="15" t="inlineStr"/>
       <c r="L17" s="15" t="inlineStr"/>
@@ -9751,7 +9857,7 @@
         </is>
       </c>
       <c r="J19" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K19" s="15" t="inlineStr"/>
       <c r="L19" s="15" t="inlineStr"/>
@@ -9797,7 +9903,9 @@
         <v>0</v>
       </c>
       <c r="K20" s="15" t="inlineStr"/>
-      <c r="L20" s="15" t="inlineStr"/>
+      <c r="L20" s="16" t="n">
+        <v>9</v>
+      </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
           <t>Mirum Pharmaceuticals, Inc.</t>
@@ -9880,7 +9988,7 @@
         </is>
       </c>
       <c r="J22" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K22" s="15" t="inlineStr"/>
       <c r="L22" s="15" t="inlineStr"/>
@@ -9969,7 +10077,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="15" t="inlineStr"/>
-      <c r="L24" s="17" t="n">
+      <c r="L24" s="16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M24" s="14" t="inlineStr">
@@ -10011,7 +10119,7 @@
         </is>
       </c>
       <c r="J25" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K25" s="15" t="inlineStr"/>
       <c r="L25" s="15" t="inlineStr"/>
@@ -10140,7 +10248,7 @@
         </is>
       </c>
       <c r="J28" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15" t="inlineStr"/>
       <c r="L28" s="15" t="inlineStr"/>
@@ -10355,7 +10463,7 @@
         </is>
       </c>
       <c r="J33" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K33" s="15" t="inlineStr"/>
       <c r="L33" s="15" t="inlineStr"/>
@@ -10526,7 +10634,7 @@
         </is>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
@@ -10590,7 +10698,7 @@
         </is>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
@@ -10846,7 +10954,7 @@
         </is>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
@@ -10942,7 +11050,7 @@
         </is>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
@@ -11313,7 +11421,7 @@
         </is>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H67" s="14" t="inlineStr">
         <is>
@@ -11345,7 +11453,7 @@
         </is>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
@@ -11409,7 +11517,7 @@
         </is>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
@@ -11473,7 +11581,7 @@
         </is>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
@@ -11592,7 +11700,7 @@
       <c r="D76" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E76" s="16" t="inlineStr"/>
+      <c r="E76" s="17" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -12133,7 +12241,7 @@
       <c r="D96" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E96" s="16" t="inlineStr"/>
+      <c r="E96" s="17" t="inlineStr"/>
       <c r="F96" s="14" t="inlineStr"/>
       <c r="G96" s="14" t="inlineStr"/>
     </row>
@@ -12954,7 +13062,7 @@
         <v>1</v>
       </c>
       <c r="H123" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
@@ -13510,7 +13618,7 @@
       <c r="G6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="16" t="inlineStr"/>
+      <c r="H6" s="17" t="inlineStr"/>
       <c r="I6" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -13637,7 +13745,7 @@
       <c r="G9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="16" t="inlineStr"/>
+      <c r="H9" s="17" t="inlineStr"/>
       <c r="I9" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -13721,7 +13829,7 @@
       <c r="G11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="16" t="inlineStr"/>
+      <c r="H11" s="17" t="inlineStr"/>
       <c r="I11" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -13762,10 +13870,12 @@
       <c r="G12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="16" t="inlineStr"/>
+      <c r="H12" s="13" t="n">
+        <v>58.77413615</v>
+      </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="J12" s="12" t="n">
@@ -13803,7 +13913,7 @@
       <c r="G13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="16" t="inlineStr"/>
+      <c r="H13" s="17" t="inlineStr"/>
       <c r="I13" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -13844,7 +13954,7 @@
       <c r="G14" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="16" t="inlineStr"/>
+      <c r="H14" s="17" t="inlineStr"/>
       <c r="I14" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -13885,10 +13995,12 @@
       <c r="G15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="16" t="inlineStr"/>
+      <c r="H15" s="13" t="n">
+        <v>34.23332991</v>
+      </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="J15" s="12" t="n">
@@ -13926,7 +14038,7 @@
       <c r="G16" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="16" t="inlineStr"/>
+      <c r="H16" s="17" t="inlineStr"/>
       <c r="I16" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -14010,10 +14122,12 @@
       <c r="G18" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="16" t="inlineStr"/>
+      <c r="H18" s="13" t="n">
+        <v>2.87</v>
+      </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="J18" s="12" t="n">
@@ -14051,10 +14165,12 @@
       <c r="G19" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="16" t="inlineStr"/>
+      <c r="H19" s="13" t="n">
+        <v>51</v>
+      </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="J19" s="12" t="n">
@@ -14092,7 +14208,7 @@
       <c r="G20" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="16" t="inlineStr"/>
+      <c r="H20" s="17" t="inlineStr"/>
       <c r="I20" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -14133,7 +14249,7 @@
       <c r="G21" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="16" t="inlineStr"/>
+      <c r="H21" s="17" t="inlineStr"/>
       <c r="I21" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -14174,10 +14290,12 @@
       <c r="G22" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="16" t="inlineStr"/>
+      <c r="H22" s="13" t="n">
+        <v>78.15679656</v>
+      </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="J22" s="12" t="n">
@@ -14215,10 +14333,12 @@
       <c r="G23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="16" t="inlineStr"/>
+      <c r="H23" s="13" t="n">
+        <v>70.11389728</v>
+      </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="J23" s="12" t="n">
@@ -14256,7 +14376,7 @@
       <c r="G24" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="16" t="inlineStr"/>
+      <c r="H24" s="17" t="inlineStr"/>
       <c r="I24" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -14297,10 +14417,12 @@
       <c r="G25" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="16" t="inlineStr"/>
+      <c r="H25" s="13" t="n">
+        <v>69.73333682000001</v>
+      </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="J25" s="12" t="n">
@@ -14381,7 +14503,7 @@
       <c r="G27" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="16" t="inlineStr"/>
+      <c r="H27" s="17" t="inlineStr"/>
       <c r="I27" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -14422,7 +14544,7 @@
       <c r="G28" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="16" t="inlineStr"/>
+      <c r="H28" s="17" t="inlineStr"/>
       <c r="I28" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -14463,7 +14585,7 @@
       <c r="G29" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="16" t="inlineStr"/>
+      <c r="H29" s="17" t="inlineStr"/>
       <c r="I29" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -14504,7 +14626,7 @@
       <c r="G30" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="16" t="inlineStr"/>
+      <c r="H30" s="17" t="inlineStr"/>
       <c r="I30" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -14545,10 +14667,12 @@
       <c r="G31" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="16" t="inlineStr"/>
+      <c r="H31" s="13" t="n">
+        <v>1.913333224</v>
+      </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="J31" s="12" t="n">
@@ -14586,10 +14710,12 @@
       <c r="G32" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="16" t="inlineStr"/>
+      <c r="H32" s="13" t="n">
+        <v>0.9604248896000001</v>
+      </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="J32" s="12" t="n">
@@ -14670,7 +14796,7 @@
       <c r="G34" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="16" t="inlineStr"/>
+      <c r="H34" s="17" t="inlineStr"/>
       <c r="I34" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -14711,10 +14837,12 @@
       <c r="G35" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="16" t="inlineStr"/>
+      <c r="H35" s="13" t="n">
+        <v>106.82143142</v>
+      </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="J35" s="12" t="n">
@@ -14794,7 +14922,7 @@
       <c r="D40" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="16" t="inlineStr"/>
+      <c r="E40" s="17" t="inlineStr"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -14820,10 +14948,12 @@
       <c r="D41" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="16" t="inlineStr"/>
+      <c r="E41" s="13" t="n">
+        <v>67.40000336999999</v>
+      </c>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G41" s="12" t="n">
@@ -14850,7 +14980,7 @@
       <c r="D42" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="16" t="inlineStr"/>
+      <c r="E42" s="17" t="inlineStr"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -14880,7 +15010,7 @@
       <c r="D43" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E43" s="16" t="inlineStr"/>
+      <c r="E43" s="17" t="inlineStr"/>
       <c r="F43" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -14910,10 +15040,12 @@
       <c r="D44" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="16" t="inlineStr"/>
+      <c r="E44" s="13" t="n">
+        <v>74.06667037</v>
+      </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G44" s="12" t="n">
@@ -14972,7 +15104,7 @@
       <c r="D46" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E46" s="16" t="inlineStr"/>
+      <c r="E46" s="17" t="inlineStr"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -15034,7 +15166,7 @@
       <c r="D48" s="12" t="n">
         <v>0.1</v>
       </c>
-      <c r="E48" s="16" t="inlineStr"/>
+      <c r="E48" s="17" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -15128,7 +15260,7 @@
       <c r="D51" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="16" t="inlineStr"/>
+      <c r="E51" s="17" t="inlineStr"/>
       <c r="F51" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -15158,7 +15290,7 @@
       <c r="D52" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="16" t="inlineStr"/>
+      <c r="E52" s="17" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -15184,10 +15316,12 @@
       <c r="D53" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E53" s="16" t="inlineStr"/>
+      <c r="E53" s="13" t="n">
+        <v>57.97758445</v>
+      </c>
       <c r="F53" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G53" s="12" t="n">
@@ -15214,10 +15348,12 @@
       <c r="D54" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E54" s="16" t="inlineStr"/>
+      <c r="E54" s="13" t="n">
+        <v>76.125</v>
+      </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G54" s="12" t="n">
@@ -15276,7 +15412,7 @@
       <c r="D56" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="16" t="inlineStr"/>
+      <c r="E56" s="17" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -15302,7 +15438,7 @@
       <c r="D57" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E57" s="16" t="inlineStr"/>
+      <c r="E57" s="17" t="inlineStr"/>
       <c r="F57" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -15415,10 +15551,12 @@
       <c r="D63" s="12" t="n">
         <v>0.8</v>
       </c>
-      <c r="E63" s="16" t="inlineStr"/>
+      <c r="E63" s="13" t="n">
+        <v>7834.14584</v>
+      </c>
       <c r="F63" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G63" s="12" t="n">
@@ -15454,7 +15592,7 @@
         </is>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
@@ -15477,7 +15615,7 @@
       <c r="D65" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E65" s="16" t="inlineStr"/>
+      <c r="E65" s="17" t="inlineStr"/>
       <c r="F65" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -15603,10 +15741,12 @@
       <c r="D69" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E69" s="16" t="inlineStr"/>
+      <c r="E69" s="13" t="n">
+        <v>565.72096261</v>
+      </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G69" s="12" t="n">
@@ -15633,7 +15773,7 @@
       <c r="D70" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E70" s="16" t="inlineStr"/>
+      <c r="E70" s="17" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -15659,7 +15799,7 @@
       <c r="D71" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E71" s="16" t="inlineStr"/>
+      <c r="E71" s="17" t="inlineStr"/>
       <c r="F71" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -15760,7 +15900,7 @@
       <c r="D77" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E77" s="16" t="inlineStr"/>
+      <c r="E77" s="17" t="inlineStr"/>
       <c r="F77" s="14" t="inlineStr"/>
       <c r="G77" s="14" t="inlineStr"/>
     </row>
@@ -15777,7 +15917,7 @@
       <c r="D78" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E78" s="16" t="inlineStr"/>
+      <c r="E78" s="17" t="inlineStr"/>
       <c r="F78" s="14" t="inlineStr"/>
       <c r="G78" s="14" t="inlineStr"/>
     </row>
@@ -15798,7 +15938,7 @@
       <c r="D79" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E79" s="16" t="inlineStr"/>
+      <c r="E79" s="17" t="inlineStr"/>
       <c r="F79" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -15823,7 +15963,7 @@
       <c r="D80" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E80" s="16" t="inlineStr"/>
+      <c r="E80" s="17" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr"/>
       <c r="G80" s="14" t="inlineStr"/>
     </row>
@@ -15891,17 +16031,17 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>ENHA</t>
+          <t>SPEG</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D85" s="12" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>45.33300069</v>
+        <v>34.23332991</v>
       </c>
       <c r="F85" s="11" t="n">
         <v>0</v>
@@ -15914,7 +16054,7 @@
       </c>
       <c r="I85" s="14" t="inlineStr">
         <is>
-          <t>Enhanced Group Inc.</t>
+          <t>Silver Pegasus Acquisition Corp.</t>
         </is>
       </c>
     </row>
@@ -15926,17 +16066,17 @@
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>LATA</t>
+          <t>APXTW</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E86" s="13" t="n">
-        <v>0.606</v>
+        <v>2.87</v>
       </c>
       <c r="F86" s="11" t="n">
         <v>0</v>
@@ -15949,7 +16089,7 @@
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>Galata Acquisition Corp. II</t>
+          <t>Apex Treasury Corporation</t>
         </is>
       </c>
     </row>
@@ -15961,17 +16101,17 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>BPACU</t>
+          <t>DNMXW</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D87" s="12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>14.7775</v>
+        <v>1.913333224</v>
       </c>
       <c r="F87" s="11" t="n">
         <v>0</v>
@@ -15984,7 +16124,7 @@
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
-          <t>Blueport Acquisition Ltd</t>
+          <t>Dynamix Corporation III</t>
         </is>
       </c>
     </row>
@@ -15996,17 +16136,17 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>MMTXW</t>
+          <t>FIGXW</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D88" s="12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E88" s="13" t="n">
-        <v>1.147653</v>
+        <v>0.9604248896000001</v>
       </c>
       <c r="F88" s="11" t="n">
         <v>0</v>
@@ -16019,7 +16159,7 @@
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>Miluna Acquisition Corp</t>
+          <t>FIGX Capital Acquisition Corp.</t>
         </is>
       </c>
     </row>
@@ -16031,17 +16171,17 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>RFAIU</t>
+          <t>BCSS-WT</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D89" s="12" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>38.84825</v>
+        <v>1.02</v>
       </c>
       <c r="F89" s="11" t="n">
         <v>0</v>
@@ -16054,7 +16194,7 @@
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
-          <t>RF Acquisition Corp II</t>
+          <t>Bain Capital GSS Investment Corp</t>
         </is>
       </c>
     </row>
@@ -16136,17 +16276,17 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>SOUL</t>
+          <t>MKLYU</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
         <v>5</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E92" s="13" t="n">
-        <v>265.0389</v>
+        <v>58.77413615</v>
       </c>
       <c r="F92" s="11" t="n">
         <v>0</v>
@@ -16159,7 +16299,7 @@
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>Soulpower Acquisition Corporatio</t>
+          <t>McKinley Acquisition Corporation</t>
         </is>
       </c>
     </row>
@@ -16171,17 +16311,17 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>INAC</t>
+          <t>SOUL</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
         <v>5</v>
       </c>
       <c r="D93" s="12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>151.0912</v>
+        <v>265.0389</v>
       </c>
       <c r="F93" s="11" t="n">
         <v>0</v>
@@ -16194,7 +16334,7 @@
       </c>
       <c r="I93" s="14" t="inlineStr">
         <is>
-          <t>Indigo Acquisition Corp.</t>
+          <t>Soulpower Acquisition Corporatio</t>
         </is>
       </c>
     </row>
@@ -16206,17 +16346,17 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>RANGU</t>
+          <t>HVMC</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
         <v>5</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E94" s="13" t="n">
-        <v>173.8465</v>
+        <v>51</v>
       </c>
       <c r="F94" s="11" t="n">
         <v>0</v>
@@ -16229,7 +16369,7 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>Range Capital Acquisition Corp.</t>
+          <t>Highview Merger Corp.</t>
         </is>
       </c>
     </row>
@@ -16416,17 +16556,17 @@
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>DBRG</t>
+          <t>CWAN</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="E100" s="13" t="n">
-        <v>2876.01246414</v>
+        <v>7165.286550659999</v>
       </c>
       <c r="F100" s="11" t="n">
         <v>0</v>
@@ -16439,7 +16579,7 @@
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>DigitalBridge Group, Inc.</t>
+          <t>Clearwater Analytics Holdings, I</t>
         </is>
       </c>
     </row>
@@ -16451,20 +16591,20 @@
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>SEM</t>
+          <t>DBRG</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D101" s="12" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>2051.237872</v>
+        <v>2876.01246414</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" s="11" t="n">
         <v>0</v>
@@ -16474,7 +16614,7 @@
       </c>
       <c r="I101" s="14" t="inlineStr">
         <is>
-          <t>Select Medical Holdings Corporat</t>
+          <t>DigitalBridge Group, Inc.</t>
         </is>
       </c>
     </row>
@@ -16486,20 +16626,20 @@
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>IDCC</t>
+          <t>SEM</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>4.8</v>
+        <v>1.4</v>
       </c>
       <c r="E102" s="13" t="n">
-        <v>7651.162385160001</v>
+        <v>2051.237872</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102" s="11" t="n">
         <v>0</v>
@@ -16509,7 +16649,7 @@
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>InterDigital, Inc.</t>
+          <t>Select Medical Holdings Corporat</t>
         </is>
       </c>
     </row>
@@ -16521,17 +16661,17 @@
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>WBS-PG</t>
+          <t>IDCC</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D103" s="12" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>3874.05356718</v>
+        <v>7651.162385160001</v>
       </c>
       <c r="F103" s="11" t="n">
         <v>0</v>
@@ -16544,7 +16684,7 @@
       </c>
       <c r="I103" s="14" t="inlineStr">
         <is>
-          <t>Webster Financial Corporation</t>
+          <t>InterDigital, Inc.</t>
         </is>
       </c>
     </row>
@@ -16556,7 +16696,7 @@
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>AAUC</t>
+          <t>WBS-PG</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
@@ -16566,7 +16706,7 @@
         <v>0.7</v>
       </c>
       <c r="E104" s="13" t="n">
-        <v>3198.26234644</v>
+        <v>3874.05356718</v>
       </c>
       <c r="F104" s="11" t="n">
         <v>0</v>
@@ -16579,7 +16719,7 @@
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>Allied Gold Corporation</t>
+          <t>Webster Financial Corporation</t>
         </is>
       </c>
     </row>
@@ -16976,7 +17116,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="15" t="inlineStr"/>
-      <c r="L7" s="17" t="n">
+      <c r="L7" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="M7" s="14" t="inlineStr">
@@ -17150,7 +17290,9 @@
         <v>0</v>
       </c>
       <c r="K11" s="15" t="inlineStr"/>
-      <c r="L11" s="15" t="inlineStr"/>
+      <c r="L11" s="16" t="n">
+        <v>7.7</v>
+      </c>
       <c r="M11" s="14" t="inlineStr">
         <is>
           <t>Pool Corporation</t>
@@ -17279,7 +17421,9 @@
         <v>0</v>
       </c>
       <c r="K14" s="15" t="inlineStr"/>
-      <c r="L14" s="15" t="inlineStr"/>
+      <c r="L14" s="16" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
           <t>Solventum Corporation</t>
@@ -17365,7 +17509,7 @@
         <v>6.1</v>
       </c>
       <c r="K16" s="15" t="inlineStr"/>
-      <c r="L16" s="17" t="n">
+      <c r="L16" s="16" t="n">
         <v>0.3</v>
       </c>
       <c r="M16" s="14" t="inlineStr">
@@ -17625,7 +17769,9 @@
         <v>0</v>
       </c>
       <c r="K22" s="15" t="inlineStr"/>
-      <c r="L22" s="15" t="inlineStr"/>
+      <c r="L22" s="16" t="n">
+        <v>0.2</v>
+      </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
           <t>Ferroglobe PLC</t>
@@ -17797,7 +17943,9 @@
         <v>0</v>
       </c>
       <c r="K26" s="15" t="inlineStr"/>
-      <c r="L26" s="15" t="inlineStr"/>
+      <c r="L26" s="16" t="n">
+        <v>0.4</v>
+      </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
           <t>Aptiv PLC</t>
@@ -17828,10 +17976,12 @@
       <c r="G27" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="16" t="inlineStr"/>
+      <c r="H27" s="13" t="n">
+        <v>1557.06982</v>
+      </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>small</t>
         </is>
       </c>
       <c r="J27" s="12" t="n">
@@ -17878,7 +18028,7 @@
         </is>
       </c>
       <c r="J28" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K28" s="15" t="inlineStr"/>
       <c r="L28" s="15" t="inlineStr"/>
@@ -18139,7 +18289,9 @@
         <v>0</v>
       </c>
       <c r="K34" s="15" t="inlineStr"/>
-      <c r="L34" s="15" t="inlineStr"/>
+      <c r="L34" s="16" t="n">
+        <v>0.7</v>
+      </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
           <t>Sonoco Products Company</t>
@@ -18182,7 +18334,7 @@
         <v>0</v>
       </c>
       <c r="K35" s="15" t="inlineStr"/>
-      <c r="L35" s="17" t="n">
+      <c r="L35" s="16" t="n">
         <v>0.1</v>
       </c>
       <c r="M35" s="14" t="inlineStr">
@@ -18321,7 +18473,7 @@
       <c r="D42" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="16" t="inlineStr"/>
+      <c r="E42" s="17" t="inlineStr"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -18539,7 +18691,7 @@
       <c r="D49" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E49" s="16" t="inlineStr"/>
+      <c r="E49" s="17" t="inlineStr"/>
       <c r="F49" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -18574,7 +18726,7 @@
         </is>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
@@ -18597,7 +18749,7 @@
       <c r="D51" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="16" t="inlineStr"/>
+      <c r="E51" s="17" t="inlineStr"/>
       <c r="F51" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -18723,10 +18875,12 @@
       <c r="D55" s="12" t="n">
         <v>0.4</v>
       </c>
-      <c r="E55" s="16" t="inlineStr"/>
+      <c r="E55" s="13" t="n">
+        <v>870.4685900000001</v>
+      </c>
       <c r="F55" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G55" s="12" t="n">
@@ -19072,7 +19226,7 @@
       <c r="D71" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E71" s="16" t="inlineStr"/>
+      <c r="E71" s="17" t="inlineStr"/>
       <c r="F71" s="14" t="inlineStr"/>
       <c r="G71" s="14" t="inlineStr"/>
     </row>
@@ -19089,7 +19243,7 @@
       <c r="D72" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E72" s="16" t="inlineStr"/>
+      <c r="E72" s="17" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr"/>
       <c r="G72" s="14" t="inlineStr"/>
     </row>
@@ -19137,7 +19291,7 @@
       <c r="D74" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E74" s="16" t="inlineStr"/>
+      <c r="E74" s="17" t="inlineStr"/>
       <c r="F74" s="14" t="inlineStr"/>
       <c r="G74" s="14" t="inlineStr"/>
     </row>
@@ -19309,7 +19463,7 @@
       <c r="D80" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E80" s="16" t="inlineStr"/>
+      <c r="E80" s="17" t="inlineStr"/>
       <c r="F80" s="14" t="inlineStr"/>
       <c r="G80" s="14" t="inlineStr"/>
     </row>
@@ -19622,17 +19776,17 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>PUMP</t>
+          <t>RVLV</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="E92" s="13" t="n">
-        <v>1808.600396</v>
+        <v>1557.06982</v>
       </c>
       <c r="F92" s="11" t="n">
         <v>0</v>
@@ -19645,7 +19799,7 @@
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>ProPetro Holding Corp.</t>
+          <t>Revolve Group, Inc.</t>
         </is>
       </c>
     </row>
@@ -19657,17 +19811,17 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>CCB</t>
+          <t>PUMP</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D93" s="12" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>1092.5770932</v>
+        <v>1808.600396</v>
       </c>
       <c r="F93" s="11" t="n">
         <v>0</v>
@@ -19680,7 +19834,7 @@
       </c>
       <c r="I93" s="14" t="inlineStr">
         <is>
-          <t>Coastal Financial Corporation</t>
+          <t>ProPetro Holding Corp.</t>
         </is>
       </c>
     </row>
@@ -19692,17 +19846,17 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>THRM</t>
+          <t>CCB</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E94" s="13" t="n">
-        <v>1101.8757297</v>
+        <v>1092.5770932</v>
       </c>
       <c r="F94" s="11" t="n">
         <v>0</v>
@@ -19715,7 +19869,7 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>Gentherm Incorporated</t>
+          <t>Coastal Financial Corporation</t>
         </is>
       </c>
     </row>
@@ -20089,7 +20243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M131"/>
+  <dimension ref="A1:M132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20404,17 +20558,19 @@
       <c r="G10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="16" t="inlineStr"/>
+      <c r="H10" s="13" t="n">
+        <v>9160.919039999999</v>
+      </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J10" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K10" s="15" t="inlineStr"/>
-      <c r="L10" s="17" t="n">
+      <c r="L10" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M10" s="14" t="inlineStr">
@@ -20619,7 +20775,7 @@
       <c r="G15" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="H15" s="16" t="inlineStr"/>
+      <c r="H15" s="17" t="inlineStr"/>
       <c r="I15" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -20703,10 +20859,12 @@
       <c r="G17" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="16" t="inlineStr"/>
+      <c r="H17" s="13" t="n">
+        <v>1462675.48</v>
+      </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J17" s="12" t="n">
@@ -20744,10 +20902,12 @@
       <c r="G18" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="H18" s="16" t="inlineStr"/>
+      <c r="H18" s="13" t="n">
+        <v>54313.77967512</v>
+      </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J18" s="12" t="n">
@@ -20957,17 +21117,19 @@
       <c r="G23" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="16" t="inlineStr"/>
+      <c r="H23" s="13" t="n">
+        <v>33508.15951608</v>
+      </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J23" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K23" s="15" t="inlineStr"/>
-      <c r="L23" s="17" t="n">
+      <c r="L23" s="16" t="n">
         <v>8.9</v>
       </c>
       <c r="M23" s="14" t="inlineStr">
@@ -21086,10 +21248,12 @@
       <c r="G26" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="16" t="inlineStr"/>
+      <c r="H26" s="13" t="n">
+        <v>6716.809792</v>
+      </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J26" s="12" t="n">
@@ -21213,17 +21377,19 @@
       <c r="G29" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="16" t="inlineStr"/>
+      <c r="H29" s="13" t="n">
+        <v>29437.82641572</v>
+      </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K29" s="15" t="inlineStr"/>
-      <c r="L29" s="17" t="n">
+      <c r="L29" s="16" t="n">
         <v>0.2</v>
       </c>
       <c r="M29" s="14" t="inlineStr">
@@ -21256,17 +21422,19 @@
       <c r="G30" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="16" t="inlineStr"/>
+      <c r="H30" s="13" t="n">
+        <v>32850</v>
+      </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="15" t="inlineStr"/>
-      <c r="L30" s="17" t="n">
+      <c r="L30" s="16" t="n">
         <v>136.6</v>
       </c>
       <c r="M30" s="14" t="inlineStr">
@@ -21428,17 +21596,19 @@
       <c r="G34" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="16" t="inlineStr"/>
+      <c r="H34" s="13" t="n">
+        <v>75529.51433999999</v>
+      </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="15" t="inlineStr"/>
-      <c r="L34" s="17" t="n">
+      <c r="L34" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M34" s="14" t="inlineStr">
@@ -21812,10 +21982,12 @@
       <c r="D48" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="E48" s="16" t="inlineStr"/>
+      <c r="E48" s="13" t="n">
+        <v>5377.20768</v>
+      </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G48" s="12" t="n">
@@ -21842,7 +22014,7 @@
       <c r="D49" s="12" t="n">
         <v>85.8</v>
       </c>
-      <c r="E49" s="16" t="inlineStr"/>
+      <c r="E49" s="17" t="inlineStr"/>
       <c r="F49" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -21872,10 +22044,12 @@
       <c r="D50" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="E50" s="16" t="inlineStr"/>
+      <c r="E50" s="13" t="n">
+        <v>1462675.48</v>
+      </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G50" s="12" t="n">
@@ -22030,10 +22204,12 @@
       <c r="D55" s="12" t="n">
         <v>6.6</v>
       </c>
-      <c r="E55" s="16" t="inlineStr"/>
+      <c r="E55" s="13" t="n">
+        <v>75529.51433999999</v>
+      </c>
       <c r="F55" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G55" s="12" t="n">
@@ -22060,10 +22236,12 @@
       <c r="D56" s="12" t="n">
         <v>7.3</v>
       </c>
-      <c r="E56" s="16" t="inlineStr"/>
+      <c r="E56" s="13" t="n">
+        <v>6716.809792</v>
+      </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G56" s="12" t="n">
@@ -22301,14 +22479,16 @@
       <c r="D66" s="12" t="n">
         <v>2.9</v>
       </c>
-      <c r="E66" s="16" t="inlineStr"/>
+      <c r="E66" s="13" t="n">
+        <v>33508.15951608</v>
+      </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
@@ -22555,10 +22735,12 @@
       <c r="D74" s="12" t="n">
         <v>6.6</v>
       </c>
-      <c r="E74" s="16" t="inlineStr"/>
+      <c r="E74" s="13" t="n">
+        <v>75529.51433999999</v>
+      </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G74" s="12" t="n">
@@ -22585,7 +22767,7 @@
       <c r="D75" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E75" s="16" t="inlineStr"/>
+      <c r="E75" s="17" t="inlineStr"/>
       <c r="F75" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -22611,10 +22793,12 @@
       <c r="D76" s="12" t="n">
         <v>17.5</v>
       </c>
-      <c r="E76" s="16" t="inlineStr"/>
+      <c r="E76" s="13" t="n">
+        <v>32850</v>
+      </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G76" s="12" t="n">
@@ -22641,7 +22825,7 @@
       <c r="D77" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E77" s="16" t="inlineStr"/>
+      <c r="E77" s="17" t="inlineStr"/>
       <c r="F77" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -22735,10 +22919,12 @@
       <c r="D80" s="12" t="n">
         <v>0.4</v>
       </c>
-      <c r="E80" s="16" t="inlineStr"/>
+      <c r="E80" s="13" t="n">
+        <v>870.4685900000001</v>
+      </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G80" s="12" t="n">
@@ -22841,7 +23027,7 @@
       <c r="D86" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E86" s="16" t="inlineStr"/>
+      <c r="E86" s="17" t="inlineStr"/>
       <c r="F86" s="14" t="inlineStr"/>
       <c r="G86" s="14" t="inlineStr"/>
     </row>
@@ -23110,10 +23296,12 @@
       <c r="D95" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="E95" s="16" t="inlineStr"/>
+      <c r="E95" s="13" t="n">
+        <v>97243.60665285001</v>
+      </c>
       <c r="F95" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G95" s="14" t="inlineStr">
@@ -23294,10 +23482,12 @@
       <c r="D101" s="11" t="n">
         <v>71</v>
       </c>
-      <c r="E101" s="16" t="inlineStr"/>
+      <c r="E101" s="13" t="n">
+        <v>1462675.48</v>
+      </c>
       <c r="F101" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G101" s="14" t="inlineStr">
@@ -23385,10 +23575,12 @@
       <c r="D104" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="E104" s="16" t="inlineStr"/>
+      <c r="E104" s="13" t="n">
+        <v>6716.809792</v>
+      </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G104" s="14" t="inlineStr">
@@ -23527,7 +23719,7 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>CRIS</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
@@ -23537,7 +23729,7 @@
         <v>0</v>
       </c>
       <c r="E111" s="13" t="n">
-        <v>16.410029753</v>
+        <v>0.56213788</v>
       </c>
       <c r="F111" s="11" t="n">
         <v>0</v>
@@ -23550,29 +23742,29 @@
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
-          <t>Curis, Inc.</t>
+          <t>Erie Indemnity Company</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>IVVD</t>
+          <t>CRIS</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E112" s="13" t="n">
-        <v>285.7397676948</v>
+        <v>16.410029753</v>
       </c>
       <c r="F112" s="11" t="n">
         <v>0</v>
@@ -23581,11 +23773,11 @@
         <v>0</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>Invivyd, Inc.</t>
+          <t>Curis, Inc.</t>
         </is>
       </c>
     </row>
@@ -23597,17 +23789,17 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>RERE</t>
+          <t>IVVD</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E113" s="13" t="n">
-        <v>73.62787040000001</v>
+        <v>285.7397676948</v>
       </c>
       <c r="F113" s="11" t="n">
         <v>0</v>
@@ -23616,11 +23808,11 @@
         <v>0</v>
       </c>
       <c r="H113" s="12" t="n">
-        <v>8.4</v>
+        <v>9.9</v>
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
-          <t>ATRenew Inc.</t>
+          <t>Invivyd, Inc.</t>
         </is>
       </c>
     </row>
@@ -23632,17 +23824,17 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>GUTS</t>
+          <t>RERE</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E114" s="13" t="n">
-        <v>136.120810254</v>
+        <v>73.62787040000001</v>
       </c>
       <c r="F114" s="11" t="n">
         <v>0</v>
@@ -23651,11 +23843,11 @@
         <v>0</v>
       </c>
       <c r="H114" s="12" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>Fractyl Health, Inc.</t>
+          <t>ATRenew Inc.</t>
         </is>
       </c>
     </row>
@@ -23667,7 +23859,7 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>PAASF</t>
+          <t>GUTS</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
@@ -23677,7 +23869,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="13" t="n">
-        <v>295.2929321999999</v>
+        <v>136.120810254</v>
       </c>
       <c r="F115" s="11" t="n">
         <v>0</v>
@@ -23686,11 +23878,11 @@
         <v>0</v>
       </c>
       <c r="H115" s="12" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
-          <t>Pan American Silver Corp.</t>
+          <t>Fractyl Health, Inc.</t>
         </is>
       </c>
     </row>
@@ -23702,7 +23894,7 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>PEPG</t>
+          <t>PAASF</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
@@ -23712,7 +23904,7 @@
         <v>0</v>
       </c>
       <c r="E116" s="13" t="n">
-        <v>123.81289485</v>
+        <v>295.2929321999999</v>
       </c>
       <c r="F116" s="11" t="n">
         <v>0</v>
@@ -23721,33 +23913,33 @@
         <v>0</v>
       </c>
       <c r="H116" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>PepGen Inc.</t>
+          <t>Pan American Silver Corp.</t>
         </is>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>BELFA</t>
+          <t>PEPG</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D117" s="12" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="E117" s="13" t="n">
-        <v>578.0263622399999</v>
+        <v>123.81289485</v>
       </c>
       <c r="F117" s="11" t="n">
         <v>0</v>
@@ -23756,11 +23948,11 @@
         <v>0</v>
       </c>
       <c r="H117" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I117" s="14" t="inlineStr">
         <is>
-          <t>Bel Fuse Inc.</t>
+          <t>PepGen Inc.</t>
         </is>
       </c>
     </row>
@@ -23772,17 +23964,17 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>TIC</t>
+          <t>BELFA</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="E118" s="13" t="n">
-        <v>1861.17872568</v>
+        <v>578.0263622399999</v>
       </c>
       <c r="F118" s="11" t="n">
         <v>0</v>
@@ -23795,7 +23987,7 @@
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>TIC Solutions, Inc.</t>
+          <t>Bel Fuse Inc.</t>
         </is>
       </c>
     </row>
@@ -23807,20 +23999,20 @@
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>WLTH</t>
+          <t>TIC</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D119" s="12" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E119" s="13" t="n">
-        <v>1260.60866304</v>
+        <v>1861.17872568</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G119" s="11" t="n">
         <v>0</v>
@@ -23830,7 +24022,7 @@
       </c>
       <c r="I119" s="14" t="inlineStr">
         <is>
-          <t>Wealthfront Corporation</t>
+          <t>TIC Solutions, Inc.</t>
         </is>
       </c>
     </row>
@@ -23842,7 +24034,7 @@
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>MIR</t>
+          <t>WLTH</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
@@ -23852,10 +24044,10 @@
         <v>0.6</v>
       </c>
       <c r="E120" s="13" t="n">
-        <v>348.9375</v>
+        <v>1260.60866304</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G120" s="11" t="n">
         <v>0</v>
@@ -23865,7 +24057,7 @@
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>Mirion Technologies, Inc.</t>
+          <t>Wealthfront Corporation</t>
         </is>
       </c>
     </row>
@@ -23877,17 +24069,17 @@
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>MIR</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D121" s="12" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E121" s="13" t="n">
-        <v>1466.96622321</v>
+        <v>348.9375</v>
       </c>
       <c r="F121" s="11" t="n">
         <v>0</v>
@@ -23900,42 +24092,42 @@
       </c>
       <c r="I121" s="14" t="inlineStr">
         <is>
-          <t>G-III Apparel Group, Ltd.</t>
+          <t>Mirion Technologies, Inc.</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>small</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>13.4</v>
+        <v>0.4</v>
       </c>
       <c r="E122" s="13" t="n">
-        <v>9384.211261600001</v>
+        <v>1466.96622321</v>
       </c>
       <c r="F122" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G122" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H122" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>Norwegian Cruise Line Holdings L</t>
+          <t>G-III Apparel Group, Ltd.</t>
         </is>
       </c>
     </row>
@@ -23947,17 +24139,17 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>NAMS</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="E123" s="13" t="n">
-        <v>3487.24569357</v>
+        <v>9160.919039999999</v>
       </c>
       <c r="F123" s="11" t="n">
         <v>0</v>
@@ -23966,11 +24158,11 @@
         <v>0</v>
       </c>
       <c r="H123" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
-          <t>NewAmsterdam Pharma Company N.V.</t>
+          <t>Carvana Co.</t>
         </is>
       </c>
     </row>
@@ -23982,20 +24174,20 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>BILL</t>
+          <t>CHYM</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>4.5</v>
+        <v>7.3</v>
       </c>
       <c r="E124" s="13" t="n">
-        <v>3233.90572569</v>
+        <v>6716.809792</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G124" s="11" t="n">
         <v>0</v>
@@ -24005,7 +24197,7 @@
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>BILL Holdings, Inc.</t>
+          <t>Chime Financial, Inc.</t>
         </is>
       </c>
     </row>
@@ -24017,30 +24209,30 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>EQPT</t>
+          <t>NCLH</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>0.4</v>
+        <v>13.4</v>
       </c>
       <c r="E125" s="13" t="n">
-        <v>2079.28</v>
+        <v>9384.211261600001</v>
       </c>
       <c r="F125" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G125" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H125" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
-          <t>EquipmentShare.com Inc.</t>
+          <t>Norwegian Cruise Line Holdings L</t>
         </is>
       </c>
     </row>
@@ -24052,17 +24244,17 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>BIO</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>3.4</v>
+        <v>0.2</v>
       </c>
       <c r="E126" s="13" t="n">
-        <v>7814.55867564</v>
+        <v>3624.467052850001</v>
       </c>
       <c r="F126" s="11" t="n">
         <v>0</v>
@@ -24075,29 +24267,29 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>Bio-Rad Laboratories, Inc.</t>
+          <t>Netskope, Inc.</t>
         </is>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="14" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>ZG</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>14.4</v>
+        <v>1.3</v>
       </c>
       <c r="E127" s="13" t="n">
-        <v>11983938.23164452</v>
+        <v>7657.30818</v>
       </c>
       <c r="F127" s="11" t="n">
         <v>0</v>
@@ -24110,7 +24302,7 @@
       </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturi</t>
+          <t>Zillow Group, Inc.</t>
         </is>
       </c>
     </row>
@@ -24122,30 +24314,30 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
         <v>8</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>13.4</v>
+        <v>14.4</v>
       </c>
       <c r="E128" s="13" t="n">
-        <v>4459051.48</v>
+        <v>11983938.23164452</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H128" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Taiwan Semiconductor Manufacturi</t>
         </is>
       </c>
     </row>
@@ -24157,20 +24349,20 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
         <v>8</v>
       </c>
       <c r="D129" s="12" t="n">
-        <v>9.1</v>
+        <v>13.4</v>
       </c>
       <c r="E129" s="13" t="n">
-        <v>2628929.97506404</v>
+        <v>4459051.48</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G129" s="11" t="n">
         <v>1</v>
@@ -24180,7 +24372,7 @@
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
     </row>
@@ -24192,20 +24384,20 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>10.8</v>
+        <v>9.1</v>
       </c>
       <c r="E130" s="13" t="n">
-        <v>5098698</v>
+        <v>2628929.97506404</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G130" s="11" t="n">
         <v>1</v>
@@ -24215,7 +24407,7 @@
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
     </row>
@@ -24227,28 +24419,63 @@
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D131" s="12" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="E131" s="13" t="n">
+        <v>5098698</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="14" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="14" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
           <t>AVGO</t>
         </is>
       </c>
-      <c r="C131" s="11" t="n">
+      <c r="C132" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="D131" s="12" t="n">
+      <c r="D132" s="12" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="E131" s="13" t="n">
+      <c r="E132" s="13" t="n">
         <v>1957030.6144473</v>
       </c>
-      <c r="F131" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G131" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H131" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" s="14" t="inlineStr">
+      <c r="F132" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="14" t="inlineStr">
         <is>
           <t>Broadcom Inc.</t>
         </is>
@@ -24472,7 +24699,9 @@
         <v>0</v>
       </c>
       <c r="K7" s="15" t="inlineStr"/>
-      <c r="L7" s="15" t="inlineStr"/>
+      <c r="L7" s="16" t="n">
+        <v>6</v>
+      </c>
       <c r="M7" s="14" t="inlineStr">
         <is>
           <t>Global Partners LP</t>
@@ -25028,7 +25257,7 @@
         </is>
       </c>
       <c r="J20" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K20" s="15" t="inlineStr"/>
       <c r="L20" s="15" t="inlineStr"/>
@@ -25277,7 +25506,7 @@
       <c r="G26" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="16" t="inlineStr"/>
+      <c r="H26" s="17" t="inlineStr"/>
       <c r="I26" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -25502,7 +25731,9 @@
         <v>0</v>
       </c>
       <c r="K31" s="15" t="inlineStr"/>
-      <c r="L31" s="15" t="inlineStr"/>
+      <c r="L31" s="16" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M31" s="14" t="inlineStr">
         <is>
           <t>Northern Oil and Gas, Inc.</t>
@@ -25545,7 +25776,9 @@
         <v>0</v>
       </c>
       <c r="K32" s="15" t="inlineStr"/>
-      <c r="L32" s="15" t="inlineStr"/>
+      <c r="L32" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
           <t>Atlantic Union Bankshares Corporation</t>
@@ -25588,7 +25821,9 @@
         <v>0</v>
       </c>
       <c r="K33" s="15" t="inlineStr"/>
-      <c r="L33" s="15" t="inlineStr"/>
+      <c r="L33" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="M33" s="14" t="inlineStr">
         <is>
           <t>Quest Resource Holding Corporation</t>
@@ -25958,7 +26193,7 @@
       <c r="D49" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E49" s="16" t="inlineStr"/>
+      <c r="E49" s="17" t="inlineStr"/>
       <c r="F49" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -26122,7 +26357,7 @@
       <c r="D57" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E57" s="16" t="inlineStr"/>
+      <c r="E57" s="17" t="inlineStr"/>
       <c r="F57" s="14" t="inlineStr"/>
       <c r="G57" s="14" t="inlineStr"/>
     </row>
@@ -26170,7 +26405,7 @@
       <c r="D59" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E59" s="16" t="inlineStr"/>
+      <c r="E59" s="17" t="inlineStr"/>
       <c r="F59" s="14" t="inlineStr"/>
       <c r="G59" s="14" t="inlineStr"/>
     </row>
@@ -26249,7 +26484,7 @@
       <c r="D62" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E62" s="16" t="inlineStr"/>
+      <c r="E62" s="17" t="inlineStr"/>
       <c r="F62" s="14" t="inlineStr"/>
       <c r="G62" s="14" t="inlineStr"/>
     </row>
@@ -26297,7 +26532,7 @@
       <c r="D64" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E64" s="16" t="inlineStr"/>
+      <c r="E64" s="17" t="inlineStr"/>
       <c r="F64" s="14" t="inlineStr"/>
       <c r="G64" s="14" t="inlineStr"/>
     </row>
@@ -26905,7 +27140,7 @@
         <v>0</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
@@ -27368,7 +27603,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="15" t="inlineStr"/>
-      <c r="L6" s="17" t="n">
+      <c r="L6" s="16" t="n">
         <v>0.3</v>
       </c>
       <c r="M6" s="14" t="inlineStr">
@@ -27413,7 +27648,9 @@
         <v>0</v>
       </c>
       <c r="K7" s="15" t="inlineStr"/>
-      <c r="L7" s="15" t="inlineStr"/>
+      <c r="L7" s="16" t="n">
+        <v>0.2</v>
+      </c>
       <c r="M7" s="14" t="inlineStr">
         <is>
           <t>Waystar Holding Corp.</t>
@@ -27585,7 +27822,9 @@
         <v>0</v>
       </c>
       <c r="K11" s="15" t="inlineStr"/>
-      <c r="L11" s="15" t="inlineStr"/>
+      <c r="L11" s="16" t="n">
+        <v>28.9</v>
+      </c>
       <c r="M11" s="14" t="inlineStr">
         <is>
           <t>Anteris Technologies Global Corp.</t>
@@ -27628,7 +27867,9 @@
         <v>0</v>
       </c>
       <c r="K12" s="15" t="inlineStr"/>
-      <c r="L12" s="15" t="inlineStr"/>
+      <c r="L12" s="16" t="n">
+        <v>3.3</v>
+      </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
           <t>Corcept Therapeutics Incorporated</t>
@@ -27711,7 +27952,7 @@
         </is>
       </c>
       <c r="J14" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K14" s="15" t="inlineStr"/>
       <c r="L14" s="15" t="inlineStr"/>
@@ -29319,7 +29560,7 @@
         <v>0</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
@@ -29424,7 +29665,7 @@
         <v>0</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I69" s="14" t="inlineStr">
         <is>
@@ -29915,7 +30156,7 @@
     <col width="9.5" customWidth="1" min="3" max="3"/>
     <col width="9.5" customWidth="1" min="4" max="4"/>
     <col width="20.5" customWidth="1" min="5" max="5"/>
-    <col width="9.5" customWidth="1" min="6" max="6"/>
+    <col width="8.5" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="20.5" customWidth="1" min="8" max="8"/>
     <col width="34.5" customWidth="1" min="9" max="9"/>
@@ -30136,17 +30377,19 @@
       <c r="G8" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="H8" s="16" t="inlineStr"/>
+      <c r="H8" s="13" t="n">
+        <v>75529.51433999999</v>
+      </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K8" s="15" t="inlineStr"/>
-      <c r="L8" s="17" t="n">
+      <c r="L8" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="14" t="inlineStr">
@@ -30222,10 +30465,12 @@
       <c r="G10" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="16" t="inlineStr"/>
+      <c r="H10" s="13" t="n">
+        <v>44687.48108000001</v>
+      </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J10" s="12" t="n">
@@ -30392,10 +30637,12 @@
       <c r="G14" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="16" t="inlineStr"/>
+      <c r="H14" s="13" t="n">
+        <v>14301.56696</v>
+      </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J14" s="12" t="n">
@@ -30433,7 +30680,7 @@
       <c r="G15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="16" t="inlineStr"/>
+      <c r="H15" s="17" t="inlineStr"/>
       <c r="I15" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -30572,7 +30819,9 @@
         <v>0</v>
       </c>
       <c r="K18" s="15" t="inlineStr"/>
-      <c r="L18" s="15" t="inlineStr"/>
+      <c r="L18" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
           <t>Flutter Entertainment plc</t>
@@ -30787,7 +31036,9 @@
         <v>0</v>
       </c>
       <c r="K23" s="15" t="inlineStr"/>
-      <c r="L23" s="15" t="inlineStr"/>
+      <c r="L23" s="16" t="n">
+        <v>0.2</v>
+      </c>
       <c r="M23" s="14" t="inlineStr">
         <is>
           <t>Waystar Holding Corp.</t>
@@ -30830,7 +31081,9 @@
         <v>2</v>
       </c>
       <c r="K24" s="15" t="inlineStr"/>
-      <c r="L24" s="15" t="inlineStr"/>
+      <c r="L24" s="16" t="n">
+        <v>0.4</v>
+      </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
           <t>WESCO International, Inc.</t>
@@ -30861,7 +31114,7 @@
       <c r="G25" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="16" t="inlineStr"/>
+      <c r="H25" s="17" t="inlineStr"/>
       <c r="I25" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -31031,10 +31284,12 @@
       <c r="G29" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="16" t="inlineStr"/>
+      <c r="H29" s="13" t="n">
+        <v>1462675.48</v>
+      </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J29" s="12" t="n">
@@ -31072,10 +31327,12 @@
       <c r="G30" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="16" t="inlineStr"/>
+      <c r="H30" s="13" t="n">
+        <v>40786.32640656</v>
+      </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J30" s="12" t="n">
@@ -31199,10 +31456,12 @@
       <c r="G33" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="16" t="inlineStr"/>
+      <c r="H33" s="13" t="n">
+        <v>4197.27353648</v>
+      </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J33" s="12" t="n">
@@ -31283,17 +31542,21 @@
       <c r="G35" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="16" t="inlineStr"/>
+      <c r="H35" s="13" t="n">
+        <v>27142.26</v>
+      </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K35" s="15" t="inlineStr"/>
-      <c r="L35" s="15" t="inlineStr"/>
+      <c r="L35" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="M35" s="14" t="inlineStr">
         <is>
           <t>Venture Global, Inc.</t>
@@ -31449,10 +31712,12 @@
       <c r="D45" s="12" t="n">
         <v>6.6</v>
       </c>
-      <c r="E45" s="16" t="inlineStr"/>
+      <c r="E45" s="13" t="n">
+        <v>75529.51433999999</v>
+      </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G45" s="12" t="n">
@@ -31819,17 +32084,17 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>LTH</t>
+          <t>STUB</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>8218.493086959999</v>
+        <v>4197.27353648</v>
       </c>
       <c r="F61" s="11" t="n">
         <v>0</v>
@@ -31842,7 +32107,7 @@
       </c>
       <c r="I61" s="14" t="inlineStr">
         <is>
-          <t>Life Time Group Holdings, Inc.</t>
+          <t>StubHub Holdings, Inc.</t>
         </is>
       </c>
     </row>
@@ -31854,17 +32119,17 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>LOMA</t>
+          <t>LTH</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E62" s="13" t="n">
-        <v>7054.311295590001</v>
+        <v>8218.493086959999</v>
       </c>
       <c r="F62" s="11" t="n">
         <v>0</v>
@@ -31877,7 +32142,7 @@
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>Loma Negra Compañía Industrial A</t>
+          <t>Life Time Group Holdings, Inc.</t>
         </is>
       </c>
     </row>
@@ -31959,30 +32224,30 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D65" s="12" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>28627.75441304</v>
+        <v>75529.51433999999</v>
       </c>
       <c r="F65" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G65" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I65" s="14" t="inlineStr">
         <is>
-          <t>nVent Electric plc</t>
+          <t>DoorDash, Inc.</t>
         </is>
       </c>
     </row>
@@ -31994,17 +32259,17 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>35374.13919885999</v>
+        <v>28627.75441304</v>
       </c>
       <c r="F66" s="11" t="n">
         <v>0</v>
@@ -32017,7 +32282,7 @@
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>Qnity Electronics, Inc.</t>
+          <t>nVent Electric plc</t>
         </is>
       </c>
     </row>
@@ -32029,17 +32294,17 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>ARMK</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D67" s="12" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>14023.31356812</v>
+        <v>44687.48108000001</v>
       </c>
       <c r="F67" s="11" t="n">
         <v>0</v>
@@ -32048,11 +32313,11 @@
         <v>0</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I67" s="14" t="inlineStr">
         <is>
-          <t>Aramark</t>
+          <t>Block, Inc.</t>
         </is>
       </c>
     </row>
@@ -32228,7 +32493,9 @@
         <v>0</v>
       </c>
       <c r="J6" s="15" t="inlineStr"/>
-      <c r="K6" s="15" t="inlineStr"/>
+      <c r="K6" s="16" t="n">
+        <v>6</v>
+      </c>
       <c r="L6" s="15" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr">
         <is>
@@ -32380,17 +32647,21 @@
       <c r="F10" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="16" t="inlineStr"/>
+      <c r="G10" s="13" t="n">
+        <v>20211.75389</v>
+      </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="15" t="inlineStr"/>
-      <c r="K10" s="15" t="inlineStr"/>
+      <c r="K10" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="L10" s="15" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr">
         <is>
@@ -32419,10 +32690,12 @@
       <c r="F11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="16" t="inlineStr"/>
+      <c r="G11" s="13" t="n">
+        <v>1462675.48</v>
+      </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I11" s="12" t="n">
@@ -32458,7 +32731,7 @@
       <c r="F12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="16" t="inlineStr"/>
+      <c r="G12" s="17" t="inlineStr"/>
       <c r="H12" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -32819,10 +33092,12 @@
       <c r="F23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="16" t="inlineStr"/>
+      <c r="G23" s="13" t="n">
+        <v>1462675.48</v>
+      </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I23" s="12" t="n">
@@ -33716,10 +33991,12 @@
         </is>
       </c>
       <c r="I49" s="12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J49" s="15" t="inlineStr"/>
-      <c r="K49" s="15" t="inlineStr"/>
+      <c r="K49" s="16" t="n">
+        <v>37.5</v>
+      </c>
       <c r="L49" s="15" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr">
         <is>
@@ -34234,10 +34511,12 @@
       <c r="F64" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G64" s="16" t="inlineStr"/>
+      <c r="G64" s="13" t="n">
+        <v>27470</v>
+      </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I64" s="12" t="n">
@@ -34285,7 +34564,9 @@
         <v>0</v>
       </c>
       <c r="J65" s="15" t="inlineStr"/>
-      <c r="K65" s="15" t="inlineStr"/>
+      <c r="K65" s="16" t="n">
+        <v>1.2</v>
+      </c>
       <c r="L65" s="15" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr">
         <is>
@@ -34759,10 +35040,12 @@
       <c r="F79" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G79" s="16" t="inlineStr"/>
+      <c r="G79" s="13" t="n">
+        <v>1462675.48</v>
+      </c>
       <c r="H79" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I79" s="12" t="n">
@@ -34839,10 +35122,12 @@
       <c r="F81" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G81" s="16" t="inlineStr"/>
+      <c r="G81" s="13" t="n">
+        <v>14821.13635</v>
+      </c>
       <c r="H81" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I81" s="12" t="n">
@@ -34890,7 +35175,9 @@
         <v>0</v>
       </c>
       <c r="J82" s="15" t="inlineStr"/>
-      <c r="K82" s="15" t="inlineStr"/>
+      <c r="K82" s="16" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L82" s="15" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr">
         <is>
@@ -35405,10 +35692,12 @@
       <c r="F97" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G97" s="16" t="inlineStr"/>
+      <c r="G97" s="13" t="n">
+        <v>4197.27353648</v>
+      </c>
       <c r="H97" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="I97" s="12" t="n">
@@ -35901,7 +36190,9 @@
         <v>0</v>
       </c>
       <c r="J111" s="15" t="inlineStr"/>
-      <c r="K111" s="15" t="inlineStr"/>
+      <c r="K111" s="16" t="n">
+        <v>0.2</v>
+      </c>
       <c r="L111" s="15" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr">
         <is>
@@ -36220,7 +36511,7 @@
         </is>
       </c>
       <c r="I121" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J121" s="15" t="inlineStr"/>
       <c r="K121" s="15" t="inlineStr"/>
@@ -36343,7 +36634,7 @@
         </is>
       </c>
       <c r="I124" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J124" s="15" t="inlineStr"/>
       <c r="K124" s="15" t="inlineStr"/>
@@ -36384,7 +36675,7 @@
         </is>
       </c>
       <c r="I125" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J125" s="15" t="inlineStr"/>
       <c r="K125" s="15" t="inlineStr"/>
@@ -36466,7 +36757,7 @@
         </is>
       </c>
       <c r="I127" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J127" s="15" t="inlineStr"/>
       <c r="K127" s="15" t="inlineStr"/>
@@ -36574,7 +36865,7 @@
       <c r="F132" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G132" s="16" t="inlineStr"/>
+      <c r="G132" s="17" t="inlineStr"/>
       <c r="H132" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -36654,10 +36945,12 @@
       <c r="F134" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G134" s="16" t="inlineStr"/>
+      <c r="G134" s="13" t="n">
+        <v>69.73333682000001</v>
+      </c>
       <c r="H134" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="I134" s="12" t="n">
@@ -36693,10 +36986,12 @@
       <c r="F135" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G135" s="16" t="inlineStr"/>
+      <c r="G135" s="13" t="n">
+        <v>34.23332991</v>
+      </c>
       <c r="H135" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="I135" s="12" t="n">
@@ -36773,7 +37068,7 @@
       <c r="F137" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G137" s="16" t="inlineStr"/>
+      <c r="G137" s="17" t="inlineStr"/>
       <c r="H137" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -36853,7 +37148,7 @@
       <c r="F139" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G139" s="16" t="inlineStr"/>
+      <c r="G139" s="17" t="inlineStr"/>
       <c r="H139" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -36892,10 +37187,12 @@
       <c r="F140" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G140" s="16" t="inlineStr"/>
+      <c r="G140" s="13" t="n">
+        <v>58.77413615</v>
+      </c>
       <c r="H140" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="I140" s="12" t="n">
@@ -36931,7 +37228,7 @@
       <c r="F141" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G141" s="16" t="inlineStr"/>
+      <c r="G141" s="17" t="inlineStr"/>
       <c r="H141" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -37140,7 +37437,7 @@
         <v>5.9</v>
       </c>
       <c r="J148" s="15" t="inlineStr"/>
-      <c r="K148" s="17" t="n">
+      <c r="K148" s="16" t="n">
         <v>0.6</v>
       </c>
       <c r="L148" s="15" t="inlineStr"/>
@@ -37739,17 +38036,19 @@
       <c r="F165" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G165" s="16" t="inlineStr"/>
+      <c r="G165" s="13" t="n">
+        <v>9160.919039999999</v>
+      </c>
       <c r="H165" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="I165" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J165" s="15" t="inlineStr"/>
-      <c r="K165" s="17" t="n">
+      <c r="K165" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L165" s="15" t="inlineStr"/>
@@ -37821,7 +38120,7 @@
       <c r="F167" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G167" s="16" t="inlineStr"/>
+      <c r="G167" s="17" t="inlineStr"/>
       <c r="H167" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -38194,7 +38493,9 @@
         <v>0</v>
       </c>
       <c r="J178" s="15" t="inlineStr"/>
-      <c r="K178" s="15" t="inlineStr"/>
+      <c r="K178" s="16" t="n">
+        <v>6</v>
+      </c>
       <c r="L178" s="15" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr">
         <is>
@@ -38516,7 +38817,7 @@
         <v>0</v>
       </c>
       <c r="J188" s="15" t="inlineStr"/>
-      <c r="K188" s="17" t="n">
+      <c r="K188" s="16" t="n">
         <v>11.4</v>
       </c>
       <c r="L188" s="15" t="inlineStr"/>
@@ -38641,7 +38942,9 @@
         <v>0</v>
       </c>
       <c r="J191" s="15" t="inlineStr"/>
-      <c r="K191" s="15" t="inlineStr"/>
+      <c r="K191" s="16" t="n">
+        <v>0.2</v>
+      </c>
       <c r="L191" s="15" t="inlineStr"/>
       <c r="M191" s="14" t="inlineStr">
         <is>
@@ -38720,7 +39023,7 @@
         </is>
       </c>
       <c r="I193" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J193" s="15" t="inlineStr"/>
       <c r="K193" s="15" t="inlineStr"/>
@@ -38992,10 +39295,12 @@
       <c r="F202" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G202" s="16" t="inlineStr"/>
+      <c r="G202" s="13" t="n">
+        <v>44687.48108000001</v>
+      </c>
       <c r="H202" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I202" s="12" t="n">
@@ -39043,7 +39348,9 @@
         <v>2</v>
       </c>
       <c r="J203" s="15" t="inlineStr"/>
-      <c r="K203" s="15" t="inlineStr"/>
+      <c r="K203" s="16" t="n">
+        <v>0.4</v>
+      </c>
       <c r="L203" s="15" t="inlineStr"/>
       <c r="M203" s="14" t="inlineStr">
         <is>
@@ -39084,7 +39391,9 @@
         <v>0</v>
       </c>
       <c r="J204" s="15" t="inlineStr"/>
-      <c r="K204" s="15" t="inlineStr"/>
+      <c r="K204" s="16" t="n">
+        <v>0.2</v>
+      </c>
       <c r="L204" s="15" t="inlineStr"/>
       <c r="M204" s="14" t="inlineStr">
         <is>
@@ -39195,17 +39504,21 @@
       <c r="F207" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G207" s="16" t="inlineStr"/>
+      <c r="G207" s="13" t="n">
+        <v>27142.26</v>
+      </c>
       <c r="H207" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I207" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J207" s="15" t="inlineStr"/>
-      <c r="K207" s="15" t="inlineStr"/>
+      <c r="K207" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="L207" s="15" t="inlineStr"/>
       <c r="M207" s="14" t="inlineStr">
         <is>
@@ -39275,7 +39588,7 @@
       <c r="F209" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G209" s="16" t="inlineStr"/>
+      <c r="G209" s="17" t="inlineStr"/>
       <c r="H209" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -39314,10 +39627,12 @@
       <c r="F210" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G210" s="16" t="inlineStr"/>
+      <c r="G210" s="13" t="n">
+        <v>4197.27353648</v>
+      </c>
       <c r="H210" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="I210" s="12" t="n">
@@ -39542,7 +39857,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="I7" s="15" t="inlineStr"/>
       <c r="J7" s="15" t="inlineStr"/>
@@ -39582,7 +39897,9 @@
         <v>0</v>
       </c>
       <c r="I8" s="15" t="inlineStr"/>
-      <c r="J8" s="15" t="inlineStr"/>
+      <c r="J8" s="16" t="n">
+        <v>0.1</v>
+      </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
           <t>PENN Entertainment, Inc.</t>
@@ -39693,7 +40010,9 @@
         <v>0</v>
       </c>
       <c r="I11" s="15" t="inlineStr"/>
-      <c r="J11" s="15" t="inlineStr"/>
+      <c r="J11" s="16" t="n">
+        <v>6</v>
+      </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
           <t>Global Partners LP</t>
@@ -39712,10 +40031,12 @@
       <c r="C12" s="12" t="n">
         <v>5.5</v>
       </c>
-      <c r="D12" s="16" t="inlineStr"/>
+      <c r="D12" s="13" t="n">
+        <v>20211.75389</v>
+      </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="F12" s="11" t="n">
@@ -39728,7 +40049,9 @@
         <v>0</v>
       </c>
       <c r="I12" s="15" t="inlineStr"/>
-      <c r="J12" s="15" t="inlineStr"/>
+      <c r="J12" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
           <t>Strategy Inc</t>
@@ -39979,7 +40302,9 @@
         <v>0</v>
       </c>
       <c r="I21" s="15" t="inlineStr"/>
-      <c r="J21" s="15" t="inlineStr"/>
+      <c r="J21" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
           <t>Illumina, Inc.</t>
@@ -40301,7 +40626,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="I32" s="15" t="inlineStr"/>
       <c r="J32" s="15" t="inlineStr"/>
@@ -40378,7 +40703,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="15" t="inlineStr"/>
-      <c r="J34" s="17" t="n">
+      <c r="J34" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="K34" s="14" t="inlineStr">
@@ -40528,7 +40853,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="15" t="inlineStr"/>
-      <c r="J38" s="17" t="n">
+      <c r="J38" s="16" t="n">
         <v>0.5</v>
       </c>
       <c r="K38" s="14" t="inlineStr">
@@ -40726,10 +41051,12 @@
       <c r="C46" s="12" t="n">
         <v>16.4</v>
       </c>
-      <c r="D46" s="16" t="inlineStr"/>
+      <c r="D46" s="13" t="n">
+        <v>1462675.48</v>
+      </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="F46" s="11" t="n">
@@ -40761,10 +41088,12 @@
       <c r="C47" s="12" t="n">
         <v>16.7</v>
       </c>
-      <c r="D47" s="16" t="inlineStr"/>
+      <c r="D47" s="13" t="n">
+        <v>15370.7589144</v>
+      </c>
       <c r="E47" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="F47" s="11" t="n">
@@ -40777,7 +41106,9 @@
         <v>0</v>
       </c>
       <c r="I47" s="15" t="inlineStr"/>
-      <c r="J47" s="15" t="inlineStr"/>
+      <c r="J47" s="16" t="n">
+        <v>5.5</v>
+      </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
           <t>TKO Group Holdings, Inc.</t>
@@ -41028,7 +41359,7 @@
         <v>8.6</v>
       </c>
       <c r="I56" s="15" t="inlineStr"/>
-      <c r="J56" s="17" t="n">
+      <c r="J56" s="16" t="n">
         <v>1</v>
       </c>
       <c r="K56" s="14" t="inlineStr">
@@ -41049,10 +41380,12 @@
       <c r="C57" s="12" t="n">
         <v>17.2</v>
       </c>
-      <c r="D57" s="16" t="inlineStr"/>
+      <c r="D57" s="13" t="n">
+        <v>20211.75389</v>
+      </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="F57" s="11" t="n">
@@ -41065,7 +41398,9 @@
         <v>0</v>
       </c>
       <c r="I57" s="15" t="inlineStr"/>
-      <c r="J57" s="15" t="inlineStr"/>
+      <c r="J57" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="K57" s="14" t="inlineStr">
         <is>
           <t>Strategy Inc</t>
@@ -41387,7 +41722,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>27.4</v>
+        <v>31.3</v>
       </c>
       <c r="I68" s="15" t="inlineStr"/>
       <c r="J68" s="15" t="inlineStr"/>
@@ -41409,7 +41744,7 @@
       <c r="C69" s="12" t="n">
         <v>99.2</v>
       </c>
-      <c r="D69" s="16" t="inlineStr"/>
+      <c r="D69" s="17" t="inlineStr"/>
       <c r="E69" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -41510,7 +41845,7 @@
       <c r="C72" s="12" t="n">
         <v>28.3</v>
       </c>
-      <c r="D72" s="16" t="inlineStr"/>
+      <c r="D72" s="17" t="inlineStr"/>
       <c r="E72" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -41559,7 +41894,9 @@
         <v>0</v>
       </c>
       <c r="I73" s="15" t="inlineStr"/>
-      <c r="J73" s="15" t="inlineStr"/>
+      <c r="J73" s="16" t="n">
+        <v>0.2</v>
+      </c>
       <c r="K73" s="14" t="inlineStr">
         <is>
           <t>Cognizant Technology Solutions C</t>
@@ -41578,7 +41915,7 @@
       <c r="C74" s="12" t="n">
         <v>14.6</v>
       </c>
-      <c r="D74" s="16" t="inlineStr"/>
+      <c r="D74" s="17" t="inlineStr"/>
       <c r="E74" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -41815,7 +42152,9 @@
         <v>0</v>
       </c>
       <c r="I83" s="15" t="inlineStr"/>
-      <c r="J83" s="15" t="inlineStr"/>
+      <c r="J83" s="16" t="n">
+        <v>0.3</v>
+      </c>
       <c r="K83" s="14" t="inlineStr">
         <is>
           <t>Ascendis Pharma A/S</t>
@@ -41923,7 +42262,7 @@
         <v>1</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I86" s="15" t="inlineStr"/>
       <c r="J86" s="15" t="inlineStr"/>
@@ -42332,7 +42671,9 @@
         <v>6.7</v>
       </c>
       <c r="I100" s="15" t="inlineStr"/>
-      <c r="J100" s="15" t="inlineStr"/>
+      <c r="J100" s="16" t="n">
+        <v>37.2</v>
+      </c>
       <c r="K100" s="14" t="inlineStr">
         <is>
           <t>MGM Resorts International</t>
@@ -42676,10 +43017,12 @@
       <c r="C112" s="12" t="n">
         <v>2.2</v>
       </c>
-      <c r="D112" s="16" t="inlineStr"/>
+      <c r="D112" s="13" t="n">
+        <v>1462675.48</v>
+      </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="F112" s="11" t="n">
@@ -42802,7 +43145,7 @@
         <v>0</v>
       </c>
       <c r="I118" s="15" t="inlineStr"/>
-      <c r="J118" s="17" t="n">
+      <c r="J118" s="16" t="n">
         <v>0.1</v>
       </c>
       <c r="K118" s="14" t="inlineStr">
@@ -42841,7 +43184,7 @@
         <v>0</v>
       </c>
       <c r="I119" s="15" t="inlineStr"/>
-      <c r="J119" s="17" t="n">
+      <c r="J119" s="16" t="n">
         <v>0.1</v>
       </c>
       <c r="K119" s="14" t="inlineStr">
@@ -42991,7 +43334,9 @@
         <v>0</v>
       </c>
       <c r="I123" s="15" t="inlineStr"/>
-      <c r="J123" s="15" t="inlineStr"/>
+      <c r="J123" s="16" t="n">
+        <v>0.2</v>
+      </c>
       <c r="K123" s="14" t="inlineStr">
         <is>
           <t>TeraWulf Inc.</t>
@@ -43298,7 +43643,7 @@
       <c r="C134" s="12" t="n">
         <v>30.3</v>
       </c>
-      <c r="D134" s="16" t="inlineStr"/>
+      <c r="D134" s="17" t="inlineStr"/>
       <c r="E134" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -43311,10 +43656,12 @@
         <v>0</v>
       </c>
       <c r="H134" s="12" t="n">
-        <v>0</v>
+        <v>76.5</v>
       </c>
       <c r="I134" s="15" t="inlineStr"/>
-      <c r="J134" s="15" t="inlineStr"/>
+      <c r="J134" s="16" t="n">
+        <v>0.2</v>
+      </c>
       <c r="K134" s="14" t="inlineStr"/>
     </row>
     <row r="135" ht="18" customHeight="1">
@@ -43421,7 +43768,9 @@
         <v>0</v>
       </c>
       <c r="I137" s="15" t="inlineStr"/>
-      <c r="J137" s="15" t="inlineStr"/>
+      <c r="J137" s="16" t="n">
+        <v>5</v>
+      </c>
       <c r="K137" s="14" t="inlineStr">
         <is>
           <t>Vail Resorts, Inc.</t>
@@ -43524,7 +43873,9 @@
         <v>0</v>
       </c>
       <c r="I142" s="15" t="inlineStr"/>
-      <c r="J142" s="15" t="inlineStr"/>
+      <c r="J142" s="16" t="n">
+        <v>1.3</v>
+      </c>
       <c r="K142" s="14" t="inlineStr">
         <is>
           <t>Grupo Aeromexico, S.A.B. de C.V</t>
@@ -43728,7 +44079,7 @@
       <c r="C148" s="12" t="n">
         <v>26.4</v>
       </c>
-      <c r="D148" s="16" t="inlineStr"/>
+      <c r="D148" s="17" t="inlineStr"/>
       <c r="E148" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -43873,7 +44224,7 @@
       <c r="C155" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="D155" s="16" t="inlineStr"/>
+      <c r="D155" s="17" t="inlineStr"/>
       <c r="E155" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -43993,7 +44344,7 @@
         <v>0</v>
       </c>
       <c r="H158" s="12" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="I158" s="15" t="inlineStr"/>
       <c r="J158" s="15" t="inlineStr"/>
@@ -44104,7 +44455,7 @@
         <v>0</v>
       </c>
       <c r="H161" s="12" t="n">
-        <v>0</v>
+        <v>21.6</v>
       </c>
       <c r="I161" s="15" t="inlineStr"/>
       <c r="J161" s="15" t="inlineStr"/>
@@ -44594,10 +44945,12 @@
       <c r="C180" s="12" t="n">
         <v>31.1</v>
       </c>
-      <c r="D180" s="16" t="inlineStr"/>
+      <c r="D180" s="13" t="n">
+        <v>9160.919039999999</v>
+      </c>
       <c r="E180" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="F180" s="11" t="n">
@@ -44610,7 +44963,7 @@
         <v>5</v>
       </c>
       <c r="I180" s="15" t="inlineStr"/>
-      <c r="J180" s="17" t="n">
+      <c r="J180" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K180" s="14" t="inlineStr">
@@ -44631,10 +44984,12 @@
       <c r="C181" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="D181" s="16" t="inlineStr"/>
+      <c r="D181" s="13" t="n">
+        <v>1462675.48</v>
+      </c>
       <c r="E181" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="F181" s="11" t="n">
@@ -44795,7 +45150,9 @@
         <v>0</v>
       </c>
       <c r="I185" s="15" t="inlineStr"/>
-      <c r="J185" s="15" t="inlineStr"/>
+      <c r="J185" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="K185" s="14" t="inlineStr">
         <is>
           <t>Interactive Brokers Group, Inc.</t>
@@ -44917,7 +45274,7 @@
       <c r="C191" s="12" t="n">
         <v>85.8</v>
       </c>
-      <c r="D191" s="16" t="inlineStr"/>
+      <c r="D191" s="17" t="inlineStr"/>
       <c r="E191" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -45026,10 +45383,12 @@
       <c r="C194" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="D194" s="16" t="inlineStr"/>
+      <c r="D194" s="13" t="n">
+        <v>20211.75389</v>
+      </c>
       <c r="E194" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="F194" s="11" t="n">
@@ -45042,7 +45401,9 @@
         <v>0</v>
       </c>
       <c r="I194" s="15" t="inlineStr"/>
-      <c r="J194" s="15" t="inlineStr"/>
+      <c r="J194" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="K194" s="14" t="inlineStr">
         <is>
           <t>Strategy Inc</t>
@@ -45312,7 +45673,7 @@
       <c r="C204" s="12" t="n">
         <v>15.3</v>
       </c>
-      <c r="D204" s="16" t="inlineStr"/>
+      <c r="D204" s="17" t="inlineStr"/>
       <c r="E204" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -45361,7 +45722,9 @@
         <v>0</v>
       </c>
       <c r="I205" s="15" t="inlineStr"/>
-      <c r="J205" s="15" t="inlineStr"/>
+      <c r="J205" s="16" t="n">
+        <v>7.8</v>
+      </c>
       <c r="K205" s="14" t="inlineStr">
         <is>
           <t>Zentalis Pharmaceuticals, Inc.</t>
@@ -46609,7 +46972,9 @@
         <v>0</v>
       </c>
       <c r="I247" s="15" t="inlineStr"/>
-      <c r="J247" s="15" t="inlineStr"/>
+      <c r="J247" s="16" t="n">
+        <v>6</v>
+      </c>
       <c r="K247" s="14" t="inlineStr">
         <is>
           <t>Global Partners LP</t>
@@ -46867,7 +47232,7 @@
         <v>16</v>
       </c>
       <c r="I257" s="15" t="inlineStr"/>
-      <c r="J257" s="17" t="n">
+      <c r="J257" s="16" t="n">
         <v>0.3</v>
       </c>
       <c r="K257" s="14" t="inlineStr">
@@ -47120,7 +47485,9 @@
         <v>0</v>
       </c>
       <c r="I266" s="15" t="inlineStr"/>
-      <c r="J266" s="15" t="inlineStr"/>
+      <c r="J266" s="16" t="n">
+        <v>0.1</v>
+      </c>
       <c r="K266" s="14" t="inlineStr">
         <is>
           <t>Pitney Bowes Inc.</t>
@@ -47139,10 +47506,12 @@
       <c r="C267" s="12" t="n">
         <v>43.3</v>
       </c>
-      <c r="D267" s="16" t="inlineStr"/>
+      <c r="D267" s="13" t="n">
+        <v>11596.12</v>
+      </c>
       <c r="E267" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="F267" s="11" t="n">
@@ -47174,10 +47543,12 @@
       <c r="C268" s="12" t="n">
         <v>29.8</v>
       </c>
-      <c r="D268" s="16" t="inlineStr"/>
+      <c r="D268" s="13" t="n">
+        <v>9160.919039999999</v>
+      </c>
       <c r="E268" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="F268" s="11" t="n">
@@ -47190,7 +47561,7 @@
         <v>5</v>
       </c>
       <c r="I268" s="15" t="inlineStr"/>
-      <c r="J268" s="17" t="n">
+      <c r="J268" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K268" s="14" t="inlineStr">
@@ -47322,7 +47693,7 @@
       <c r="C272" s="12" t="n">
         <v>8.5</v>
       </c>
-      <c r="D272" s="16" t="inlineStr"/>
+      <c r="D272" s="17" t="inlineStr"/>
       <c r="E272" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -47567,10 +47938,12 @@
       <c r="C281" s="12" t="n">
         <v>14.3</v>
       </c>
-      <c r="D281" s="16" t="inlineStr"/>
+      <c r="D281" s="13" t="n">
+        <v>2823.53281114</v>
+      </c>
       <c r="E281" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="F281" s="11" t="n">
@@ -47583,7 +47956,9 @@
         <v>0</v>
       </c>
       <c r="I281" s="15" t="inlineStr"/>
-      <c r="J281" s="15" t="inlineStr"/>
+      <c r="J281" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="K281" s="14" t="inlineStr">
         <is>
           <t>CarGurus, Inc.</t>
@@ -48370,10 +48745,12 @@
       <c r="C308" s="12" t="n">
         <v>4.4</v>
       </c>
-      <c r="D308" s="16" t="inlineStr"/>
+      <c r="D308" s="13" t="n">
+        <v>9160.919039999999</v>
+      </c>
       <c r="E308" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="F308" s="11" t="n">
@@ -48386,7 +48763,7 @@
         <v>5</v>
       </c>
       <c r="I308" s="15" t="inlineStr"/>
-      <c r="J308" s="17" t="n">
+      <c r="J308" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K308" s="14" t="inlineStr">
@@ -48554,10 +48931,12 @@
       <c r="C316" s="12" t="n">
         <v>81.7</v>
       </c>
-      <c r="D316" s="16" t="inlineStr"/>
+      <c r="D316" s="13" t="n">
+        <v>9160.919039999999</v>
+      </c>
       <c r="E316" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="F316" s="11" t="n">
@@ -48570,7 +48949,7 @@
         <v>5</v>
       </c>
       <c r="I316" s="15" t="inlineStr"/>
-      <c r="J316" s="17" t="n">
+      <c r="J316" s="16" t="n">
         <v>0</v>
       </c>
       <c r="K316" s="14" t="inlineStr">
@@ -49404,10 +49783,12 @@
         <v>1</v>
       </c>
       <c r="H343" s="12" t="n">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="I343" s="15" t="inlineStr"/>
-      <c r="J343" s="15" t="inlineStr"/>
+      <c r="J343" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="K343" s="14" t="inlineStr">
         <is>
           <t>Texas Pacific Land Corporation</t>
@@ -49481,7 +49862,9 @@
         <v>0</v>
       </c>
       <c r="I345" s="15" t="inlineStr"/>
-      <c r="J345" s="15" t="inlineStr"/>
+      <c r="J345" s="16" t="n">
+        <v>0.3</v>
+      </c>
       <c r="K345" s="14" t="inlineStr">
         <is>
           <t>Ascendis Pharma A/S</t>
@@ -49500,10 +49883,12 @@
       <c r="C346" s="12" t="n">
         <v>15.2</v>
       </c>
-      <c r="D346" s="16" t="inlineStr"/>
+      <c r="D346" s="13" t="n">
+        <v>21933.42174</v>
+      </c>
       <c r="E346" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="F346" s="11" t="n">
@@ -50007,7 +50392,7 @@
       <c r="C365" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="D365" s="16" t="inlineStr"/>
+      <c r="D365" s="17" t="inlineStr"/>
       <c r="E365" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -50116,7 +50501,7 @@
       <c r="C368" s="12" t="n">
         <v>0.7</v>
       </c>
-      <c r="D368" s="16" t="inlineStr"/>
+      <c r="D368" s="17" t="inlineStr"/>
       <c r="E368" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -50188,7 +50573,7 @@
       <c r="C370" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="D370" s="16" t="inlineStr"/>
+      <c r="D370" s="17" t="inlineStr"/>
       <c r="E370" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -50223,10 +50608,12 @@
       <c r="C371" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="D371" s="16" t="inlineStr"/>
+      <c r="D371" s="13" t="n">
+        <v>58.77413615</v>
+      </c>
       <c r="E371" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="F371" s="11" t="n">
@@ -50258,7 +50645,7 @@
       <c r="C372" s="12" t="n">
         <v>0.6</v>
       </c>
-      <c r="D372" s="16" t="inlineStr"/>
+      <c r="D372" s="17" t="inlineStr"/>
       <c r="E372" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -50493,7 +50880,9 @@
         <v>0</v>
       </c>
       <c r="K6" s="15" t="inlineStr"/>
-      <c r="L6" s="15" t="inlineStr"/>
+      <c r="L6" s="16" t="n">
+        <v>6</v>
+      </c>
       <c r="M6" s="14" t="inlineStr">
         <is>
           <t>Global Partners LP</t>
@@ -50653,17 +51042,21 @@
       <c r="G10" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="16" t="inlineStr"/>
+      <c r="H10" s="13" t="n">
+        <v>20211.75389</v>
+      </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K10" s="15" t="inlineStr"/>
-      <c r="L10" s="15" t="inlineStr"/>
+      <c r="L10" s="16" t="n">
+        <v>1</v>
+      </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
           <t>Strategy Inc</t>
@@ -50694,10 +51087,12 @@
       <c r="G11" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="16" t="inlineStr"/>
+      <c r="H11" s="13" t="n">
+        <v>1462675.48</v>
+      </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J11" s="12" t="n">
@@ -50864,7 +51259,7 @@
       <c r="G15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="16" t="inlineStr"/>
+      <c r="H15" s="17" t="inlineStr"/>
       <c r="I15" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -50991,7 +51386,7 @@
       <c r="G18" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="16" t="inlineStr"/>
+      <c r="H18" s="17" t="inlineStr"/>
       <c r="I18" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -51032,10 +51427,12 @@
       <c r="G19" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="16" t="inlineStr"/>
+      <c r="H19" s="13" t="n">
+        <v>58.77413615</v>
+      </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="J19" s="12" t="n">
@@ -51073,10 +51470,12 @@
       <c r="G20" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="16" t="inlineStr"/>
+      <c r="H20" s="13" t="n">
+        <v>0.5750000000000001</v>
+      </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="J20" s="12" t="n">
@@ -51110,10 +51509,12 @@
       <c r="G21" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="16" t="inlineStr"/>
+      <c r="H21" s="13" t="n">
+        <v>1.8</v>
+      </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="J21" s="12" t="n">
@@ -51151,7 +51552,7 @@
       <c r="G22" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="16" t="inlineStr"/>
+      <c r="H22" s="17" t="inlineStr"/>
       <c r="I22" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -51161,7 +51562,9 @@
         <v>0</v>
       </c>
       <c r="K22" s="15" t="inlineStr"/>
-      <c r="L22" s="15" t="inlineStr"/>
+      <c r="L22" s="16" t="n">
+        <v>3.4</v>
+      </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
           <t>Muzero Acquisition Corp</t>
@@ -51192,14 +51595,14 @@
       <c r="G23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="16" t="inlineStr"/>
+      <c r="H23" s="17" t="inlineStr"/>
       <c r="I23" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
       <c r="J23" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K23" s="15" t="inlineStr"/>
       <c r="L23" s="15" t="inlineStr"/>
@@ -51233,10 +51636,12 @@
       <c r="G24" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="16" t="inlineStr"/>
+      <c r="H24" s="13" t="n">
+        <v>2.32575</v>
+      </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="J24" s="12" t="n">
@@ -51274,7 +51679,7 @@
       <c r="G25" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="16" t="inlineStr"/>
+      <c r="H25" s="17" t="inlineStr"/>
       <c r="I25" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -51397,7 +51802,7 @@
       <c r="G28" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="16" t="inlineStr"/>
+      <c r="H28" s="17" t="inlineStr"/>
       <c r="I28" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -51481,7 +51886,7 @@
       <c r="G30" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="16" t="inlineStr"/>
+      <c r="H30" s="17" t="inlineStr"/>
       <c r="I30" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -51522,7 +51927,7 @@
       <c r="G31" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="16" t="inlineStr"/>
+      <c r="H31" s="17" t="inlineStr"/>
       <c r="I31" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -51606,10 +52011,12 @@
       <c r="G33" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="16" t="inlineStr"/>
+      <c r="H33" s="13" t="n">
+        <v>0.5329999466999999</v>
+      </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="J33" s="12" t="n">
@@ -51647,7 +52054,7 @@
       <c r="G34" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="16" t="inlineStr"/>
+      <c r="H34" s="17" t="inlineStr"/>
       <c r="I34" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -51688,7 +52095,7 @@
       <c r="G35" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="16" t="inlineStr"/>
+      <c r="H35" s="17" t="inlineStr"/>
       <c r="I35" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -51835,10 +52242,12 @@
       <c r="D42" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="16" t="inlineStr"/>
+      <c r="E42" s="13" t="n">
+        <v>9053.593919999999</v>
+      </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G42" s="12" t="n">
@@ -51865,10 +52274,12 @@
       <c r="D43" s="12" t="n">
         <v>3.7</v>
       </c>
-      <c r="E43" s="16" t="inlineStr"/>
+      <c r="E43" s="13" t="n">
+        <v>8729.92288</v>
+      </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G43" s="12" t="n">
@@ -51968,7 +52379,7 @@
         </is>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
@@ -51991,7 +52402,7 @@
       <c r="D47" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E47" s="16" t="inlineStr"/>
+      <c r="E47" s="17" t="inlineStr"/>
       <c r="F47" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -52149,7 +52560,7 @@
       <c r="D52" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="16" t="inlineStr"/>
+      <c r="E52" s="17" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -52179,10 +52590,12 @@
       <c r="D53" s="12" t="n">
         <v>9.9</v>
       </c>
-      <c r="E53" s="16" t="inlineStr"/>
+      <c r="E53" s="13" t="n">
+        <v>445.7924025</v>
+      </c>
       <c r="F53" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G53" s="12" t="n">
@@ -52314,7 +52727,7 @@
         </is>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0</v>
+        <v>17.9</v>
       </c>
       <c r="H57" s="14" t="inlineStr">
         <is>
@@ -52484,10 +52897,12 @@
       <c r="D65" s="12" t="n">
         <v>2.8</v>
       </c>
-      <c r="E65" s="16" t="inlineStr"/>
+      <c r="E65" s="13" t="n">
+        <v>40786.32640656</v>
+      </c>
       <c r="F65" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G65" s="12" t="n">
@@ -52578,7 +52993,7 @@
       <c r="D68" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E68" s="16" t="inlineStr"/>
+      <c r="E68" s="17" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -52800,10 +53215,12 @@
       <c r="D75" s="12" t="n">
         <v>5.5</v>
       </c>
-      <c r="E75" s="16" t="inlineStr"/>
+      <c r="E75" s="13" t="n">
+        <v>14475.42</v>
+      </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G75" s="12" t="n">
@@ -52862,7 +53279,7 @@
       <c r="D77" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E77" s="16" t="inlineStr"/>
+      <c r="E77" s="17" t="inlineStr"/>
       <c r="F77" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -52920,7 +53337,7 @@
       <c r="D79" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E79" s="16" t="inlineStr"/>
+      <c r="E79" s="17" t="inlineStr"/>
       <c r="F79" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -52959,7 +53376,7 @@
         </is>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
@@ -53123,7 +53540,7 @@
       <c r="D88" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="E88" s="16" t="inlineStr"/>
+      <c r="E88" s="17" t="inlineStr"/>
       <c r="F88" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -53237,7 +53654,7 @@
       <c r="D92" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E92" s="16" t="inlineStr"/>
+      <c r="E92" s="17" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr"/>
       <c r="G92" s="14" t="inlineStr"/>
     </row>
@@ -53281,7 +53698,7 @@
       <c r="D94" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E94" s="16" t="inlineStr"/>
+      <c r="E94" s="17" t="inlineStr"/>
       <c r="F94" s="14" t="inlineStr"/>
       <c r="G94" s="14" t="inlineStr"/>
     </row>
@@ -53298,7 +53715,7 @@
       <c r="D95" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E95" s="16" t="inlineStr"/>
+      <c r="E95" s="17" t="inlineStr"/>
       <c r="F95" s="14" t="inlineStr"/>
       <c r="G95" s="14" t="inlineStr"/>
     </row>
@@ -53563,7 +53980,7 @@
       <c r="D104" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E104" s="16" t="inlineStr"/>
+      <c r="E104" s="17" t="inlineStr"/>
       <c r="F104" s="14" t="inlineStr"/>
       <c r="G104" s="14" t="inlineStr"/>
     </row>
@@ -53631,17 +54048,17 @@
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>SCAGW</t>
+          <t>REEWF</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D109" s="12" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E109" s="13" t="n">
-        <v>4.262395528</v>
+        <v>0.5750000000000001</v>
       </c>
       <c r="F109" s="11" t="n">
         <v>0</v>
@@ -53652,11 +54069,7 @@
       <c r="H109" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I109" s="14" t="inlineStr">
-        <is>
-          <t>Scage Future</t>
-        </is>
-      </c>
+      <c r="I109" s="14" t="inlineStr"/>
     </row>
     <row r="110" ht="18" customHeight="1">
       <c r="A110" s="14" t="inlineStr">
@@ -53666,17 +54079,17 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>NBRGU</t>
+          <t>ONCHW</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E110" s="13" t="n">
-        <v>14.590625</v>
+        <v>1.8</v>
       </c>
       <c r="F110" s="11" t="n">
         <v>0</v>
@@ -53689,7 +54102,7 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>Newbridge Acquisition Limited</t>
+          <t>1RT Acquisition Corp.</t>
         </is>
       </c>
     </row>
@@ -53701,17 +54114,17 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>ENHA</t>
+          <t>MESHW</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="E111" s="13" t="n">
-        <v>45.33300069</v>
+        <v>2.32575</v>
       </c>
       <c r="F111" s="11" t="n">
         <v>0</v>
@@ -53724,7 +54137,7 @@
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
-          <t>Enhanced Group Inc.</t>
+          <t>Meshflow Acquisition Corp.</t>
         </is>
       </c>
     </row>
@@ -53736,17 +54149,17 @@
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>ALDFW</t>
+          <t>EMISR</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="E112" s="13" t="n">
-        <v>8.963451021399999</v>
+        <v>0.5329999466999999</v>
       </c>
       <c r="F112" s="11" t="n">
         <v>0</v>
@@ -53759,7 +54172,7 @@
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>Aldel Financial II Inc.</t>
+          <t>Emmis Acquisition Corp.</t>
         </is>
       </c>
     </row>
@@ -53771,17 +54184,17 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>BPACU</t>
+          <t>LFACW</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E113" s="13" t="n">
-        <v>14.7775</v>
+        <v>1.33333344</v>
       </c>
       <c r="F113" s="11" t="n">
         <v>0</v>
@@ -53794,7 +54207,7 @@
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
-          <t>Blueport Acquisition Ltd</t>
+          <t>Leapfrog Acquisition Corporation</t>
         </is>
       </c>
     </row>
@@ -53876,17 +54289,17 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>GLED-UN</t>
+          <t>MKLYU</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D116" s="12" t="n">
         <v>0.7</v>
       </c>
       <c r="E116" s="13" t="n">
-        <v>161.902725</v>
+        <v>58.77413615</v>
       </c>
       <c r="F116" s="11" t="n">
         <v>0</v>
@@ -53899,7 +54312,7 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>GalaxyEdge Acquisition Corporat</t>
+          <t>McKinley Acquisition Corporation</t>
         </is>
       </c>
     </row>
@@ -53911,17 +54324,17 @@
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>SSAC</t>
+          <t>GIX</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
         <v>7</v>
       </c>
       <c r="D117" s="12" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="E117" s="13" t="n">
-        <v>181.917485755</v>
+        <v>70.11389728</v>
       </c>
       <c r="F117" s="11" t="n">
         <v>0</v>
@@ -53934,7 +54347,7 @@
       </c>
       <c r="I117" s="14" t="inlineStr">
         <is>
-          <t>SPACSphere Acquisition Corp.</t>
+          <t>GigCapital9 Corp.</t>
         </is>
       </c>
     </row>
@@ -53946,17 +54359,17 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>LEGT</t>
+          <t>GLED-UN</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
         <v>8</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="E118" s="13" t="n">
-        <v>245.61005</v>
+        <v>161.902725</v>
       </c>
       <c r="F118" s="11" t="n">
         <v>0</v>
@@ -53969,7 +54382,7 @@
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>Legato Merger Corp. III</t>
+          <t>GalaxyEdge Acquisition Corporat</t>
         </is>
       </c>
     </row>
@@ -54035,7 +54448,7 @@
         <v>0</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>27.4</v>
+        <v>31.3</v>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
@@ -54210,7 +54623,7 @@
         <v>0</v>
       </c>
       <c r="H125" s="12" t="n">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
@@ -54346,7 +54759,7 @@
         <v>1</v>
       </c>
       <c r="H129" s="12" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
@@ -54467,20 +54880,20 @@
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D133" s="12" t="n">
-        <v>5.6</v>
+        <v>17.2</v>
       </c>
       <c r="E133" s="13" t="n">
-        <v>4459051.48</v>
+        <v>20211.75389</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G133" s="11" t="n">
         <v>0</v>
@@ -54490,7 +54903,7 @@
       </c>
       <c r="I133" s="14" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
     </row>
@@ -54786,10 +55199,12 @@
       <c r="G9" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="H9" s="16" t="inlineStr"/>
+      <c r="H9" s="13" t="n">
+        <v>1462675.48</v>
+      </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J9" s="12" t="n">
@@ -55730,10 +56145,12 @@
       <c r="G31" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="16" t="inlineStr"/>
+      <c r="H31" s="13" t="n">
+        <v>21933.42174</v>
+      </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J31" s="12" t="n">
@@ -56145,10 +56562,12 @@
       <c r="D45" s="12" t="n">
         <v>6.1</v>
       </c>
-      <c r="E45" s="16" t="inlineStr"/>
+      <c r="E45" s="13" t="n">
+        <v>62159.65</v>
+      </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G45" s="12" t="n">
@@ -56706,10 +57125,12 @@
       <c r="D65" s="12" t="n">
         <v>15.2</v>
       </c>
-      <c r="E65" s="16" t="inlineStr"/>
+      <c r="E65" s="13" t="n">
+        <v>21933.42174</v>
+      </c>
       <c r="F65" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G65" s="12" t="n">
@@ -56800,10 +57221,12 @@
       <c r="D68" s="12" t="n">
         <v>2.1</v>
       </c>
-      <c r="E68" s="16" t="inlineStr"/>
+      <c r="E68" s="13" t="n">
+        <v>1456.70767283</v>
+      </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>small</t>
         </is>
       </c>
       <c r="G68" s="12" t="n">
@@ -56935,7 +57358,7 @@
         </is>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
@@ -57022,7 +57445,7 @@
       <c r="D75" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E75" s="16" t="inlineStr"/>
+      <c r="E75" s="17" t="inlineStr"/>
       <c r="F75" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -57052,7 +57475,7 @@
       <c r="D76" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E76" s="16" t="inlineStr"/>
+      <c r="E76" s="17" t="inlineStr"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -57174,10 +57597,12 @@
       <c r="D80" s="12" t="n">
         <v>7.7</v>
       </c>
-      <c r="E80" s="16" t="inlineStr"/>
+      <c r="E80" s="13" t="n">
+        <v>54313.77967512</v>
+      </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G80" s="12" t="n">
@@ -57284,10 +57709,12 @@
       <c r="D86" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="E86" s="16" t="inlineStr"/>
+      <c r="E86" s="13" t="n">
+        <v>9160.919039999999</v>
+      </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -57313,10 +57740,12 @@
       <c r="D87" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="E87" s="16" t="inlineStr"/>
+      <c r="E87" s="13" t="n">
+        <v>9160.919039999999</v>
+      </c>
       <c r="F87" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G87" s="14" t="inlineStr">
@@ -57493,7 +57922,7 @@
       <c r="D93" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E93" s="16" t="inlineStr"/>
+      <c r="E93" s="17" t="inlineStr"/>
       <c r="F93" s="14" t="inlineStr"/>
       <c r="G93" s="14" t="inlineStr"/>
     </row>
@@ -57665,7 +58094,7 @@
       <c r="D99" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E99" s="16" t="inlineStr"/>
+      <c r="E99" s="17" t="inlineStr"/>
       <c r="F99" s="14" t="inlineStr"/>
       <c r="G99" s="14" t="inlineStr"/>
     </row>
@@ -57989,17 +58418,17 @@
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>XRXDW</t>
+          <t>MOVAA</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E112" s="13" t="n">
-        <v>39.75700174399999</v>
+        <v>44.382</v>
       </c>
       <c r="F112" s="11" t="n">
         <v>0</v>
@@ -58010,11 +58439,7 @@
       <c r="H112" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I112" s="14" t="inlineStr">
-        <is>
-          <t>Xerox Holdings Corporation</t>
-        </is>
-      </c>
+      <c r="I112" s="14" t="inlineStr"/>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="14" t="inlineStr">
@@ -58024,17 +58449,17 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>ARCXF</t>
+          <t>XRXDW</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="E113" s="13" t="n">
-        <v>44.6780855753</v>
+        <v>39.75700174399999</v>
       </c>
       <c r="F113" s="11" t="n">
         <v>0</v>
@@ -58047,7 +58472,7 @@
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
-          <t>ArcelorMittal South Africa Limit</t>
+          <t>Xerox Holdings Corporation</t>
         </is>
       </c>
     </row>
@@ -58059,17 +58484,17 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>SURG</t>
+          <t>ARCXF</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="E114" s="13" t="n">
-        <v>10.5511959</v>
+        <v>44.6780855753</v>
       </c>
       <c r="F114" s="11" t="n">
         <v>0</v>
@@ -58082,7 +58507,7 @@
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>SurgePays, Inc.</t>
+          <t>ArcelorMittal South Africa Limit</t>
         </is>
       </c>
     </row>
@@ -58374,20 +58799,20 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>CODI</t>
+          <t>EVC</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>11.5</v>
+        <v>12.2</v>
       </c>
       <c r="E123" s="13" t="n">
-        <v>760.63561626</v>
+        <v>906.9768327999999</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G123" s="11" t="n">
         <v>0</v>
@@ -58397,7 +58822,7 @@
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
-          <t>Compass Diversified</t>
+          <t>Entravision Communications Corpo</t>
         </is>
       </c>
     </row>
@@ -58409,20 +58834,20 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>KW</t>
+          <t>CODI</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="E124" s="13" t="n">
-        <v>1521.191763</v>
+        <v>760.63561626</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G124" s="11" t="n">
         <v>0</v>
@@ -58432,7 +58857,7 @@
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>Kennedy-Wilson Holdings, Inc.</t>
+          <t>Compass Diversified</t>
         </is>
       </c>
     </row>
@@ -58444,30 +58869,30 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>JOE</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
         <v>5</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>79.7</v>
+        <v>81.7</v>
       </c>
       <c r="E125" s="13" t="n">
-        <v>3785.59865124</v>
+        <v>9160.919039999999</v>
       </c>
       <c r="F125" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G125" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H125" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
-          <t>The St. Joe Company</t>
+          <t>Carvana Co.</t>
         </is>
       </c>
     </row>
@@ -58479,17 +58904,17 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>BRSL</t>
+          <t>JOE</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>42.2</v>
+        <v>79.7</v>
       </c>
       <c r="E126" s="13" t="n">
-        <v>2113.29115491</v>
+        <v>3785.59865124</v>
       </c>
       <c r="F126" s="11" t="n">
         <v>0</v>
@@ -58502,7 +58927,7 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>Brightstar Lottery PLC</t>
+          <t>The St. Joe Company</t>
         </is>
       </c>
     </row>
@@ -58514,17 +58939,17 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>GPI</t>
+          <t>BRSL</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>47.7</v>
+        <v>42.2</v>
       </c>
       <c r="E127" s="13" t="n">
-        <v>3726.03811988</v>
+        <v>2113.29115491</v>
       </c>
       <c r="F127" s="11" t="n">
         <v>0</v>
@@ -58537,7 +58962,7 @@
       </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
-          <t>Group 1 Automotive, Inc.</t>
+          <t>Brightstar Lottery PLC</t>
         </is>
       </c>
     </row>
@@ -58549,17 +58974,17 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>TDGMW</t>
+          <t>GPI</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>35.4</v>
+        <v>47.7</v>
       </c>
       <c r="E128" s="13" t="n">
-        <v>3033.569772</v>
+        <v>3726.03811988</v>
       </c>
       <c r="F128" s="11" t="n">
         <v>0</v>
@@ -58568,11 +58993,11 @@
         <v>0</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>Tidewater Inc.</t>
+          <t>Group 1 Automotive, Inc.</t>
         </is>
       </c>
     </row>
@@ -58584,17 +59009,17 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>TDGMW</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D129" s="12" t="n">
-        <v>30.5</v>
+        <v>35.4</v>
       </c>
       <c r="E129" s="13" t="n">
-        <v>4054.238496</v>
+        <v>3033.569772</v>
       </c>
       <c r="F129" s="11" t="n">
         <v>0</v>
@@ -58603,11 +59028,11 @@
         <v>0</v>
       </c>
       <c r="H129" s="12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>Interactive Brokers Group, Inc.</t>
+          <t>Tidewater Inc.</t>
         </is>
       </c>
     </row>
@@ -58759,30 +59184,30 @@
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>28.6</v>
+        <v>19.6</v>
       </c>
       <c r="E134" s="13" t="n">
-        <v>5098698</v>
+        <v>1462675.48</v>
       </c>
       <c r="F134" s="11" t="n">
         <v>1</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H134" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
     </row>
@@ -58813,11 +59238,11 @@
     <col width="33.5" customWidth="1" min="2" max="2"/>
     <col width="9.5" customWidth="1" min="3" max="3"/>
     <col width="9.5" customWidth="1" min="4" max="4"/>
-    <col width="23.5" customWidth="1" min="5" max="5"/>
+    <col width="20.5" customWidth="1" min="5" max="5"/>
     <col width="9.5" customWidth="1" min="6" max="6"/>
     <col width="33.5" customWidth="1" min="7" max="7"/>
     <col width="40.5" customWidth="1" min="8" max="8"/>
-    <col width="33.5" customWidth="1" min="9" max="9"/>
+    <col width="34.5" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="8.5" customWidth="1" min="11" max="11"/>
     <col width="8.5" customWidth="1" min="12" max="12"/>
@@ -59336,10 +59761,12 @@
       <c r="G15" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="H15" s="16" t="inlineStr"/>
+      <c r="H15" s="13" t="n">
+        <v>1462675.48</v>
+      </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J15" s="12" t="n">
@@ -59893,7 +60320,7 @@
       <c r="G28" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="16" t="inlineStr"/>
+      <c r="H28" s="17" t="inlineStr"/>
       <c r="I28" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -59946,7 +60373,9 @@
         <v>0</v>
       </c>
       <c r="K29" s="15" t="inlineStr"/>
-      <c r="L29" s="15" t="inlineStr"/>
+      <c r="L29" s="16" t="n">
+        <v>0.9</v>
+      </c>
       <c r="M29" s="14" t="inlineStr">
         <is>
           <t>Expand Energy Corporation</t>
@@ -60469,7 +60898,7 @@
       <c r="D46" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E46" s="16" t="inlineStr"/>
+      <c r="E46" s="17" t="inlineStr"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -60495,7 +60924,7 @@
       <c r="D47" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E47" s="16" t="inlineStr"/>
+      <c r="E47" s="17" t="inlineStr"/>
       <c r="F47" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -60521,7 +60950,7 @@
       <c r="D48" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="16" t="inlineStr"/>
+      <c r="E48" s="17" t="inlineStr"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -60647,7 +61076,7 @@
       <c r="D52" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="16" t="inlineStr"/>
+      <c r="E52" s="17" t="inlineStr"/>
       <c r="F52" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -60673,7 +61102,7 @@
       <c r="D53" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E53" s="16" t="inlineStr"/>
+      <c r="E53" s="17" t="inlineStr"/>
       <c r="F53" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -60699,7 +61128,7 @@
       <c r="D54" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E54" s="16" t="inlineStr"/>
+      <c r="E54" s="17" t="inlineStr"/>
       <c r="F54" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -60757,7 +61186,7 @@
       <c r="D56" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="16" t="inlineStr"/>
+      <c r="E56" s="17" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -60815,7 +61244,7 @@
       <c r="D58" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E58" s="16" t="inlineStr"/>
+      <c r="E58" s="17" t="inlineStr"/>
       <c r="F58" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -61052,7 +61481,7 @@
       <c r="D68" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E68" s="16" t="inlineStr"/>
+      <c r="E68" s="17" t="inlineStr"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -61462,10 +61891,12 @@
       <c r="D81" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="E81" s="16" t="inlineStr"/>
+      <c r="E81" s="13" t="n">
+        <v>1462675.48</v>
+      </c>
       <c r="F81" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G81" s="12" t="n">
@@ -61568,7 +61999,7 @@
       <c r="D87" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E87" s="16" t="inlineStr"/>
+      <c r="E87" s="17" t="inlineStr"/>
       <c r="F87" s="14" t="inlineStr"/>
       <c r="G87" s="14" t="inlineStr"/>
     </row>
@@ -61647,7 +62078,7 @@
       <c r="D90" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="E90" s="16" t="inlineStr"/>
+      <c r="E90" s="17" t="inlineStr"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -61676,10 +62107,12 @@
       <c r="D91" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="E91" s="16" t="inlineStr"/>
+      <c r="E91" s="13" t="n">
+        <v>9160.919039999999</v>
+      </c>
       <c r="F91" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G91" s="14" t="inlineStr">
@@ -61701,7 +62134,7 @@
       <c r="D92" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E92" s="16" t="inlineStr"/>
+      <c r="E92" s="17" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr"/>
       <c r="G92" s="14" t="inlineStr"/>
     </row>
@@ -61753,10 +62186,12 @@
       <c r="D94" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="E94" s="16" t="inlineStr"/>
+      <c r="E94" s="13" t="n">
+        <v>20211.75389</v>
+      </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
@@ -61782,10 +62217,12 @@
       <c r="D95" s="11" t="n">
         <v>71</v>
       </c>
-      <c r="E95" s="16" t="inlineStr"/>
+      <c r="E95" s="13" t="n">
+        <v>1462675.48</v>
+      </c>
       <c r="F95" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G95" s="14" t="inlineStr">
@@ -61842,7 +62279,7 @@
       <c r="D97" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="E97" s="16" t="inlineStr"/>
+      <c r="E97" s="17" t="inlineStr"/>
       <c r="F97" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -62228,17 +62665,17 @@
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>ONEW</t>
+          <t>MOVAA</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E112" s="13" t="n">
-        <v>0.01133</v>
+        <v>44.382</v>
       </c>
       <c r="F112" s="11" t="n">
         <v>0</v>
@@ -62249,11 +62686,7 @@
       <c r="H112" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I112" s="14" t="inlineStr">
-        <is>
-          <t>OneWater Marine Inc.</t>
-        </is>
-      </c>
+      <c r="I112" s="14" t="inlineStr"/>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="14" t="inlineStr">
@@ -62263,17 +62696,17 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>SES-WT</t>
+          <t>SEI</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E113" s="13" t="n">
-        <v>13.7037123375</v>
+        <v>2.47595712</v>
       </c>
       <c r="F113" s="11" t="n">
         <v>0</v>
@@ -62282,11 +62715,11 @@
         <v>0</v>
       </c>
       <c r="H113" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
-          <t>SES AI Corporation WT</t>
+          <t>Solaris Energy Infrastructure, I</t>
         </is>
       </c>
     </row>
@@ -62298,7 +62731,7 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>XRXDW</t>
+          <t>ONEW</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
@@ -62308,7 +62741,7 @@
         <v>0</v>
       </c>
       <c r="E114" s="13" t="n">
-        <v>39.75700174399999</v>
+        <v>0.01133</v>
       </c>
       <c r="F114" s="11" t="n">
         <v>0</v>
@@ -62321,7 +62754,7 @@
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>Xerox Holdings Corporation</t>
+          <t>OneWater Marine Inc.</t>
         </is>
       </c>
     </row>
@@ -62333,7 +62766,7 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>CHWY</t>
+          <t>SES-WT</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
@@ -62343,7 +62776,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="13" t="n">
-        <v>0.001821</v>
+        <v>13.7037123375</v>
       </c>
       <c r="F115" s="11" t="n">
         <v>0</v>
@@ -62356,7 +62789,7 @@
       </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
-          <t>Chewy, Inc.</t>
+          <t>SES AI Corporation WT</t>
         </is>
       </c>
     </row>
@@ -62492,7 +62925,7 @@
         <v>0</v>
       </c>
       <c r="H119" s="12" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="I119" s="14" t="inlineStr">
         <is>
@@ -62753,17 +63186,17 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>13.6</v>
+        <v>31.1</v>
       </c>
       <c r="E127" s="13" t="n">
-        <v>4416.86155416</v>
+        <v>9160.919039999999</v>
       </c>
       <c r="F127" s="11" t="n">
         <v>0</v>
@@ -62772,11 +63205,11 @@
         <v>1</v>
       </c>
       <c r="H127" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
-          <t>KT Corporation</t>
+          <t>Carvana Co.</t>
         </is>
       </c>
     </row>
@@ -62788,30 +63221,30 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="E128" s="13" t="n">
-        <v>4054.238496</v>
+        <v>4416.86155416</v>
       </c>
       <c r="F128" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G128" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H128" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>Interactive Brokers Group, Inc.</t>
+          <t>KT Corporation</t>
         </is>
       </c>
     </row>
@@ -62823,17 +63256,17 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D129" s="12" t="n">
-        <v>14.5</v>
+        <v>13.4</v>
       </c>
       <c r="E129" s="13" t="n">
-        <v>2725.21804835</v>
+        <v>4054.238496</v>
       </c>
       <c r="F129" s="11" t="n">
         <v>0</v>
@@ -62842,11 +63275,11 @@
         <v>0</v>
       </c>
       <c r="H129" s="12" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>Seabridge Gold Inc.</t>
+          <t>Interactive Brokers Group, Inc.</t>
         </is>
       </c>
     </row>
@@ -62858,17 +63291,17 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>CACC</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>13.8</v>
+        <v>14.5</v>
       </c>
       <c r="E130" s="13" t="n">
-        <v>6064.016960829999</v>
+        <v>2725.21804835</v>
       </c>
       <c r="F130" s="11" t="n">
         <v>0</v>
@@ -62877,11 +63310,11 @@
         <v>0</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>Credit Acceptance Corporation</t>
+          <t>Seabridge Gold Inc.</t>
         </is>
       </c>
     </row>
@@ -62994,30 +63427,30 @@
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>11.6</v>
+        <v>21.8</v>
       </c>
       <c r="E134" s="13" t="n">
-        <v>153567.46273608</v>
+        <v>1462675.48</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H134" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
     </row>
@@ -63029,17 +63462,17 @@
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
         <v>7</v>
       </c>
       <c r="D135" s="12" t="n">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="E135" s="13" t="n">
-        <v>60014.06322947</v>
+        <v>153567.46273608</v>
       </c>
       <c r="F135" s="11" t="n">
         <v>0</v>
@@ -63052,7 +63485,7 @@
       </c>
       <c r="I135" s="14" t="inlineStr">
         <is>
-          <t>Mastercard Incorporated</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
     </row>
@@ -63271,10 +63704,12 @@
         </is>
       </c>
       <c r="J7" s="12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="K7" s="15" t="inlineStr"/>
-      <c r="L7" s="15" t="inlineStr"/>
+      <c r="L7" s="16" t="n">
+        <v>37.5</v>
+      </c>
       <c r="M7" s="14" t="inlineStr">
         <is>
           <t>PAR Technology Corporation</t>
@@ -63606,7 +64041,7 @@
       <c r="G15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="16" t="inlineStr"/>
+      <c r="H15" s="17" t="inlineStr"/>
       <c r="I15" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -63655,7 +64090,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="15" t="inlineStr"/>
-      <c r="L16" s="17" t="n">
+      <c r="L16" s="16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M16" s="14" t="inlineStr">
@@ -64204,17 +64639,21 @@
       <c r="G29" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="16" t="inlineStr"/>
+      <c r="H29" s="13" t="n">
+        <v>3482.877</v>
+      </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K29" s="15" t="inlineStr"/>
-      <c r="L29" s="15" t="inlineStr"/>
+      <c r="L29" s="16" t="n">
+        <v>2.4</v>
+      </c>
       <c r="M29" s="14" t="inlineStr">
         <is>
           <t>Atlanta Braves Holdings, Inc.</t>
@@ -64386,7 +64825,9 @@
         <v>0</v>
       </c>
       <c r="K33" s="15" t="inlineStr"/>
-      <c r="L33" s="15" t="inlineStr"/>
+      <c r="L33" s="16" t="n">
+        <v>0.1</v>
+      </c>
       <c r="M33" s="14" t="inlineStr">
         <is>
           <t>Pitney Bowes Inc.</t>
@@ -64417,17 +64858,19 @@
       <c r="G34" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="16" t="inlineStr"/>
+      <c r="H34" s="13" t="n">
+        <v>9160.919039999999</v>
+      </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J34" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K34" s="15" t="inlineStr"/>
-      <c r="L34" s="17" t="n">
+      <c r="L34" s="16" t="n">
         <v>0</v>
       </c>
       <c r="M34" s="14" t="inlineStr">
@@ -64682,7 +65125,7 @@
         </is>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
@@ -64961,7 +65404,7 @@
       <c r="D53" s="12" t="n">
         <v>2.7</v>
       </c>
-      <c r="E53" s="16" t="inlineStr"/>
+      <c r="E53" s="17" t="inlineStr"/>
       <c r="F53" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -65055,7 +65498,7 @@
       <c r="D56" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="16" t="inlineStr"/>
+      <c r="E56" s="17" t="inlineStr"/>
       <c r="F56" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -65196,10 +65639,12 @@
       <c r="D63" s="12" t="n">
         <v>3.4</v>
       </c>
-      <c r="E63" s="16" t="inlineStr"/>
+      <c r="E63" s="13" t="n">
+        <v>2694.66935616</v>
+      </c>
       <c r="F63" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G63" s="12" t="n">
@@ -65331,7 +65776,7 @@
         </is>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="H67" s="14" t="inlineStr">
         <is>
@@ -65354,10 +65799,12 @@
       <c r="D68" s="12" t="n">
         <v>1.3</v>
       </c>
-      <c r="E68" s="16" t="inlineStr"/>
+      <c r="E68" s="13" t="n">
+        <v>13045.92289</v>
+      </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G68" s="12" t="n">
@@ -65640,7 +66087,7 @@
       <c r="D77" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E77" s="16" t="inlineStr"/>
+      <c r="E77" s="17" t="inlineStr"/>
       <c r="F77" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -65698,7 +66145,7 @@
       <c r="D79" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E79" s="16" t="inlineStr"/>
+      <c r="E79" s="17" t="inlineStr"/>
       <c r="F79" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -65800,7 +66247,7 @@
       <c r="D85" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E85" s="16" t="inlineStr"/>
+      <c r="E85" s="17" t="inlineStr"/>
       <c r="F85" s="14" t="inlineStr"/>
       <c r="G85" s="14" t="inlineStr"/>
     </row>
@@ -65883,10 +66330,12 @@
       <c r="D88" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="E88" s="16" t="inlineStr"/>
+      <c r="E88" s="13" t="n">
+        <v>11596.12</v>
+      </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -65943,10 +66392,12 @@
       <c r="D90" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="E90" s="16" t="inlineStr"/>
+      <c r="E90" s="13" t="n">
+        <v>9160.919039999999</v>
+      </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
@@ -65999,7 +66450,7 @@
       <c r="D92" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E92" s="16" t="inlineStr"/>
+      <c r="E92" s="17" t="inlineStr"/>
       <c r="F92" s="14" t="inlineStr"/>
       <c r="G92" s="14" t="inlineStr"/>
     </row>
@@ -66016,7 +66467,7 @@
       <c r="D93" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E93" s="16" t="inlineStr"/>
+      <c r="E93" s="17" t="inlineStr"/>
       <c r="F93" s="14" t="inlineStr"/>
       <c r="G93" s="14" t="inlineStr"/>
     </row>
@@ -66188,7 +66639,7 @@
       <c r="D99" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E99" s="16" t="inlineStr"/>
+      <c r="E99" s="17" t="inlineStr"/>
       <c r="F99" s="14" t="inlineStr"/>
       <c r="G99" s="14" t="inlineStr"/>
     </row>
@@ -66236,7 +66687,7 @@
       <c r="D101" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E101" s="16" t="inlineStr"/>
+      <c r="E101" s="17" t="inlineStr"/>
       <c r="F101" s="14" t="inlineStr"/>
       <c r="G101" s="14" t="inlineStr"/>
     </row>
@@ -66253,7 +66704,7 @@
       <c r="D102" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E102" s="16" t="inlineStr"/>
+      <c r="E102" s="17" t="inlineStr"/>
       <c r="F102" s="14" t="inlineStr"/>
       <c r="G102" s="14" t="inlineStr"/>
     </row>
@@ -66356,17 +66807,17 @@
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>NPWR</t>
+          <t>SEI</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E108" s="13" t="n">
-        <v>6.886699920000001</v>
+        <v>2.47595712</v>
       </c>
       <c r="F108" s="11" t="n">
         <v>0</v>
@@ -66375,11 +66826,11 @@
         <v>0</v>
       </c>
       <c r="H108" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>NET Power Inc.</t>
+          <t>Solaris Energy Infrastructure, I</t>
         </is>
       </c>
     </row>
@@ -66391,17 +66842,17 @@
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>FBLA</t>
+          <t>FACT</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D109" s="12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E109" s="13" t="n">
-        <v>2.33997561</v>
+        <v>48.34303848</v>
       </c>
       <c r="F109" s="11" t="n">
         <v>0</v>
@@ -66414,7 +66865,7 @@
       </c>
       <c r="I109" s="14" t="inlineStr">
         <is>
-          <t>FB Bancorp, Inc.</t>
+          <t>FACT II Acquisition Corp</t>
         </is>
       </c>
     </row>
@@ -66426,20 +66877,20 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>SRG</t>
+          <t>MOVAA</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E110" s="13" t="n">
-        <v>0.000266</v>
+        <v>44.382</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" s="11" t="n">
         <v>0</v>
@@ -66447,11 +66898,7 @@
       <c r="H110" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I110" s="14" t="inlineStr">
-        <is>
-          <t>Seritage Growth Properties</t>
-        </is>
-      </c>
+      <c r="I110" s="14" t="inlineStr"/>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="14" t="inlineStr">
@@ -66461,17 +66908,17 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>CULP</t>
+          <t>NPWR</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>3.5</v>
+        <v>0.3</v>
       </c>
       <c r="E111" s="13" t="n">
-        <v>40.5209088</v>
+        <v>6.886699920000001</v>
       </c>
       <c r="F111" s="11" t="n">
         <v>0</v>
@@ -66480,11 +66927,11 @@
         <v>0</v>
       </c>
       <c r="H111" s="12" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
-          <t>Culp, Inc.</t>
+          <t>NET Power Inc.</t>
         </is>
       </c>
     </row>
@@ -66690,7 +67137,7 @@
         <v>1</v>
       </c>
       <c r="H117" s="12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="I117" s="14" t="inlineStr">
         <is>
@@ -66881,30 +67328,30 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>CLBT</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>14.6</v>
+        <v>29.8</v>
       </c>
       <c r="E123" s="13" t="n">
-        <v>3200.31285211</v>
+        <v>9160.919039999999</v>
       </c>
       <c r="F123" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G123" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H123" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
-          <t>Cellebrite DI Ltd.</t>
+          <t>Carvana Co.</t>
         </is>
       </c>
     </row>
@@ -66916,30 +67363,30 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>NATL</t>
+          <t>CLBT</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>18</v>
+        <v>14.6</v>
       </c>
       <c r="E124" s="13" t="n">
-        <v>3219.01341571</v>
+        <v>3200.31285211</v>
       </c>
       <c r="F124" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G124" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H124" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>NCR Atleos Corporation</t>
+          <t>Cellebrite DI Ltd.</t>
         </is>
       </c>
     </row>
@@ -66951,17 +67398,17 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>HGTY</t>
+          <t>NATL</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>17.2</v>
+        <v>18</v>
       </c>
       <c r="E125" s="13" t="n">
-        <v>3761.479442289999</v>
+        <v>3219.01341571</v>
       </c>
       <c r="F125" s="11" t="n">
         <v>0</v>
@@ -66974,7 +67421,7 @@
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
-          <t>Hagerty, Inc.</t>
+          <t>NCR Atleos Corporation</t>
         </is>
       </c>
     </row>
@@ -66986,17 +67433,17 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>TDGMW</t>
+          <t>HGTY</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>12.5</v>
+        <v>17.2</v>
       </c>
       <c r="E126" s="13" t="n">
-        <v>3033.569772</v>
+        <v>3761.479442289999</v>
       </c>
       <c r="F126" s="11" t="n">
         <v>0</v>
@@ -67005,11 +67452,11 @@
         <v>0</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>Tidewater Inc.</t>
+          <t>Hagerty, Inc.</t>
         </is>
       </c>
     </row>
@@ -67056,17 +67503,17 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>10.4</v>
+        <v>43.3</v>
       </c>
       <c r="E128" s="13" t="n">
-        <v>2628929.97506404</v>
+        <v>11596.12</v>
       </c>
       <c r="F128" s="11" t="n">
         <v>0</v>
@@ -67079,7 +67526,7 @@
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Wayfair Inc.</t>
         </is>
       </c>
     </row>
@@ -67091,17 +67538,17 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D129" s="12" t="n">
-        <v>20.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" s="13" t="n">
-        <v>19805.38760403</v>
+        <v>2628929.97506404</v>
       </c>
       <c r="F129" s="11" t="n">
         <v>0</v>
@@ -67114,7 +67561,7 @@
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>Talen Energy Corporation</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
     </row>
@@ -67126,17 +67573,17 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>TLN</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>11.6</v>
+        <v>20.1</v>
       </c>
       <c r="E130" s="13" t="n">
-        <v>4459051.48</v>
+        <v>19805.38760403</v>
       </c>
       <c r="F130" s="11" t="n">
         <v>0</v>
@@ -67149,7 +67596,7 @@
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Talen Energy Corporation</t>
         </is>
       </c>
     </row>
@@ -67161,30 +67608,30 @@
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D131" s="12" t="n">
-        <v>6.8</v>
+        <v>11.6</v>
       </c>
       <c r="E131" s="13" t="n">
-        <v>2818348.1266976</v>
+        <v>4459051.48</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G131" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H131" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I131" s="14" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
     </row>
@@ -67406,7 +67853,9 @@
         <v>0</v>
       </c>
       <c r="K7" s="15" t="inlineStr"/>
-      <c r="L7" s="15" t="inlineStr"/>
+      <c r="L7" s="16" t="n">
+        <v>1.2</v>
+      </c>
       <c r="M7" s="14" t="inlineStr">
         <is>
           <t>Bausch + Lomb Corporation</t>
@@ -67480,10 +67929,12 @@
       <c r="G9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="16" t="inlineStr"/>
+      <c r="H9" s="13" t="n">
+        <v>27470</v>
+      </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J9" s="12" t="n">
@@ -68006,7 +68457,9 @@
         <v>0</v>
       </c>
       <c r="K21" s="15" t="inlineStr"/>
-      <c r="L21" s="15" t="inlineStr"/>
+      <c r="L21" s="16" t="n">
+        <v>6</v>
+      </c>
       <c r="M21" s="14" t="inlineStr">
         <is>
           <t>Global Partners LP</t>
@@ -68135,7 +68588,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="15" t="inlineStr"/>
-      <c r="L24" s="17" t="n">
+      <c r="L24" s="16" t="n">
         <v>6.2</v>
       </c>
       <c r="M24" s="14" t="inlineStr">
@@ -68180,7 +68633,9 @@
         <v>0</v>
       </c>
       <c r="K25" s="15" t="inlineStr"/>
-      <c r="L25" s="15" t="inlineStr"/>
+      <c r="L25" s="16" t="n">
+        <v>1.3</v>
+      </c>
       <c r="M25" s="14" t="inlineStr">
         <is>
           <t>Grupo Aeromexico, S.A.B. de C.V</t>
@@ -68438,7 +68893,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="15" t="inlineStr"/>
-      <c r="L31" s="17" t="n">
+      <c r="L31" s="16" t="n">
         <v>0.1</v>
       </c>
       <c r="M31" s="14" t="inlineStr">
@@ -68480,7 +68935,7 @@
         </is>
       </c>
       <c r="J32" s="12" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="K32" s="15" t="inlineStr"/>
       <c r="L32" s="15" t="inlineStr"/>
@@ -68569,7 +69024,9 @@
         <v>6.7</v>
       </c>
       <c r="K34" s="15" t="inlineStr"/>
-      <c r="L34" s="15" t="inlineStr"/>
+      <c r="L34" s="16" t="n">
+        <v>37.2</v>
+      </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
           <t>MGM Resorts International</t>
@@ -68845,7 +69302,7 @@
       <c r="D45" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="16" t="inlineStr"/>
+      <c r="E45" s="17" t="inlineStr"/>
       <c r="F45" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -69227,7 +69684,7 @@
       <c r="D57" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E57" s="16" t="inlineStr"/>
+      <c r="E57" s="17" t="inlineStr"/>
       <c r="F57" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -69752,10 +70209,12 @@
       <c r="D76" s="12" t="n">
         <v>14.2</v>
       </c>
-      <c r="E76" s="16" t="inlineStr"/>
+      <c r="E76" s="13" t="n">
+        <v>8468.4256</v>
+      </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G76" s="12" t="n">
@@ -70264,7 +70723,7 @@
       <c r="D95" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E95" s="16" t="inlineStr"/>
+      <c r="E95" s="17" t="inlineStr"/>
       <c r="F95" s="14" t="inlineStr"/>
       <c r="G95" s="14" t="inlineStr"/>
     </row>
@@ -70285,7 +70744,7 @@
       <c r="D96" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E96" s="16" t="inlineStr"/>
+      <c r="E96" s="17" t="inlineStr"/>
       <c r="F96" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -70306,7 +70765,7 @@
       <c r="D97" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E97" s="16" t="inlineStr"/>
+      <c r="E97" s="17" t="inlineStr"/>
       <c r="F97" s="14" t="inlineStr"/>
       <c r="G97" s="14" t="inlineStr"/>
     </row>
@@ -70327,7 +70786,7 @@
       <c r="D98" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E98" s="16" t="inlineStr"/>
+      <c r="E98" s="17" t="inlineStr"/>
       <c r="F98" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -70352,7 +70811,7 @@
       <c r="D99" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E99" s="16" t="inlineStr"/>
+      <c r="E99" s="17" t="inlineStr"/>
       <c r="F99" s="14" t="inlineStr"/>
       <c r="G99" s="14" t="inlineStr"/>
     </row>
@@ -70369,7 +70828,7 @@
       <c r="D100" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E100" s="16" t="inlineStr"/>
+      <c r="E100" s="17" t="inlineStr"/>
       <c r="F100" s="14" t="inlineStr"/>
       <c r="G100" s="14" t="inlineStr"/>
     </row>
@@ -70534,17 +70993,17 @@
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>COCH</t>
+          <t>MCGAW</t>
         </is>
       </c>
       <c r="C108" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D108" s="12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E108" s="13" t="n">
-        <v>48.74262374000001</v>
+        <v>1.6225</v>
       </c>
       <c r="F108" s="11" t="n">
         <v>0</v>
@@ -70557,7 +71016,7 @@
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>Envoy Medical, Inc.</t>
+          <t>Yorkville Acquisition Corp.</t>
         </is>
       </c>
     </row>
@@ -70569,7 +71028,7 @@
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>MLECW</t>
+          <t>ONCHW</t>
         </is>
       </c>
       <c r="C109" s="11" t="n">
@@ -70579,7 +71038,7 @@
         <v>0</v>
       </c>
       <c r="E109" s="13" t="n">
-        <v>0.5919852708</v>
+        <v>1.8</v>
       </c>
       <c r="F109" s="11" t="n">
         <v>0</v>
@@ -70592,7 +71051,7 @@
       </c>
       <c r="I109" s="14" t="inlineStr">
         <is>
-          <t>Moolec Science SA</t>
+          <t>1RT Acquisition Corp.</t>
         </is>
       </c>
     </row>
@@ -70604,7 +71063,7 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>CXAI</t>
+          <t>COCH</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
@@ -70614,7 +71073,7 @@
         <v>0</v>
       </c>
       <c r="E110" s="13" t="n">
-        <v>17.8797745627</v>
+        <v>48.74262374000001</v>
       </c>
       <c r="F110" s="11" t="n">
         <v>0</v>
@@ -70627,7 +71086,7 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>CXApp Inc.</t>
+          <t>Envoy Medical, Inc.</t>
         </is>
       </c>
     </row>
@@ -70639,7 +71098,7 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>BGLWW</t>
+          <t>MLECW</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
@@ -70649,7 +71108,7 @@
         <v>0</v>
       </c>
       <c r="E111" s="13" t="n">
-        <v>1.07540631</v>
+        <v>0.5919852708</v>
       </c>
       <c r="F111" s="11" t="n">
         <v>0</v>
@@ -70662,7 +71121,7 @@
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
-          <t>Blue Gold Limited</t>
+          <t>Moolec Science SA</t>
         </is>
       </c>
     </row>
@@ -71397,7 +71856,7 @@
     <col width="9.5" customWidth="1" min="6" max="6"/>
     <col width="34.5" customWidth="1" min="7" max="7"/>
     <col width="40.5" customWidth="1" min="8" max="8"/>
-    <col width="33.5" customWidth="1" min="9" max="9"/>
+    <col width="34.5" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="8.5" customWidth="1" min="11" max="11"/>
     <col width="8.5" customWidth="1" min="12" max="12"/>
@@ -71658,10 +72117,12 @@
       <c r="G9" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="16" t="inlineStr"/>
+      <c r="H9" s="13" t="n">
+        <v>1462675.48</v>
+      </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J9" s="12" t="n">
@@ -71797,7 +72258,9 @@
         <v>0</v>
       </c>
       <c r="K12" s="15" t="inlineStr"/>
-      <c r="L12" s="15" t="inlineStr"/>
+      <c r="L12" s="16" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
           <t>CME Group Inc.</t>
@@ -71828,10 +72291,12 @@
       <c r="G13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="16" t="inlineStr"/>
+      <c r="H13" s="13" t="n">
+        <v>14821.13635</v>
+      </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J13" s="12" t="n">
@@ -72182,7 +72647,9 @@
         <v>0</v>
       </c>
       <c r="K21" s="15" t="inlineStr"/>
-      <c r="L21" s="15" t="inlineStr"/>
+      <c r="L21" s="16" t="n">
+        <v>6</v>
+      </c>
       <c r="M21" s="14" t="inlineStr">
         <is>
           <t>Global Partners LP</t>
@@ -72471,7 +72938,7 @@
       <c r="G28" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="16" t="inlineStr"/>
+      <c r="H28" s="17" t="inlineStr"/>
       <c r="I28" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -72649,7 +73116,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="15" t="inlineStr"/>
-      <c r="L32" s="17" t="n">
+      <c r="L32" s="16" t="n">
         <v>0.1</v>
       </c>
       <c r="M32" s="14" t="inlineStr">
@@ -72694,7 +73161,9 @@
         <v>0</v>
       </c>
       <c r="K33" s="15" t="inlineStr"/>
-      <c r="L33" s="15" t="inlineStr"/>
+      <c r="L33" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="M33" s="14" t="inlineStr">
         <is>
           <t>Interactive Brokers Group, Inc.</t>
@@ -72737,7 +73206,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="15" t="inlineStr"/>
-      <c r="L34" s="17" t="n">
+      <c r="L34" s="16" t="n">
         <v>4.4</v>
       </c>
       <c r="M34" s="14" t="inlineStr">
@@ -72938,7 +73407,7 @@
       <c r="D45" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="16" t="inlineStr"/>
+      <c r="E45" s="17" t="inlineStr"/>
       <c r="F45" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -73165,7 +73634,7 @@
         </is>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
@@ -73188,7 +73657,7 @@
       <c r="D53" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E53" s="16" t="inlineStr"/>
+      <c r="E53" s="17" t="inlineStr"/>
       <c r="F53" s="14" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -73324,7 +73793,7 @@
       <c r="D60" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="16" t="inlineStr"/>
+      <c r="E60" s="17" t="inlineStr"/>
       <c r="F60" s="14" t="inlineStr"/>
       <c r="G60" s="14" t="inlineStr"/>
     </row>
@@ -73403,7 +73872,7 @@
       <c r="D63" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E63" s="16" t="inlineStr"/>
+      <c r="E63" s="17" t="inlineStr"/>
       <c r="F63" s="14" t="inlineStr"/>
       <c r="G63" s="14" t="inlineStr"/>
     </row>
@@ -73451,7 +73920,7 @@
       <c r="D65" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E65" s="16" t="inlineStr"/>
+      <c r="E65" s="17" t="inlineStr"/>
       <c r="F65" s="14" t="inlineStr"/>
       <c r="G65" s="14" t="inlineStr"/>
     </row>
@@ -73592,7 +74061,7 @@
       <c r="D70" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E70" s="16" t="inlineStr"/>
+      <c r="E70" s="17" t="inlineStr"/>
       <c r="F70" s="14" t="inlineStr"/>
       <c r="G70" s="14" t="inlineStr"/>
     </row>
@@ -73640,7 +74109,7 @@
       <c r="D72" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E72" s="16" t="inlineStr"/>
+      <c r="E72" s="17" t="inlineStr"/>
       <c r="F72" s="14" t="inlineStr"/>
       <c r="G72" s="14" t="inlineStr"/>
     </row>
@@ -73657,7 +74126,7 @@
       <c r="D73" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E73" s="16" t="inlineStr"/>
+      <c r="E73" s="17" t="inlineStr"/>
       <c r="F73" s="14" t="inlineStr"/>
       <c r="G73" s="14" t="inlineStr"/>
     </row>
@@ -73861,7 +74330,7 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>CHWY</t>
+          <t>SVACW</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
@@ -73871,7 +74340,7 @@
         <v>0</v>
       </c>
       <c r="E82" s="13" t="n">
-        <v>0.001821</v>
+        <v>12.500000625</v>
       </c>
       <c r="F82" s="11" t="n">
         <v>0</v>
@@ -73884,7 +74353,7 @@
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>Chewy, Inc.</t>
+          <t xml:space="preserve">Spring Valley Acquisition Corp. </t>
         </is>
       </c>
     </row>
@@ -73896,17 +74365,17 @@
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>XRXDW</t>
+          <t>CHWY</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E83" s="13" t="n">
-        <v>39.75700174399999</v>
+        <v>0.001821</v>
       </c>
       <c r="F83" s="11" t="n">
         <v>0</v>
@@ -73919,7 +74388,7 @@
       </c>
       <c r="I83" s="14" t="inlineStr">
         <is>
-          <t>Xerox Holdings Corporation</t>
+          <t>Chewy, Inc.</t>
         </is>
       </c>
     </row>
@@ -74036,17 +74505,17 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>CNDT</t>
+          <t>CEPV</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D87" s="12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>217.1355396</v>
+        <v>56.65000000000001</v>
       </c>
       <c r="F87" s="11" t="n">
         <v>0</v>
@@ -74059,7 +74528,7 @@
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
-          <t>Conduent Incorporated</t>
+          <t>Cantor Equity Partners V, Inc.</t>
         </is>
       </c>
     </row>
@@ -74071,7 +74540,7 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>OSG</t>
+          <t>CNDT</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
@@ -74081,7 +74550,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="13" t="n">
-        <v>259.27828992</v>
+        <v>217.1355396</v>
       </c>
       <c r="F88" s="11" t="n">
         <v>0</v>
@@ -74090,11 +74559,11 @@
         <v>0</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>Octave Specialty Group, Inc.</t>
+          <t>Conduent Incorporated</t>
         </is>
       </c>
     </row>

--- a/style_analysis.xlsx
+++ b/style_analysis.xlsx
@@ -35,8 +35,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="[&gt;=1000000]&quot;$&quot;#,##0.0,,&quot;T&quot;;[&gt;=1000]&quot;$&quot;#,##0.0,&quot;B&quot;;&quot;$&quot;#,##0&quot; M&quot;"/>
+    <numFmt numFmtId="166" formatCode="[&gt;=1000]&quot;$&quot;#,##0.0,&quot;B&quot;;&quot;$&quot;#,##0.0&quot; M&quot;"/>
   </numFmts>
   <fonts count="7">
     <font>

--- a/style_analysis.xlsx
+++ b/style_analysis.xlsx
@@ -828,14 +828,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O132"/>
+  <dimension ref="A1:O130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="33.5" customWidth="1" min="2" max="2"/>
     <col width="9.5" customWidth="1" min="3" max="3"/>
     <col width="9.5" customWidth="1" min="4" max="4"/>
-    <col width="23.5" customWidth="1" min="5" max="5"/>
+    <col width="20.5" customWidth="1" min="5" max="5"/>
     <col width="9.5" customWidth="1" min="6" max="6"/>
     <col width="32.5" customWidth="1" min="7" max="7"/>
     <col width="40.5" customWidth="1" min="8" max="8"/>
@@ -2077,7 +2077,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>6203.27562275</v>
+        <v>7104.0871356</v>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>0</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>4197.27353648</v>
+        <v>4418.65260064</v>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>53.05625826</v>
+        <v>133.42717</v>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>0.4</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>11838.6424</v>
+        <v>11959.84894</v>
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>7.7</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>54313.77967512</v>
+        <v>58257.37343047999</v>
       </c>
       <c r="F65" s="14" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>2.8</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>40786.32640656</v>
+        <v>41053.37577964</v>
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>6.5</v>
       </c>
       <c r="E72" s="13" t="n">
-        <v>1278839.13649349</v>
+        <v>1280720.53930249</v>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>21.8</v>
       </c>
       <c r="E74" s="13" t="n">
-        <v>1462675.48</v>
+        <v>1479992.08</v>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
@@ -4374,17 +4374,17 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>GLXY</t>
+          <t>SVACW</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E110" s="13" t="n">
-        <v>0.00342</v>
+        <v>12.500000625</v>
       </c>
       <c r="F110" s="11" t="n">
         <v>0</v>
@@ -4397,29 +4397,29 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>Galaxy Digital</t>
+          <t xml:space="preserve">Spring Valley Acquisition Corp. </t>
         </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="14" t="inlineStr">
         <is>
-          <t>nano</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>MWH</t>
+          <t>SRL</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="E111" s="13" t="n">
-        <v>0.003421</v>
+        <v>90.786287375</v>
       </c>
       <c r="F111" s="11" t="n">
         <v>0</v>
@@ -4432,29 +4432,29 @@
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
-          <t>SOLV Energy, Inc.</t>
+          <t>Scully Royalty Ltd.</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>nano</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>SVACW</t>
+          <t>THRY</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="E112" s="13" t="n">
-        <v>12.500000625</v>
+        <v>155.224251</v>
       </c>
       <c r="F112" s="11" t="n">
         <v>0</v>
@@ -4463,11 +4463,11 @@
         <v>0</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spring Valley Acquisition Corp. </t>
+          <t>Thryv Holdings, Inc.</t>
         </is>
       </c>
     </row>
@@ -4479,17 +4479,17 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>SRL</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>15.2</v>
+        <v>0.2</v>
       </c>
       <c r="E113" s="13" t="n">
-        <v>90.786287375</v>
+        <v>295.7383494</v>
       </c>
       <c r="F113" s="11" t="n">
         <v>0</v>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
-          <t>Scully Royalty Ltd.</t>
+          <t>Citizens, Inc.</t>
         </is>
       </c>
     </row>
@@ -4514,17 +4514,17 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>THRY</t>
+          <t>BRCB</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="E114" s="13" t="n">
-        <v>155.224251</v>
+        <v>135.58094828</v>
       </c>
       <c r="F114" s="11" t="n">
         <v>0</v>
@@ -4533,11 +4533,11 @@
         <v>0</v>
       </c>
       <c r="H114" s="12" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>Thryv Holdings, Inc.</t>
+          <t>Black Rock Coffee Bar, Inc.</t>
         </is>
       </c>
     </row>
@@ -4549,17 +4549,17 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>OWL</t>
+          <t>CEPV</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D115" s="12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E115" s="13" t="n">
-        <v>65.51875</v>
+        <v>56.65000000000001</v>
       </c>
       <c r="F115" s="11" t="n">
         <v>0</v>
@@ -4572,64 +4572,64 @@
       </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
-          <t>Blue Owl Capital Inc.</t>
+          <t>Cantor Equity Partners V, Inc.</t>
         </is>
       </c>
     </row>
     <row r="116" ht="18" customHeight="1">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>small</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>OPTU</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>0.2</v>
+        <v>11.1</v>
       </c>
       <c r="E116" s="13" t="n">
-        <v>295.7383494</v>
+        <v>547.94303805</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G116" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H116" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>Citizens, Inc.</t>
+          <t>Optimum Communications, Inc.</t>
         </is>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="14" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>small</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>BRCB</t>
+          <t>BHC</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D117" s="12" t="n">
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="E117" s="13" t="n">
-        <v>135.58094828</v>
+        <v>1781.47882188</v>
       </c>
       <c r="F117" s="11" t="n">
         <v>0</v>
@@ -4638,11 +4638,11 @@
         <v>0</v>
       </c>
       <c r="H117" s="12" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="I117" s="14" t="inlineStr">
         <is>
-          <t>Black Rock Coffee Bar, Inc.</t>
+          <t>Bausch Health Companies Inc.</t>
         </is>
       </c>
     </row>
@@ -4654,30 +4654,30 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>OPTU</t>
+          <t>THM</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>11.1</v>
+        <v>7.4</v>
       </c>
       <c r="E118" s="13" t="n">
-        <v>547.94303805</v>
+        <v>432.90702351</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>0</v>
+        <v>38.1</v>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>Optimum Communications, Inc.</t>
+          <t>International Tower Hill Mines L</t>
         </is>
       </c>
     </row>
@@ -4689,17 +4689,17 @@
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>BHC</t>
+          <t>GLP</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D119" s="12" t="n">
-        <v>12.7</v>
+        <v>2.4</v>
       </c>
       <c r="E119" s="13" t="n">
-        <v>1781.47882188</v>
+        <v>1447.53107254</v>
       </c>
       <c r="F119" s="11" t="n">
         <v>0</v>
@@ -4708,11 +4708,11 @@
         <v>0</v>
       </c>
       <c r="H119" s="12" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="I119" s="14" t="inlineStr">
         <is>
-          <t>Bausch Health Companies Inc.</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
     </row>
@@ -4724,17 +4724,17 @@
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>THM</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>7.4</v>
+        <v>0.1</v>
       </c>
       <c r="E120" s="13" t="n">
-        <v>432.90702351</v>
+        <v>1573.512885</v>
       </c>
       <c r="F120" s="11" t="n">
         <v>0</v>
@@ -4743,33 +4743,33 @@
         <v>0</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>38.1</v>
+        <v>0</v>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>International Tower Hill Mines L</t>
+          <t>PureCycle Technologies, Inc.</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="A121" s="14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>GLP</t>
+          <t>NN</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D121" s="12" t="n">
-        <v>2.4</v>
+        <v>39.4</v>
       </c>
       <c r="E121" s="13" t="n">
-        <v>1447.53107254</v>
+        <v>2480.42355102</v>
       </c>
       <c r="F121" s="11" t="n">
         <v>0</v>
@@ -4782,29 +4782,29 @@
       </c>
       <c r="I121" s="14" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>NextNav Inc.</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>PPTA</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>0.1</v>
+        <v>29.2</v>
       </c>
       <c r="E122" s="13" t="n">
-        <v>1573.512885</v>
+        <v>3042.29831296</v>
       </c>
       <c r="F122" s="11" t="n">
         <v>0</v>
@@ -4813,11 +4813,11 @@
         <v>0</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>PureCycle Technologies, Inc.</t>
+          <t>Perpetua Resources Corp.</t>
         </is>
       </c>
     </row>
@@ -4829,17 +4829,17 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>NN</t>
+          <t>AAMI</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>39.4</v>
+        <v>13.5</v>
       </c>
       <c r="E123" s="13" t="n">
-        <v>2480.42355102</v>
+        <v>2677.5184482</v>
       </c>
       <c r="F123" s="11" t="n">
         <v>0</v>
@@ -4848,11 +4848,11 @@
         <v>0</v>
       </c>
       <c r="H123" s="12" t="n">
-        <v>0</v>
+        <v>21.6</v>
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
-          <t>NextNav Inc.</t>
+          <t>Acadian Asset Management Inc.</t>
         </is>
       </c>
     </row>
@@ -4864,17 +4864,17 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>PPTA</t>
+          <t>NG</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>29.2</v>
+        <v>7.9</v>
       </c>
       <c r="E124" s="13" t="n">
-        <v>3042.29831296</v>
+        <v>3422.4887892</v>
       </c>
       <c r="F124" s="11" t="n">
         <v>0</v>
@@ -4883,11 +4883,11 @@
         <v>0</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>31.2</v>
+        <v>9.6</v>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>Perpetua Resources Corp.</t>
+          <t>NovaGold Resources Inc.</t>
         </is>
       </c>
     </row>
@@ -4899,17 +4899,17 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>AAMI</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>13.5</v>
+        <v>1.8</v>
       </c>
       <c r="E125" s="13" t="n">
-        <v>2677.5184482</v>
+        <v>2116.46378184</v>
       </c>
       <c r="F125" s="11" t="n">
         <v>0</v>
@@ -4918,33 +4918,33 @@
         <v>0</v>
       </c>
       <c r="H125" s="12" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
-          <t>Acadian Asset Management Inc.</t>
+          <t>Huntsman Corporation</t>
         </is>
       </c>
     </row>
     <row r="126" ht="18" customHeight="1">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>7.9</v>
+        <v>46.7</v>
       </c>
       <c r="E126" s="13" t="n">
-        <v>3422.4887892</v>
+        <v>251547.5764068</v>
       </c>
       <c r="F126" s="11" t="n">
         <v>0</v>
@@ -4953,33 +4953,33 @@
         <v>0</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>NovaGold Resources Inc.</t>
+          <t>Wells Fargo &amp; Company</t>
         </is>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>1.8</v>
+        <v>40.5</v>
       </c>
       <c r="E127" s="13" t="n">
-        <v>2116.46378184</v>
+        <v>398828.3945862001</v>
       </c>
       <c r="F127" s="11" t="n">
         <v>0</v>
@@ -4992,7 +4992,7 @@
       </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
-          <t>Huntsman Corporation</t>
+          <t>Bank of America Corporation</t>
         </is>
       </c>
     </row>
@@ -5004,17 +5004,17 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>PCG-PX</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>46.7</v>
+        <v>28.2</v>
       </c>
       <c r="E128" s="13" t="n">
-        <v>251547.5764068</v>
+        <v>110602.29248386</v>
       </c>
       <c r="F128" s="11" t="n">
         <v>0</v>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Company</t>
+          <t>PG&amp;E Corp</t>
         </is>
       </c>
     </row>
@@ -5039,17 +5039,17 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>MDGL</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D129" s="12" t="n">
-        <v>40.5</v>
+        <v>23.4</v>
       </c>
       <c r="E129" s="13" t="n">
-        <v>398828.3945862001</v>
+        <v>11660.39953925</v>
       </c>
       <c r="F129" s="11" t="n">
         <v>0</v>
@@ -5058,11 +5058,11 @@
         <v>0</v>
       </c>
       <c r="H129" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>Bank of America Corporation</t>
+          <t>Madrigal Pharmaceuticals, Inc.</t>
         </is>
       </c>
     </row>
@@ -5074,17 +5074,17 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>PCG-PX</t>
+          <t>NTRA</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>28.2</v>
+        <v>18.1</v>
       </c>
       <c r="E130" s="13" t="n">
-        <v>110602.29248386</v>
+        <v>33141.47154862</v>
       </c>
       <c r="F130" s="11" t="n">
         <v>0</v>
@@ -5096,76 +5096,6 @@
         <v>0</v>
       </c>
       <c r="I130" s="14" t="inlineStr">
-        <is>
-          <t>PG&amp;E Corp</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="14" t="inlineStr">
-        <is>
-          <t>large</t>
-        </is>
-      </c>
-      <c r="B131" s="10" t="inlineStr">
-        <is>
-          <t>MDGL</t>
-        </is>
-      </c>
-      <c r="C131" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D131" s="12" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E131" s="13" t="n">
-        <v>11660.39953925</v>
-      </c>
-      <c r="F131" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G131" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I131" s="14" t="inlineStr">
-        <is>
-          <t>Madrigal Pharmaceuticals, Inc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="14" t="inlineStr">
-        <is>
-          <t>large</t>
-        </is>
-      </c>
-      <c r="B132" s="10" t="inlineStr">
-        <is>
-          <t>NTRA</t>
-        </is>
-      </c>
-      <c r="C132" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D132" s="12" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="E132" s="13" t="n">
-        <v>33141.47154862</v>
-      </c>
-      <c r="F132" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G132" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" s="14" t="inlineStr">
         <is>
           <t>Natera, Inc.</t>
         </is>
@@ -5591,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>60014.06322947</v>
+        <v>437382.47</v>
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
@@ -5599,10 +5529,10 @@
         </is>
       </c>
       <c r="J11" s="18" t="n">
-        <v>3.5</v>
+        <v>22.4</v>
       </c>
       <c r="K11" s="20" t="n">
-        <v>8.93</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>0</v>
@@ -5834,7 +5764,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>2113.06731792</v>
+        <v>2112.96</v>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
@@ -6165,7 +6095,7 @@
         <v>2</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>1278839.13649349</v>
+        <v>1280720.53930249</v>
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
@@ -6173,10 +6103,10 @@
         </is>
       </c>
       <c r="J23" s="18" t="n">
-        <v>69.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K23" s="20" t="n">
-        <v>12.7</v>
+        <v>12.72</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>0</v>
@@ -6410,7 +6340,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>155881.6932</v>
+        <v>156121.5282</v>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
@@ -6932,7 +6862,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>97986.24000000001</v>
+        <v>98015.51232000001</v>
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
@@ -6964,7 +6894,7 @@
         <v>6.5</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>1278839.13649349</v>
+        <v>1280720.53930249</v>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
@@ -7621,7 +7551,7 @@
         <v>6.5</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>1278839.13649349</v>
+        <v>1280720.53930249</v>
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
@@ -7653,7 +7583,7 @@
         <v>21.8</v>
       </c>
       <c r="E68" s="13" t="n">
-        <v>1462675.48</v>
+        <v>1479992.08</v>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
@@ -8174,11 +8104,11 @@
         <v>41</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>5205.99404763</v>
+        <v>31551.65838</v>
       </c>
       <c r="F87" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G87" s="14" t="inlineStr">
@@ -8205,11 +8135,11 @@
         <v>41</v>
       </c>
       <c r="E88" s="13" t="n">
-        <v>5205.99404763</v>
+        <v>31551.65838</v>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -8298,7 +8228,7 @@
         <v>53</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>690679.87641</v>
+        <v>1205407.79598</v>
       </c>
       <c r="F91" s="14" t="inlineStr">
         <is>
@@ -8484,11 +8414,11 @@
         <v>41</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>5205.99404763</v>
+        <v>31551.65838</v>
       </c>
       <c r="F97" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G97" s="14" t="inlineStr">
@@ -8515,11 +8445,11 @@
         <v>41</v>
       </c>
       <c r="E98" s="13" t="n">
-        <v>5205.99404763</v>
+        <v>31551.65838</v>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -8592,7 +8522,7 @@
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>SEI</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
@@ -8602,7 +8532,7 @@
         <v>0.1</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>4.695e-05</v>
+        <v>2.48001824</v>
       </c>
       <c r="F103" s="11" t="n">
         <v>0</v>
@@ -8611,11 +8541,11 @@
         <v>0</v>
       </c>
       <c r="H103" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I103" s="14" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Solaris Energy Infrastructure, I</t>
         </is>
       </c>
     </row>
@@ -8627,17 +8557,17 @@
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>SEI</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="C104" s="11" t="n">
         <v>11</v>
       </c>
       <c r="D104" s="12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E104" s="13" t="n">
-        <v>2.47595712</v>
+        <v>0.56213788</v>
       </c>
       <c r="F104" s="11" t="n">
         <v>0</v>
@@ -8646,11 +8576,11 @@
         <v>0</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>Solaris Energy Infrastructure, I</t>
+          <t>Erie Indemnity Company</t>
         </is>
       </c>
     </row>
@@ -8662,17 +8592,17 @@
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>SPG</t>
+          <t>WMG</t>
         </is>
       </c>
       <c r="C105" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D105" s="12" t="n">
         <v>0.1</v>
       </c>
       <c r="E105" s="13" t="n">
-        <v>1.69064</v>
+        <v>0.03011373000000001</v>
       </c>
       <c r="F105" s="11" t="n">
         <v>0</v>
@@ -8685,7 +8615,7 @@
       </c>
       <c r="I105" s="14" t="inlineStr">
         <is>
-          <t>Simon Property Group, Inc.</t>
+          <t>Warner Music Group Corp.</t>
         </is>
       </c>
     </row>
@@ -8697,17 +8627,17 @@
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>HUBG</t>
         </is>
       </c>
       <c r="C106" s="11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D106" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E106" s="13" t="n">
-        <v>0.56213788</v>
+        <v>2.67523635</v>
       </c>
       <c r="F106" s="11" t="n">
         <v>0</v>
@@ -8720,7 +8650,7 @@
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>Erie Indemnity Company</t>
+          <t>Hub Group, Inc.</t>
         </is>
       </c>
     </row>
@@ -8732,17 +8662,17 @@
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>WMG</t>
+          <t>XRXDW</t>
         </is>
       </c>
       <c r="C107" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D107" s="12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E107" s="13" t="n">
-        <v>0.03011373000000001</v>
+        <v>39.75700174399999</v>
       </c>
       <c r="F107" s="11" t="n">
         <v>0</v>
@@ -8755,7 +8685,7 @@
       </c>
       <c r="I107" s="14" t="inlineStr">
         <is>
-          <t>Warner Music Group Corp.</t>
+          <t>Xerox Holdings Corporation</t>
         </is>
       </c>
     </row>
@@ -8872,17 +8802,17 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>HLI</t>
+          <t>LAKE</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E111" s="13" t="n">
-        <v>82.75389682000001</v>
+        <v>99.48117311999999</v>
       </c>
       <c r="F111" s="11" t="n">
         <v>0</v>
@@ -8895,7 +8825,7 @@
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
-          <t>Houlihan Lokey, Inc.</t>
+          <t>Lakeland Industries, Inc.</t>
         </is>
       </c>
     </row>
@@ -8907,17 +8837,17 @@
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>OWL</t>
+          <t>RXST</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
         <v>11</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E112" s="13" t="n">
-        <v>65.51875</v>
+        <v>195.80596057</v>
       </c>
       <c r="F112" s="11" t="n">
         <v>0</v>
@@ -8930,7 +8860,7 @@
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>Blue Owl Capital Inc.</t>
+          <t>RxSight, Inc.</t>
         </is>
       </c>
     </row>
@@ -9047,7 +8977,7 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>SF-PD</t>
+          <t>FMC</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
@@ -9057,7 +8987,7 @@
         <v>0.1</v>
       </c>
       <c r="E116" s="13" t="n">
-        <v>1124.136773595</v>
+        <v>1444.27322655</v>
       </c>
       <c r="F116" s="11" t="n">
         <v>0</v>
@@ -9070,7 +9000,7 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>Stifel Financial Corp.</t>
+          <t>FMC Corporation</t>
         </is>
       </c>
     </row>
@@ -9082,17 +9012,17 @@
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>FMC</t>
+          <t>AXS-PE</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D117" s="12" t="n">
         <v>0.1</v>
       </c>
       <c r="E117" s="13" t="n">
-        <v>1444.27322655</v>
+        <v>1441.2892638</v>
       </c>
       <c r="F117" s="11" t="n">
         <v>0</v>
@@ -9105,7 +9035,7 @@
       </c>
       <c r="I117" s="14" t="inlineStr">
         <is>
-          <t>FMC Corporation</t>
+          <t>AXIS Capital Holdings Limited</t>
         </is>
       </c>
     </row>
@@ -9117,17 +9047,17 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>SATS</t>
+          <t>JBLU</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>16.4</v>
+        <v>5.4</v>
       </c>
       <c r="E118" s="13" t="n">
-        <v>5205.99404763</v>
+        <v>2112.96</v>
       </c>
       <c r="F118" s="11" t="n">
         <v>0</v>
@@ -9136,11 +9066,11 @@
         <v>0</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>EchoStar Corporation</t>
+          <t>JetBlue Airways Corporation</t>
         </is>
       </c>
     </row>
@@ -9152,17 +9082,17 @@
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>JBLU</t>
+          <t>PTON</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D119" s="12" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="E119" s="13" t="n">
-        <v>2113.06731792</v>
+        <v>2500.18484046</v>
       </c>
       <c r="F119" s="11" t="n">
         <v>0</v>
@@ -9175,7 +9105,7 @@
       </c>
       <c r="I119" s="14" t="inlineStr">
         <is>
-          <t>JetBlue Airways Corporation</t>
+          <t>Peloton Interactive, Inc.</t>
         </is>
       </c>
     </row>
@@ -9187,17 +9117,17 @@
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>HEI-A</t>
+          <t>JHG</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E120" s="13" t="n">
-        <v>6661.37906228</v>
+        <v>7993.44254304</v>
       </c>
       <c r="F120" s="11" t="n">
         <v>0</v>
@@ -9206,11 +9136,11 @@
         <v>0</v>
       </c>
       <c r="H120" s="12" t="n">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>HEICO Corporation</t>
+          <t>Janus Henderson Group plc</t>
         </is>
       </c>
     </row>
@@ -9222,17 +9152,17 @@
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>PTON</t>
+          <t>GS-PD</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D121" s="12" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="E121" s="13" t="n">
-        <v>2429.47701593</v>
+        <v>5652.342186360001</v>
       </c>
       <c r="F121" s="11" t="n">
         <v>0</v>
@@ -9245,7 +9175,7 @@
       </c>
       <c r="I121" s="14" t="inlineStr">
         <is>
-          <t>Peloton Interactive, Inc.</t>
+          <t>The Goldman Sachs Group, Inc.</t>
         </is>
       </c>
     </row>
@@ -9257,17 +9187,17 @@
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>JHG</t>
+          <t>VIRT</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="E122" s="13" t="n">
-        <v>7993.44254304</v>
+        <v>5429.931361890001</v>
       </c>
       <c r="F122" s="11" t="n">
         <v>0</v>
@@ -9276,11 +9206,11 @@
         <v>0</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>20.7</v>
+        <v>0</v>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>Janus Henderson Group plc</t>
+          <t>Virtu Financial, Inc.</t>
         </is>
       </c>
     </row>
@@ -9432,17 +9362,17 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>SATS</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>7.4</v>
+        <v>16.4</v>
       </c>
       <c r="E127" s="13" t="n">
-        <v>55213.629135</v>
+        <v>31551.65838</v>
       </c>
       <c r="F127" s="11" t="n">
         <v>0</v>
@@ -9451,11 +9381,11 @@
         <v>0</v>
       </c>
       <c r="H127" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
-          <t>Vistra Corp.</t>
+          <t>EchoStar Corporation</t>
         </is>
       </c>
     </row>
@@ -10864,16 +10794,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>275.80412562</v>
+        <v>445.8279704399999</v>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>small</t>
         </is>
       </c>
       <c r="J32" s="21" t="inlineStr"/>
       <c r="K32" s="20" t="n">
-        <v>1.1</v>
+        <v>1.78</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>0</v>
@@ -10911,7 +10841,7 @@
         <v>0</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>480.85670682</v>
+        <v>504.94411968</v>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
@@ -10920,7 +10850,7 @@
       </c>
       <c r="J33" s="21" t="inlineStr"/>
       <c r="K33" s="20" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>10</v>
@@ -12105,7 +12035,7 @@
         <v>4.1</v>
       </c>
       <c r="E74" s="13" t="n">
-        <v>57306.97979340001</v>
+        <v>65690.538</v>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
@@ -12323,11 +12253,11 @@
         <v>20.8</v>
       </c>
       <c r="E81" s="13" t="n">
-        <v>386.25986712</v>
+        <v>9710.28389253</v>
       </c>
       <c r="F81" s="14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G81" s="12" t="n">
@@ -12590,11 +12520,11 @@
         <v>19</v>
       </c>
       <c r="E92" s="13" t="n">
-        <v>386.25986712</v>
+        <v>9710.28389253</v>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
@@ -13161,17 +13091,17 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>TCRX</t>
+          <t>HOWL</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E113" s="13" t="n">
-        <v>22.05878664</v>
+        <v>17.057482767</v>
       </c>
       <c r="F113" s="11" t="n">
         <v>0</v>
@@ -13184,7 +13114,7 @@
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
-          <t>TScan Therapeutics, Inc.</t>
+          <t>Werewolf Therapeutics, Inc.</t>
         </is>
       </c>
     </row>
@@ -13196,17 +13126,17 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>HOWL</t>
+          <t>AYTU</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="E114" s="13" t="n">
-        <v>17.057482767</v>
+        <v>24.79371048</v>
       </c>
       <c r="F114" s="11" t="n">
         <v>0</v>
@@ -13219,7 +13149,7 @@
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>Werewolf Therapeutics, Inc.</t>
+          <t>Aytu BioPharma, Inc.</t>
         </is>
       </c>
     </row>
@@ -13231,17 +13161,17 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>CTNM</t>
+          <t>DRUG</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
         <v>5</v>
       </c>
       <c r="D115" s="12" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="E115" s="13" t="n">
-        <v>275.80412562</v>
+        <v>274.43111742</v>
       </c>
       <c r="F115" s="11" t="n">
         <v>0</v>
@@ -13254,7 +13184,7 @@
       </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
-          <t>Contineum Therapeutics, Inc.</t>
+          <t>Bright Minds Biosciences Inc.</t>
         </is>
       </c>
     </row>
@@ -13266,17 +13196,17 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>DRUG</t>
+          <t>FHTX</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="E116" s="13" t="n">
-        <v>274.43111742</v>
+        <v>243.6627763</v>
       </c>
       <c r="F116" s="11" t="n">
         <v>0</v>
@@ -13289,7 +13219,7 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>Bright Minds Biosciences Inc.</t>
+          <t>Foghorn Therapeutics Inc.</t>
         </is>
       </c>
     </row>
@@ -13301,30 +13231,30 @@
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>ANNX</t>
+          <t>ALXO</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D117" s="12" t="n">
-        <v>5.3</v>
+        <v>1.1</v>
       </c>
       <c r="E117" s="13" t="n">
-        <v>188.9614685</v>
+        <v>205.88126301</v>
       </c>
       <c r="F117" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G117" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H117" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I117" s="14" t="inlineStr">
         <is>
-          <t>Annexon, Inc.</t>
+          <t>ALX Oncology Holdings Inc.</t>
         </is>
       </c>
     </row>
@@ -13336,17 +13266,17 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>FHTX</t>
+          <t>ACET</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="E118" s="13" t="n">
-        <v>243.6627763</v>
+        <v>75.7207116</v>
       </c>
       <c r="F118" s="11" t="n">
         <v>0</v>
@@ -13355,11 +13285,11 @@
         <v>0</v>
       </c>
       <c r="H118" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>Foghorn Therapeutics Inc.</t>
+          <t>Adicet Bio, Inc.</t>
         </is>
       </c>
     </row>
@@ -13371,17 +13301,17 @@
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>ALXO</t>
+          <t>OKUR</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
         <v>4</v>
       </c>
       <c r="D119" s="12" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="E119" s="13" t="n">
-        <v>205.88126301</v>
+        <v>180.9717504</v>
       </c>
       <c r="F119" s="11" t="n">
         <v>0</v>
@@ -13390,11 +13320,11 @@
         <v>0</v>
       </c>
       <c r="H119" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I119" s="14" t="inlineStr">
         <is>
-          <t>ALX Oncology Holdings Inc.</t>
+          <t>OnKure Therapeutics, Inc.</t>
         </is>
       </c>
     </row>
@@ -13476,17 +13406,17 @@
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>NUVL</t>
+          <t>STOK</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>20.8</v>
+        <v>9</v>
       </c>
       <c r="E122" s="13" t="n">
-        <v>386.25986712</v>
+        <v>1930.731305</v>
       </c>
       <c r="F122" s="11" t="n">
         <v>0</v>
@@ -13495,11 +13425,11 @@
         <v>1</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>Nuvalent, Inc.</t>
+          <t>Stoke Therapeutics, Inc.</t>
         </is>
       </c>
     </row>
@@ -13511,30 +13441,30 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>STOK</t>
+          <t>RVMDW</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="E123" s="13" t="n">
-        <v>1930.731305</v>
+        <v>1466.9155878</v>
       </c>
       <c r="F123" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G123" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H123" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
-          <t>Stoke Therapeutics, Inc.</t>
+          <t>Revolution Medicines, Inc.</t>
         </is>
       </c>
     </row>
@@ -13546,20 +13476,20 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>RVMDW</t>
+          <t>SION</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>8.9</v>
+        <v>4.2</v>
       </c>
       <c r="E124" s="13" t="n">
-        <v>1466.9155878</v>
+        <v>1684.107309</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G124" s="11" t="n">
         <v>0</v>
@@ -13569,7 +13499,7 @@
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>Revolution Medicines, Inc.</t>
+          <t>Sionna Therapeutics, Inc.</t>
         </is>
       </c>
     </row>
@@ -13616,17 +13546,17 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>PRAX</t>
+          <t>NUVL</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>12.8</v>
+        <v>20.8</v>
       </c>
       <c r="E126" s="13" t="n">
-        <v>7870.45668794</v>
+        <v>9710.28389253</v>
       </c>
       <c r="F126" s="11" t="n">
         <v>0</v>
@@ -13639,7 +13569,7 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>Praxis Precision Medicines, Inc.</t>
+          <t>Nuvalent, Inc.</t>
         </is>
       </c>
     </row>
@@ -13651,17 +13581,17 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>KYMR</t>
+          <t>PRAX</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>14.6</v>
+        <v>12.8</v>
       </c>
       <c r="E127" s="13" t="n">
-        <v>7438.55368284</v>
+        <v>7870.45668794</v>
       </c>
       <c r="F127" s="11" t="n">
         <v>0</v>
@@ -13674,7 +13604,7 @@
       </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
-          <t>Kymera Therapeutics, Inc.</t>
+          <t>Praxis Precision Medicines, Inc.</t>
         </is>
       </c>
     </row>
@@ -13686,30 +13616,30 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>KYMR</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>2.6</v>
+        <v>14.6</v>
       </c>
       <c r="E128" s="13" t="n">
-        <v>2704.11351031</v>
+        <v>7438.55368284</v>
       </c>
       <c r="F128" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G128" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H128" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>Disc Medicine, Inc.</t>
+          <t>Kymera Therapeutics, Inc.</t>
         </is>
       </c>
     </row>
@@ -13721,30 +13651,30 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>EWTX</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D129" s="12" t="n">
-        <v>9.699999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="E129" s="13" t="n">
-        <v>3960.49855086</v>
+        <v>2704.11351031</v>
       </c>
       <c r="F129" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G129" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H129" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>Edgewise Therapeutics, Inc.</t>
+          <t>Disc Medicine, Inc.</t>
         </is>
       </c>
     </row>
@@ -15928,7 +15858,7 @@
         <v>0.4</v>
       </c>
       <c r="E55" s="13" t="n">
-        <v>159.28732995</v>
+        <v>116.725</v>
       </c>
       <c r="F55" s="14" t="inlineStr">
         <is>
@@ -16099,7 +16029,7 @@
         <v>0.8</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>7834.14584</v>
+        <v>7839.114990000001</v>
       </c>
       <c r="F63" s="14" t="inlineStr">
         <is>
@@ -17466,7 +17396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O104"/>
+  <dimension ref="A1:O105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18500,7 +18430,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>4065.54708848</v>
+        <v>3872.272</v>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
@@ -18509,7 +18439,7 @@
       </c>
       <c r="J24" s="21" t="inlineStr"/>
       <c r="K24" s="20" t="n">
-        <v>20.87</v>
+        <v>19.88</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>5.7</v>
@@ -18645,7 +18575,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="13" t="n">
-        <v>1557.06982</v>
+        <v>1576.52829</v>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
@@ -18653,10 +18583,10 @@
         </is>
       </c>
       <c r="J27" s="18" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="K27" s="20" t="n">
-        <v>3.84</v>
+        <v>3.89</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>0</v>
@@ -19302,7 +19232,7 @@
         <v>5</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>38661.8918228</v>
+        <v>66914.08</v>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
@@ -20232,22 +20162,22 @@
     <row r="85" ht="18" customHeight="1">
       <c r="A85" s="14" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>WW</t>
+          <t>HUBG</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D85" s="12" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>191.976192</v>
+        <v>2.67523635</v>
       </c>
       <c r="F85" s="11" t="n">
         <v>0</v>
@@ -20256,11 +20186,11 @@
         <v>0</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="I85" s="14" t="inlineStr">
         <is>
-          <t>WW International, Inc.</t>
+          <t>Hub Group, Inc.</t>
         </is>
       </c>
     </row>
@@ -20272,17 +20202,17 @@
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>TTGT</t>
+          <t>WW</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="E86" s="13" t="n">
-        <v>260.2779948</v>
+        <v>191.976192</v>
       </c>
       <c r="F86" s="11" t="n">
         <v>0</v>
@@ -20291,11 +20221,11 @@
         <v>0</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>TechTarget, Inc.</t>
+          <t>WW International, Inc.</t>
         </is>
       </c>
     </row>
@@ -20307,17 +20237,17 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>INSE</t>
+          <t>TTGT</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D87" s="12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>213.40284</v>
+        <v>260.2779948</v>
       </c>
       <c r="F87" s="11" t="n">
         <v>0</v>
@@ -20330,7 +20260,7 @@
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
-          <t>Inspired Entertainment, Inc.</t>
+          <t>TechTarget, Inc.</t>
         </is>
       </c>
     </row>
@@ -20342,7 +20272,7 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>FC</t>
+          <t>INSE</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
@@ -20352,7 +20282,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="13" t="n">
-        <v>269.29868716</v>
+        <v>213.40284</v>
       </c>
       <c r="F88" s="11" t="n">
         <v>0</v>
@@ -20365,7 +20295,7 @@
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>Franklin Covey Co.</t>
+          <t>Inspired Entertainment, Inc.</t>
         </is>
       </c>
     </row>
@@ -20377,7 +20307,7 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>SFIX</t>
+          <t>FC</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
@@ -20387,7 +20317,7 @@
         <v>0</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>108.91595676</v>
+        <v>269.29868716</v>
       </c>
       <c r="F89" s="11" t="n">
         <v>0</v>
@@ -20400,42 +20330,42 @@
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
-          <t>Stitch Fix, Inc.</t>
+          <t>Franklin Covey Co.</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>OI</t>
+          <t>TBI</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="E90" s="13" t="n">
-        <v>1414.95496649</v>
+        <v>203.7074097</v>
       </c>
       <c r="F90" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G90" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>O-I Glass, Inc.</t>
+          <t>TrueBlue, Inc.</t>
         </is>
       </c>
     </row>
@@ -20447,30 +20377,30 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>GSM</t>
+          <t>OI</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D91" s="12" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>730.62462147</v>
+        <v>1414.95496649</v>
       </c>
       <c r="F91" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G91" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" s="12" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="I91" s="14" t="inlineStr">
         <is>
-          <t>Ferroglobe PLC</t>
+          <t>O-I Glass, Inc.</t>
         </is>
       </c>
     </row>
@@ -20482,17 +20412,17 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>RVLV</t>
+          <t>GSM</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="E92" s="13" t="n">
-        <v>1557.06982</v>
+        <v>730.62462147</v>
       </c>
       <c r="F92" s="11" t="n">
         <v>0</v>
@@ -20505,7 +20435,7 @@
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>Revolve Group, Inc.</t>
+          <t>Ferroglobe PLC</t>
         </is>
       </c>
     </row>
@@ -20517,17 +20447,17 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>PUMP</t>
+          <t>RVLV</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D93" s="12" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>1808.600396</v>
+        <v>1576.52829</v>
       </c>
       <c r="F93" s="11" t="n">
         <v>0</v>
@@ -20540,7 +20470,7 @@
       </c>
       <c r="I93" s="14" t="inlineStr">
         <is>
-          <t>ProPetro Holding Corp.</t>
+          <t>Revolve Group, Inc.</t>
         </is>
       </c>
     </row>
@@ -20552,17 +20482,17 @@
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>CCB</t>
+          <t>PUMP</t>
         </is>
       </c>
       <c r="C94" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D94" s="12" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="E94" s="13" t="n">
-        <v>1092.5770932</v>
+        <v>1808.600396</v>
       </c>
       <c r="F94" s="11" t="n">
         <v>0</v>
@@ -20575,29 +20505,29 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>Coastal Financial Corporation</t>
+          <t>ProPetro Holding Corp.</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
       <c r="A95" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>small</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>FRPT</t>
+          <t>CCB</t>
         </is>
       </c>
       <c r="C95" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D95" s="12" t="n">
-        <v>39.8</v>
+        <v>1.2</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>2703.34493291</v>
+        <v>1092.5770932</v>
       </c>
       <c r="F95" s="11" t="n">
         <v>0</v>
@@ -20610,7 +20540,7 @@
       </c>
       <c r="I95" s="14" t="inlineStr">
         <is>
-          <t>Freshpet, Inc.</t>
+          <t>Coastal Financial Corporation</t>
         </is>
       </c>
     </row>
@@ -20622,17 +20552,17 @@
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>CALY</t>
+          <t>FRPT</t>
         </is>
       </c>
       <c r="C96" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D96" s="12" t="n">
-        <v>9.1</v>
+        <v>39.8</v>
       </c>
       <c r="E96" s="13" t="n">
-        <v>3275.18279786</v>
+        <v>2703.34493291</v>
       </c>
       <c r="F96" s="11" t="n">
         <v>0</v>
@@ -20645,7 +20575,7 @@
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>Callaway Golf Company</t>
+          <t>Freshpet, Inc.</t>
         </is>
       </c>
     </row>
@@ -20657,30 +20587,30 @@
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>POOL</t>
+          <t>CALY</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D97" s="12" t="n">
-        <v>6.7</v>
+        <v>9.1</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>7251.79316697</v>
+        <v>3275.18279786</v>
       </c>
       <c r="F97" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G97" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I97" s="14" t="inlineStr">
         <is>
-          <t>Pool Corporation</t>
+          <t>Callaway Golf Company</t>
         </is>
       </c>
     </row>
@@ -20692,17 +20622,17 @@
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>AAP</t>
+          <t>POOL</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>5.4</v>
+        <v>6.7</v>
       </c>
       <c r="E98" s="13" t="n">
-        <v>3624.03</v>
+        <v>7251.79316697</v>
       </c>
       <c r="F98" s="11" t="n">
         <v>0</v>
@@ -20715,7 +20645,7 @@
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>Advance Auto Parts, Inc.</t>
+          <t>Pool Corporation</t>
         </is>
       </c>
     </row>
@@ -20727,17 +20657,17 @@
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>EXTR</t>
+          <t>AAP</t>
         </is>
       </c>
       <c r="C99" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99" s="12" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>4103.81640144</v>
+        <v>3624.03</v>
       </c>
       <c r="F99" s="11" t="n">
         <v>0</v>
@@ -20750,42 +20680,42 @@
       </c>
       <c r="I99" s="14" t="inlineStr">
         <is>
-          <t>Extreme Networks, Inc.</t>
+          <t>Advance Auto Parts, Inc.</t>
         </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>EXTR</t>
         </is>
       </c>
       <c r="C100" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D100" s="12" t="n">
-        <v>26.2</v>
+        <v>0.9</v>
       </c>
       <c r="E100" s="13" t="n">
-        <v>486522.14184</v>
+        <v>4103.81640144</v>
       </c>
       <c r="F100" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G100" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>Lam Research Corporation</t>
+          <t>Extreme Networks, Inc.</t>
         </is>
       </c>
     </row>
@@ -20797,17 +20727,17 @@
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>VLTO</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C101" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D101" s="12" t="n">
-        <v>6.8</v>
+        <v>26.2</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>20635.25032932</v>
+        <v>486522.14184</v>
       </c>
       <c r="F101" s="11" t="n">
         <v>0</v>
@@ -20820,7 +20750,7 @@
       </c>
       <c r="I101" s="14" t="inlineStr">
         <is>
-          <t>Veralto Corporation</t>
+          <t>Lam Research Corporation</t>
         </is>
       </c>
     </row>
@@ -20832,20 +20762,20 @@
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>VLTO</t>
         </is>
       </c>
       <c r="C102" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D102" s="12" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="E102" s="13" t="n">
-        <v>13062.56852616</v>
+        <v>20635.25032932</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G102" s="11" t="n">
         <v>0</v>
@@ -20855,7 +20785,7 @@
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>Solventum Corporation</t>
+          <t>Veralto Corporation</t>
         </is>
       </c>
     </row>
@@ -20867,17 +20797,17 @@
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>DOCN</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="C103" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D103" s="12" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>18083.18164187</v>
+        <v>13062.56852616</v>
       </c>
       <c r="F103" s="11" t="n">
         <v>1</v>
@@ -20890,7 +20820,7 @@
       </c>
       <c r="I103" s="14" t="inlineStr">
         <is>
-          <t>DigitalOcean Holdings, Inc.</t>
+          <t>Solventum Corporation</t>
         </is>
       </c>
     </row>
@@ -20902,28 +20832,63 @@
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
+          <t>DOCN</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" s="12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E104" s="13" t="n">
+        <v>18083.18164187</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="14" t="inlineStr">
+        <is>
+          <t>DigitalOcean Holdings, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="14" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
           <t>RTO</t>
         </is>
       </c>
-      <c r="C104" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D104" s="12" t="n">
+      <c r="C105" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E104" s="13" t="n">
+      <c r="E105" s="13" t="n">
         <v>71941.6159248</v>
       </c>
-      <c r="F104" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="14" t="inlineStr">
+      <c r="F105" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="14" t="inlineStr">
         <is>
           <t>Rentokil Initial plc</t>
         </is>
@@ -20950,7 +20915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O132"/>
+  <dimension ref="A1:O131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21298,18 +21263,18 @@
         <v>1</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>9160.919039999999</v>
+        <v>14927.87712</v>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J10" s="18" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="K10" s="20" t="n">
-        <v>2.46</v>
+        <v>4.01</v>
       </c>
       <c r="L10" s="12" t="n">
         <v>5</v>
@@ -21633,7 +21598,7 @@
         <v>2</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>1462675.48</v>
+        <v>1479992.08</v>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
@@ -21641,10 +21606,10 @@
         </is>
       </c>
       <c r="J17" s="18" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="K17" s="20" t="n">
-        <v>6</v>
+        <v>6.07</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>0</v>
@@ -21682,7 +21647,7 @@
         <v>2</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>54313.77967512</v>
+        <v>58257.37343047999</v>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
@@ -21690,10 +21655,10 @@
         </is>
       </c>
       <c r="J18" s="18" t="n">
-        <v>21.7</v>
+        <v>23.4</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>4.34</v>
+        <v>4.65</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>0</v>
@@ -21925,7 +21890,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="13" t="n">
-        <v>33508.15951608</v>
+        <v>35433.62930808</v>
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
@@ -21933,10 +21898,10 @@
         </is>
       </c>
       <c r="J23" s="18" t="n">
-        <v>70.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K23" s="20" t="n">
-        <v>10.54</v>
+        <v>11.14</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>5</v>
@@ -21976,7 +21941,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>79118.24086059</v>
+        <v>79106.814</v>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
@@ -21987,7 +21952,7 @@
         <v>21.8</v>
       </c>
       <c r="K24" s="20" t="n">
-        <v>17.86</v>
+        <v>17.85</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>0</v>
@@ -22074,7 +22039,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>6716.809792</v>
+        <v>7048.387579200001</v>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
@@ -22083,7 +22048,7 @@
       </c>
       <c r="J26" s="21" t="inlineStr"/>
       <c r="K26" s="20" t="n">
-        <v>4.66</v>
+        <v>4.89</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>0</v>
@@ -22219,7 +22184,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>29437.82641572</v>
+        <v>29644.60716978</v>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
@@ -22227,10 +22192,10 @@
         </is>
       </c>
       <c r="J29" s="18" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="K29" s="20" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>0</v>
@@ -22468,7 +22433,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>75529.51433999999</v>
+        <v>76725.86796</v>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
@@ -22476,10 +22441,10 @@
         </is>
       </c>
       <c r="J34" s="18" t="n">
-        <v>48.3</v>
+        <v>49.1</v>
       </c>
       <c r="K34" s="20" t="n">
-        <v>7.41</v>
+        <v>7.52</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>0</v>
@@ -22864,7 +22829,7 @@
         <v>0.9</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>5377.20768</v>
+        <v>5420.69086</v>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
@@ -22926,7 +22891,7 @@
         <v>21.8</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>1462675.48</v>
+        <v>1479992.08</v>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
@@ -23022,11 +22987,11 @@
         <v>3.9</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>4.695e-05</v>
+        <v>20798.85</v>
       </c>
       <c r="F53" s="14" t="inlineStr">
         <is>
-          <t>nano</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G53" s="12" t="n">
@@ -23054,7 +23019,7 @@
         <v>17.2</v>
       </c>
       <c r="E54" s="13" t="n">
-        <v>21844.42111488</v>
+        <v>21061.44768</v>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
@@ -23086,7 +23051,7 @@
         <v>6.6</v>
       </c>
       <c r="E55" s="13" t="n">
-        <v>75529.51433999999</v>
+        <v>76725.86796</v>
       </c>
       <c r="F55" s="14" t="inlineStr">
         <is>
@@ -23118,7 +23083,7 @@
         <v>7.3</v>
       </c>
       <c r="E56" s="13" t="n">
-        <v>6716.809792</v>
+        <v>7048.387579200001</v>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
@@ -23361,7 +23326,7 @@
         <v>2.9</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>33508.15951608</v>
+        <v>35433.62930808</v>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
@@ -23489,7 +23454,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="E70" s="13" t="n">
-        <v>97986.24000000001</v>
+        <v>98015.51232000001</v>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
@@ -23617,7 +23582,7 @@
         <v>6.6</v>
       </c>
       <c r="E74" s="13" t="n">
-        <v>75529.51433999999</v>
+        <v>76725.86796</v>
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
@@ -23930,7 +23895,7 @@
         <v>24</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>38247.93654444</v>
+        <v>42281.06830353</v>
       </c>
       <c r="F87" s="14" t="inlineStr">
         <is>
@@ -24178,7 +24143,7 @@
         <v>26</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>97243.60665285001</v>
+        <v>98961.44870745001</v>
       </c>
       <c r="F95" s="14" t="inlineStr">
         <is>
@@ -24364,7 +24329,7 @@
         <v>71</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>1462675.48</v>
+        <v>1479992.08</v>
       </c>
       <c r="F101" s="14" t="inlineStr">
         <is>
@@ -24457,7 +24422,7 @@
         <v>21</v>
       </c>
       <c r="E104" s="13" t="n">
-        <v>6716.809792</v>
+        <v>7048.387579200001</v>
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
@@ -24565,20 +24530,20 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="E110" s="13" t="n">
-        <v>4.695e-05</v>
+        <v>0.56213788</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" s="11" t="n">
         <v>0</v>
@@ -24588,7 +24553,7 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Erie Indemnity Company</t>
         </is>
       </c>
     </row>
@@ -24600,7 +24565,7 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>CRIS</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
@@ -24610,7 +24575,7 @@
         <v>0</v>
       </c>
       <c r="E111" s="13" t="n">
-        <v>0.56213788</v>
+        <v>16.410029753</v>
       </c>
       <c r="F111" s="11" t="n">
         <v>0</v>
@@ -24623,29 +24588,29 @@
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
-          <t>Erie Indemnity Company</t>
+          <t>Curis, Inc.</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>nano</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>CRIS</t>
+          <t>IVVD</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E112" s="13" t="n">
-        <v>16.410029753</v>
+        <v>285.7397676948</v>
       </c>
       <c r="F112" s="11" t="n">
         <v>0</v>
@@ -24654,11 +24619,11 @@
         <v>0</v>
       </c>
       <c r="H112" s="12" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>Curis, Inc.</t>
+          <t>Invivyd, Inc.</t>
         </is>
       </c>
     </row>
@@ -24670,17 +24635,17 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>IVVD</t>
+          <t>GUTS</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E113" s="13" t="n">
-        <v>285.7397676948</v>
+        <v>136.120810254</v>
       </c>
       <c r="F113" s="11" t="n">
         <v>0</v>
@@ -24689,11 +24654,11 @@
         <v>0</v>
       </c>
       <c r="H113" s="12" t="n">
-        <v>9.9</v>
+        <v>8.9</v>
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
-          <t>Invivyd, Inc.</t>
+          <t>Fractyl Health, Inc.</t>
         </is>
       </c>
     </row>
@@ -24705,17 +24670,17 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>RERE</t>
+          <t>PAASF</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E114" s="13" t="n">
-        <v>73.62787040000001</v>
+        <v>295.2929321999999</v>
       </c>
       <c r="F114" s="11" t="n">
         <v>0</v>
@@ -24724,11 +24689,11 @@
         <v>0</v>
       </c>
       <c r="H114" s="12" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>ATRenew Inc.</t>
+          <t>Pan American Silver Corp.</t>
         </is>
       </c>
     </row>
@@ -24740,7 +24705,7 @@
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>GUTS</t>
+          <t>PEPG</t>
         </is>
       </c>
       <c r="C115" s="11" t="n">
@@ -24750,7 +24715,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="13" t="n">
-        <v>136.120810254</v>
+        <v>123.81289485</v>
       </c>
       <c r="F115" s="11" t="n">
         <v>0</v>
@@ -24759,11 +24724,11 @@
         <v>0</v>
       </c>
       <c r="H115" s="12" t="n">
-        <v>8.9</v>
+        <v>2</v>
       </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
-          <t>Fractyl Health, Inc.</t>
+          <t>PepGen Inc.</t>
         </is>
       </c>
     </row>
@@ -24775,7 +24740,7 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>PAASF</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
@@ -24785,7 +24750,7 @@
         <v>0</v>
       </c>
       <c r="E116" s="13" t="n">
-        <v>295.2929321999999</v>
+        <v>295.7383494</v>
       </c>
       <c r="F116" s="11" t="n">
         <v>0</v>
@@ -24798,29 +24763,29 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>Pan American Silver Corp.</t>
+          <t>Citizens, Inc.</t>
         </is>
       </c>
     </row>
     <row r="117" ht="18" customHeight="1">
       <c r="A117" s="14" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>small</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>PEPG</t>
+          <t>BELFA</t>
         </is>
       </c>
       <c r="C117" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D117" s="12" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="E117" s="13" t="n">
-        <v>123.81289485</v>
+        <v>578.0263622399999</v>
       </c>
       <c r="F117" s="11" t="n">
         <v>0</v>
@@ -24829,11 +24794,11 @@
         <v>0</v>
       </c>
       <c r="H117" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I117" s="14" t="inlineStr">
         <is>
-          <t>PepGen Inc.</t>
+          <t>Bel Fuse Inc.</t>
         </is>
       </c>
     </row>
@@ -24845,17 +24810,17 @@
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>BELFA</t>
+          <t>TIC</t>
         </is>
       </c>
       <c r="C118" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D118" s="12" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E118" s="13" t="n">
-        <v>578.0263622399999</v>
+        <v>1861.17872568</v>
       </c>
       <c r="F118" s="11" t="n">
         <v>0</v>
@@ -24868,7 +24833,7 @@
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>Bel Fuse Inc.</t>
+          <t>TIC Solutions, Inc.</t>
         </is>
       </c>
     </row>
@@ -24880,20 +24845,20 @@
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>TIC</t>
+          <t>WLTH</t>
         </is>
       </c>
       <c r="C119" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D119" s="12" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E119" s="13" t="n">
-        <v>1861.17872568</v>
+        <v>1260.60866304</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G119" s="11" t="n">
         <v>0</v>
@@ -24903,7 +24868,7 @@
       </c>
       <c r="I119" s="14" t="inlineStr">
         <is>
-          <t>TIC Solutions, Inc.</t>
+          <t>Wealthfront Corporation</t>
         </is>
       </c>
     </row>
@@ -24915,20 +24880,20 @@
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>WLTH</t>
+          <t>GIII</t>
         </is>
       </c>
       <c r="C120" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D120" s="12" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E120" s="13" t="n">
-        <v>1260.60866304</v>
+        <v>1466.96622321</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G120" s="11" t="n">
         <v>0</v>
@@ -24938,7 +24903,7 @@
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>Wealthfront Corporation</t>
+          <t>G-III Apparel Group, Ltd.</t>
         </is>
       </c>
     </row>
@@ -24950,55 +24915,55 @@
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>MIR</t>
+          <t>AMPL</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D121" s="12" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="E121" s="13" t="n">
-        <v>348.9375</v>
+        <v>870.4685900000001</v>
       </c>
       <c r="F121" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G121" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H121" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I121" s="14" t="inlineStr">
         <is>
-          <t>Mirion Technologies, Inc.</t>
+          <t>Amplitude, Inc.</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>GIII</t>
+          <t>CHYM</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>0.4</v>
+        <v>7.3</v>
       </c>
       <c r="E122" s="13" t="n">
-        <v>1466.96622321</v>
+        <v>7048.387579200001</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" s="11" t="n">
         <v>0</v>
@@ -25008,7 +24973,7 @@
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>G-III Apparel Group, Ltd.</t>
+          <t>Chime Financial, Inc.</t>
         </is>
       </c>
     </row>
@@ -25020,30 +24985,30 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>NCLH</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>4.4</v>
+        <v>13.4</v>
       </c>
       <c r="E123" s="13" t="n">
-        <v>9160.919039999999</v>
+        <v>9384.211261600001</v>
       </c>
       <c r="F123" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G123" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
-          <t>Carvana Co.</t>
+          <t>Norwegian Cruise Line Holdings L</t>
         </is>
       </c>
     </row>
@@ -25055,20 +25020,20 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>CHYM</t>
+          <t>NTSK</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>7.3</v>
+        <v>0.2</v>
       </c>
       <c r="E124" s="13" t="n">
-        <v>6716.809792</v>
+        <v>3624.467052850001</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124" s="11" t="n">
         <v>0</v>
@@ -25078,7 +25043,7 @@
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>Chime Financial, Inc.</t>
+          <t>Netskope, Inc.</t>
         </is>
       </c>
     </row>
@@ -25090,30 +25055,30 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>ZG</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>13.4</v>
+        <v>1.3</v>
       </c>
       <c r="E125" s="13" t="n">
-        <v>9384.211261600001</v>
+        <v>7786.033560000001</v>
       </c>
       <c r="F125" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G125" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H125" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
-          <t>Norwegian Cruise Line Holdings L</t>
+          <t>Zillow Group, Inc.</t>
         </is>
       </c>
     </row>
@@ -25125,20 +25090,20 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>NTSK</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="E126" s="13" t="n">
-        <v>3624.467052850001</v>
+        <v>5420.69086</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" s="11" t="n">
         <v>0</v>
@@ -25148,29 +25113,29 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>Netskope, Inc.</t>
+          <t>UiPath, Inc.</t>
         </is>
       </c>
     </row>
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>ZG</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>1.3</v>
+        <v>14.4</v>
       </c>
       <c r="E127" s="13" t="n">
-        <v>7657.30818</v>
+        <v>11983938.23164452</v>
       </c>
       <c r="F127" s="11" t="n">
         <v>0</v>
@@ -25183,7 +25148,7 @@
       </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
-          <t>Zillow Group, Inc.</t>
+          <t>Taiwan Semiconductor Manufacturi</t>
         </is>
       </c>
     </row>
@@ -25195,30 +25160,30 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
         <v>8</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>14.4</v>
+        <v>13.4</v>
       </c>
       <c r="E128" s="13" t="n">
-        <v>11983938.23164452</v>
+        <v>4459051.48</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G128" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H128" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>Taiwan Semiconductor Manufacturi</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
     </row>
@@ -25230,20 +25195,20 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
         <v>8</v>
       </c>
       <c r="D129" s="12" t="n">
-        <v>13.4</v>
+        <v>9.1</v>
       </c>
       <c r="E129" s="13" t="n">
-        <v>4459051.48</v>
+        <v>2628929.97506404</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G129" s="11" t="n">
         <v>1</v>
@@ -25253,7 +25218,7 @@
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
     </row>
@@ -25265,20 +25230,20 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>9.1</v>
+        <v>10.8</v>
       </c>
       <c r="E130" s="13" t="n">
-        <v>2628929.97506404</v>
+        <v>5098698</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G130" s="11" t="n">
         <v>1</v>
@@ -25288,7 +25253,7 @@
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
     </row>
@@ -25300,20 +25265,20 @@
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D131" s="12" t="n">
-        <v>10.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E131" s="13" t="n">
-        <v>5098698</v>
+        <v>1957030.6144473</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G131" s="11" t="n">
         <v>1</v>
@@ -25322,41 +25287,6 @@
         <v>0</v>
       </c>
       <c r="I131" s="14" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="A132" s="14" t="inlineStr">
-        <is>
-          <t>large</t>
-        </is>
-      </c>
-      <c r="B132" s="10" t="inlineStr">
-        <is>
-          <t>AVGO</t>
-        </is>
-      </c>
-      <c r="C132" s="11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D132" s="12" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="E132" s="13" t="n">
-        <v>1957030.6144473</v>
-      </c>
-      <c r="F132" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G132" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H132" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" s="14" t="inlineStr">
         <is>
           <t>Broadcom Inc.</t>
         </is>
@@ -27724,7 +27654,7 @@
         <v>0.9</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>34.83943536</v>
+        <v>34.88515212</v>
       </c>
       <c r="F71" s="11" t="n">
         <v>0</v>
@@ -28493,7 +28423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O82"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28751,7 +28681,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>11178.82945</v>
+        <v>11183.824548</v>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
@@ -29184,7 +29114,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>1941.3238576</v>
+        <v>1787.83192669</v>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
@@ -29192,10 +29122,10 @@
         </is>
       </c>
       <c r="J17" s="18" t="n">
-        <v>12.2</v>
+        <v>11.3</v>
       </c>
       <c r="K17" s="20" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>0</v>
@@ -30296,7 +30226,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>11178.82945</v>
+        <v>11183.824548</v>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
@@ -30516,7 +30446,7 @@
       </c>
       <c r="B60" s="10" t="inlineStr">
         <is>
-          <t>SER</t>
+          <t>ALGS</t>
         </is>
       </c>
       <c r="C60" s="11" t="n">
@@ -30526,7 +30456,7 @@
         <v>0.3</v>
       </c>
       <c r="E60" s="13" t="n">
-        <v>31.4947605</v>
+        <v>32.67362208</v>
       </c>
       <c r="F60" s="11" t="n">
         <v>0</v>
@@ -30539,7 +30469,7 @@
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>Serina Therapeutics, Inc.</t>
+          <t>Aligos Therapeutics, Inc.</t>
         </is>
       </c>
     </row>
@@ -30551,17 +30481,17 @@
       </c>
       <c r="B61" s="10" t="inlineStr">
         <is>
-          <t>TELA</t>
+          <t>SER</t>
         </is>
       </c>
       <c r="C61" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>35.857682946</v>
+        <v>31.4947605</v>
       </c>
       <c r="F61" s="11" t="n">
         <v>0</v>
@@ -30574,7 +30504,7 @@
       </c>
       <c r="I61" s="14" t="inlineStr">
         <is>
-          <t>TELA Bio, Inc.</t>
+          <t>Serina Therapeutics, Inc.</t>
         </is>
       </c>
     </row>
@@ -30586,17 +30516,17 @@
       </c>
       <c r="B62" s="10" t="inlineStr">
         <is>
-          <t>BOLD</t>
+          <t>TELA</t>
         </is>
       </c>
       <c r="C62" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D62" s="12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E62" s="13" t="n">
-        <v>32.12367872999999</v>
+        <v>35.857682946</v>
       </c>
       <c r="F62" s="11" t="n">
         <v>0</v>
@@ -30609,29 +30539,29 @@
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>Boundless Bio, Inc.</t>
+          <t>TELA Bio, Inc.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
       <c r="A63" s="14" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>nano</t>
         </is>
       </c>
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>BOLD</t>
         </is>
       </c>
       <c r="C63" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>184.50907547</v>
+        <v>32.12367872999999</v>
       </c>
       <c r="F63" s="11" t="n">
         <v>0</v>
@@ -30644,7 +30574,7 @@
       </c>
       <c r="I63" s="14" t="inlineStr">
         <is>
-          <t>Embecta Corp.</t>
+          <t>Boundless Bio, Inc.</t>
         </is>
       </c>
     </row>
@@ -30656,17 +30586,17 @@
       </c>
       <c r="B64" s="10" t="inlineStr">
         <is>
-          <t>TARA</t>
+          <t>EMBC</t>
         </is>
       </c>
       <c r="C64" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D64" s="12" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="E64" s="13" t="n">
-        <v>223.69286326</v>
+        <v>184.50907547</v>
       </c>
       <c r="F64" s="11" t="n">
         <v>0</v>
@@ -30679,7 +30609,7 @@
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>Protara Therapeutics, Inc.</t>
+          <t>Embecta Corp.</t>
         </is>
       </c>
     </row>
@@ -30691,17 +30621,17 @@
       </c>
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>DRUG</t>
+          <t>TARA</t>
         </is>
       </c>
       <c r="C65" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D65" s="12" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>274.43111742</v>
+        <v>223.69286326</v>
       </c>
       <c r="F65" s="11" t="n">
         <v>0</v>
@@ -30714,7 +30644,7 @@
       </c>
       <c r="I65" s="14" t="inlineStr">
         <is>
-          <t>Bright Minds Biosciences Inc.</t>
+          <t>Protara Therapeutics, Inc.</t>
         </is>
       </c>
     </row>
@@ -30726,17 +30656,17 @@
       </c>
       <c r="B66" s="10" t="inlineStr">
         <is>
-          <t>OKUR</t>
+          <t>DRUG</t>
         </is>
       </c>
       <c r="C66" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D66" s="12" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>180.9717504</v>
+        <v>274.43111742</v>
       </c>
       <c r="F66" s="11" t="n">
         <v>0</v>
@@ -30745,11 +30675,11 @@
         <v>0</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>OnKure Therapeutics, Inc.</t>
+          <t>Bright Minds Biosciences Inc.</t>
         </is>
       </c>
     </row>
@@ -30761,17 +30691,17 @@
       </c>
       <c r="B67" s="10" t="inlineStr">
         <is>
-          <t>PMVP</t>
+          <t>OKUR</t>
         </is>
       </c>
       <c r="C67" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D67" s="12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>60.26489557999999</v>
+        <v>180.9717504</v>
       </c>
       <c r="F67" s="11" t="n">
         <v>0</v>
@@ -30780,33 +30710,33 @@
         <v>0</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I67" s="14" t="inlineStr">
         <is>
-          <t>PMV Pharmaceuticals, Inc.</t>
+          <t>OnKure Therapeutics, Inc.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>AVR</t>
+          <t>PMVP</t>
         </is>
       </c>
       <c r="C68" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D68" s="12" t="n">
-        <v>4.3</v>
+        <v>0.5</v>
       </c>
       <c r="E68" s="13" t="n">
-        <v>952.00674534</v>
+        <v>60.26489557999999</v>
       </c>
       <c r="F68" s="11" t="n">
         <v>0</v>
@@ -30819,7 +30749,7 @@
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>Anteris Technologies Global Corp</t>
+          <t>PMV Pharmaceuticals, Inc.</t>
         </is>
       </c>
     </row>
@@ -30831,17 +30761,17 @@
       </c>
       <c r="B69" s="10" t="inlineStr">
         <is>
-          <t>TYRA</t>
+          <t>AVR</t>
         </is>
       </c>
       <c r="C69" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D69" s="12" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>1684.20118992</v>
+        <v>952.00674534</v>
       </c>
       <c r="F69" s="11" t="n">
         <v>0</v>
@@ -30850,11 +30780,11 @@
         <v>0</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I69" s="14" t="inlineStr">
         <is>
-          <t>Tyra Biosciences, Inc.</t>
+          <t>Anteris Technologies Global Corp</t>
         </is>
       </c>
     </row>
@@ -30866,17 +30796,17 @@
       </c>
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>ANIP</t>
+          <t>TYRA</t>
         </is>
       </c>
       <c r="C70" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D70" s="12" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="E70" s="13" t="n">
-        <v>1941.3238576</v>
+        <v>1684.20118992</v>
       </c>
       <c r="F70" s="11" t="n">
         <v>0</v>
@@ -30885,11 +30815,11 @@
         <v>0</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>ANI Pharmaceuticals, Inc.</t>
+          <t>Tyra Biosciences, Inc.</t>
         </is>
       </c>
     </row>
@@ -30901,17 +30831,17 @@
       </c>
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>VIR</t>
+          <t>ANIP</t>
         </is>
       </c>
       <c r="C71" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D71" s="12" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>1544.85208184</v>
+        <v>1787.83192669</v>
       </c>
       <c r="F71" s="11" t="n">
         <v>0</v>
@@ -30924,7 +30854,7 @@
       </c>
       <c r="I71" s="14" t="inlineStr">
         <is>
-          <t>Vir Biotechnology, Inc.</t>
+          <t>ANI Pharmaceuticals, Inc.</t>
         </is>
       </c>
     </row>
@@ -30936,17 +30866,17 @@
       </c>
       <c r="B72" s="10" t="inlineStr">
         <is>
-          <t>SION</t>
+          <t>VIR</t>
         </is>
       </c>
       <c r="C72" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D72" s="12" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="E72" s="13" t="n">
-        <v>1684.107309</v>
+        <v>1544.85208184</v>
       </c>
       <c r="F72" s="11" t="n">
         <v>0</v>
@@ -30959,42 +30889,42 @@
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>Sionna Therapeutics, Inc.</t>
+          <t>Vir Biotechnology, Inc.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="A73" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>small</t>
         </is>
       </c>
       <c r="B73" s="10" t="inlineStr">
         <is>
-          <t>MMS</t>
+          <t>SION</t>
         </is>
       </c>
       <c r="C73" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D73" s="12" t="n">
-        <v>7.1</v>
+        <v>1.7</v>
       </c>
       <c r="E73" s="13" t="n">
-        <v>2928.59983362</v>
+        <v>1684.107309</v>
       </c>
       <c r="F73" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G73" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="14" t="inlineStr">
         <is>
-          <t>Maximus, Inc.</t>
+          <t>Sionna Therapeutics, Inc.</t>
         </is>
       </c>
     </row>
@@ -31006,17 +30936,17 @@
       </c>
       <c r="B74" s="10" t="inlineStr">
         <is>
-          <t>WAY</t>
+          <t>MMS</t>
         </is>
       </c>
       <c r="C74" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D74" s="12" t="n">
-        <v>5.7</v>
+        <v>7.1</v>
       </c>
       <c r="E74" s="13" t="n">
-        <v>3542.78409677</v>
+        <v>2928.59983362</v>
       </c>
       <c r="F74" s="11" t="n">
         <v>0</v>
@@ -31029,7 +30959,7 @@
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>Waystar Holding Corp.</t>
+          <t>Maximus, Inc.</t>
         </is>
       </c>
     </row>
@@ -31041,30 +30971,30 @@
       </c>
       <c r="B75" s="10" t="inlineStr">
         <is>
-          <t>DNTH</t>
+          <t>WAY</t>
         </is>
       </c>
       <c r="C75" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D75" s="12" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>4509.41756017</v>
+        <v>3542.78409677</v>
       </c>
       <c r="F75" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G75" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I75" s="14" t="inlineStr">
         <is>
-          <t>Dianthus Therapeutics, Inc.</t>
+          <t>Waystar Holding Corp.</t>
         </is>
       </c>
     </row>
@@ -31076,17 +31006,17 @@
       </c>
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>CORT</t>
+          <t>DNTH</t>
         </is>
       </c>
       <c r="C76" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D76" s="12" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="E76" s="13" t="n">
-        <v>8578.46587654</v>
+        <v>4509.41756017</v>
       </c>
       <c r="F76" s="11" t="n">
         <v>0</v>
@@ -31099,7 +31029,7 @@
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>Corcept Therapeutics Incorporate</t>
+          <t>Dianthus Therapeutics, Inc.</t>
         </is>
       </c>
     </row>
@@ -31111,17 +31041,17 @@
       </c>
       <c r="B77" s="10" t="inlineStr">
         <is>
-          <t>LIVN</t>
+          <t>CORT</t>
         </is>
       </c>
       <c r="C77" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D77" s="12" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="E77" s="13" t="n">
-        <v>4312.282733</v>
+        <v>8578.46587654</v>
       </c>
       <c r="F77" s="11" t="n">
         <v>0</v>
@@ -31134,42 +31064,42 @@
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
-          <t>LivaNova PLC</t>
+          <t>Corcept Therapeutics Incorporate</t>
         </is>
       </c>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
         <is>
-          <t>ICLR</t>
+          <t>LIVN</t>
         </is>
       </c>
       <c r="C78" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D78" s="12" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="E78" s="13" t="n">
-        <v>11178.82945</v>
+        <v>4312.282733</v>
       </c>
       <c r="F78" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G78" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>ICON Public Limited Company</t>
+          <t>LivaNova PLC</t>
         </is>
       </c>
     </row>
@@ -31181,17 +31111,17 @@
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>ICLR</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D79" s="12" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>52887.5329398</v>
+        <v>11183.824548</v>
       </c>
       <c r="F79" s="11" t="n">
         <v>0</v>
@@ -31204,7 +31134,7 @@
       </c>
       <c r="I79" s="14" t="inlineStr">
         <is>
-          <t>Cencora, Inc.</t>
+          <t>ICON Public Limited Company</t>
         </is>
       </c>
     </row>
@@ -31216,30 +31146,30 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>GLAXF</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D80" s="12" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>110906.9371682</v>
+        <v>52887.5329398</v>
       </c>
       <c r="F80" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G80" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>GSK plc</t>
+          <t>Cencora, Inc.</t>
         </is>
       </c>
     </row>
@@ -31251,17 +31181,17 @@
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>GLAXF</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D81" s="12" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="E81" s="13" t="n">
-        <v>153993.63684789</v>
+        <v>110906.9371682</v>
       </c>
       <c r="F81" s="11" t="n">
         <v>0</v>
@@ -31274,7 +31204,7 @@
       </c>
       <c r="I81" s="14" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>GSK plc</t>
         </is>
       </c>
     </row>
@@ -31286,28 +31216,63 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
+          <t>ABT</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" s="12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E82" s="13" t="n">
+        <v>153993.63684789</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="14" t="inlineStr">
+        <is>
+          <t>Abbott Laboratories</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
           <t>SNYNF</t>
         </is>
       </c>
-      <c r="C82" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" s="12" t="n">
+      <c r="C83" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" s="12" t="n">
         <v>1.7</v>
       </c>
-      <c r="E82" s="13" t="n">
+      <c r="E83" s="13" t="n">
         <v>108443.65164728</v>
       </c>
-      <c r="F82" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="14" t="inlineStr">
+      <c r="F83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="14" t="inlineStr">
         <is>
           <t>Sanofi</t>
         </is>
@@ -31584,7 +31549,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>75529.51433999999</v>
+        <v>76725.86796</v>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
@@ -31592,10 +31557,10 @@
         </is>
       </c>
       <c r="J8" s="18" t="n">
-        <v>48.3</v>
+        <v>49.1</v>
       </c>
       <c r="K8" s="20" t="n">
-        <v>7.41</v>
+        <v>7.52</v>
       </c>
       <c r="L8" s="12" t="n">
         <v>0</v>
@@ -32591,7 +32556,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>1462675.48</v>
+        <v>1479992.08</v>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
@@ -32599,10 +32564,10 @@
         </is>
       </c>
       <c r="J29" s="18" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="K29" s="20" t="n">
-        <v>6</v>
+        <v>6.07</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>0</v>
@@ -32640,7 +32605,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="13" t="n">
-        <v>40786.32640656</v>
+        <v>41053.37577964</v>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
@@ -32649,7 +32614,7 @@
       </c>
       <c r="J30" s="21" t="inlineStr"/>
       <c r="K30" s="20" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>0</v>
@@ -32779,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>4197.27353648</v>
+        <v>4418.65260064</v>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
@@ -32869,7 +32834,7 @@
         <v>0</v>
       </c>
       <c r="H35" s="13" t="n">
-        <v>27142.26</v>
+        <v>29037.7</v>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
@@ -32877,10 +32842,10 @@
         </is>
       </c>
       <c r="J35" s="18" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="K35" s="20" t="n">
-        <v>3.75</v>
+        <v>4.01</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>0</v>
@@ -33045,7 +33010,7 @@
         <v>6.6</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>75529.51433999999</v>
+        <v>76725.86796</v>
       </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
@@ -33286,7 +33251,7 @@
         <v>0</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>621.3530491500001</v>
+        <v>617.73873265</v>
       </c>
       <c r="F57" s="11" t="n">
         <v>0</v>
@@ -33426,7 +33391,7 @@
         <v>0.4</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>4197.27353648</v>
+        <v>4418.65260064</v>
       </c>
       <c r="F61" s="11" t="n">
         <v>0</v>
@@ -33566,7 +33531,7 @@
         <v>3.5</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>75529.51433999999</v>
+        <v>76725.86796</v>
       </c>
       <c r="F65" s="11" t="n">
         <v>0</v>
@@ -34024,7 +33989,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>1462675.48</v>
+        <v>1479992.08</v>
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
@@ -34426,7 +34391,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>1462675.48</v>
+        <v>1479992.08</v>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
@@ -34508,7 +34473,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>60014.06322947</v>
+        <v>437382.47</v>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
@@ -34590,7 +34555,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>690679.87641</v>
+        <v>1205407.79598</v>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
@@ -34953,7 +34918,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="13" t="n">
-        <v>60014.06322947</v>
+        <v>437382.47</v>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
@@ -34994,7 +34959,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>135131.2920455</v>
+        <v>236913.5</v>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
@@ -35158,7 +35123,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>155881.6932</v>
+        <v>156121.5282</v>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
@@ -35482,7 +35447,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>810.3801132900001</v>
+        <v>810.46916231</v>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
@@ -35763,11 +35728,11 @@
         <v>0</v>
       </c>
       <c r="G62" s="13" t="n">
-        <v>5205.99404763</v>
+        <v>31551.65838</v>
       </c>
       <c r="H62" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I62" s="12" t="n">
@@ -35845,7 +35810,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="13" t="n">
-        <v>27470</v>
+        <v>27634</v>
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
@@ -36052,11 +36017,11 @@
         <v>1</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>1973.54693088</v>
+        <v>4507.3215</v>
       </c>
       <c r="H69" s="14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="I69" s="12" t="n">
@@ -36374,7 +36339,7 @@
         <v>0</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>1462675.48</v>
+        <v>1479992.08</v>
       </c>
       <c r="H79" s="14" t="inlineStr">
         <is>
@@ -36456,7 +36421,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>14821.13635</v>
+        <v>14831.72582</v>
       </c>
       <c r="H81" s="14" t="inlineStr">
         <is>
@@ -36497,7 +36462,7 @@
         <v>0</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>16419.64597954</v>
+        <v>89487.18704</v>
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
@@ -37026,7 +36991,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>4197.27353648</v>
+        <v>4418.65260064</v>
       </c>
       <c r="H97" s="14" t="inlineStr">
         <is>
@@ -37348,7 +37313,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>60014.06322947</v>
+        <v>437382.47</v>
       </c>
       <c r="H107" s="14" t="inlineStr">
         <is>
@@ -38802,7 +38767,7 @@
         <v>0</v>
       </c>
       <c r="G149" s="13" t="n">
-        <v>25724.6</v>
+        <v>29736.81909</v>
       </c>
       <c r="H149" s="14" t="inlineStr">
         <is>
@@ -38884,7 +38849,7 @@
         <v>0</v>
       </c>
       <c r="G151" s="13" t="n">
-        <v>5185.717128</v>
+        <v>4739.499</v>
       </c>
       <c r="H151" s="14" t="inlineStr">
         <is>
@@ -39370,11 +39335,11 @@
         <v>0</v>
       </c>
       <c r="G165" s="13" t="n">
-        <v>9160.919039999999</v>
+        <v>14927.87712</v>
       </c>
       <c r="H165" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="I165" s="12" t="n">
@@ -39899,7 +39864,7 @@
         <v>0</v>
       </c>
       <c r="G180" s="13" t="n">
-        <v>571215.1683952201</v>
+        <v>571222.45</v>
       </c>
       <c r="H180" s="14" t="inlineStr">
         <is>
@@ -40223,7 +40188,7 @@
         <v>0</v>
       </c>
       <c r="G190" s="13" t="n">
-        <v>50.82827169</v>
+        <v>50.82849144</v>
       </c>
       <c r="H190" s="14" t="inlineStr">
         <is>
@@ -40838,7 +40803,7 @@
         <v>0</v>
       </c>
       <c r="G207" s="13" t="n">
-        <v>27142.26</v>
+        <v>29037.7</v>
       </c>
       <c r="H207" s="14" t="inlineStr">
         <is>
@@ -40961,7 +40926,7 @@
         <v>0</v>
       </c>
       <c r="G210" s="13" t="n">
-        <v>4197.27353648</v>
+        <v>4418.65260064</v>
       </c>
       <c r="H210" s="14" t="inlineStr">
         <is>
@@ -42158,11 +42123,11 @@
         <v>20.8</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>386.25986712</v>
+        <v>9710.28389253</v>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="F42" s="11" t="n">
@@ -42697,7 +42662,7 @@
         <v>20.8</v>
       </c>
       <c r="D63" s="13" t="n">
-        <v>7342.38496464</v>
+        <v>9754.151779440001</v>
       </c>
       <c r="E63" s="14" t="inlineStr">
         <is>
@@ -42734,11 +42699,11 @@
         <v>11.6</v>
       </c>
       <c r="D64" s="13" t="n">
-        <v>65.51875</v>
+        <v>6490.620658159999</v>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="F64" s="11" t="n">
@@ -42808,7 +42773,7 @@
         <v>2.2</v>
       </c>
       <c r="D66" s="13" t="n">
-        <v>1462675.48</v>
+        <v>1479992.08</v>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
@@ -43033,7 +42998,7 @@
         <v>10.3</v>
       </c>
       <c r="D75" s="13" t="n">
-        <v>0.000305</v>
+        <v>4.939780000000001</v>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
@@ -44138,7 +44103,7 @@
         <v>10.6</v>
       </c>
       <c r="D118" s="13" t="n">
-        <v>60014.06322947</v>
+        <v>437382.47</v>
       </c>
       <c r="E118" s="14" t="inlineStr">
         <is>
@@ -44337,7 +44302,7 @@
         <v>17</v>
       </c>
       <c r="F127" s="13" t="n">
-        <v>29631.16949492</v>
+        <v>51770.65398224</v>
       </c>
       <c r="G127" s="14" t="inlineStr">
         <is>
@@ -44425,7 +44390,7 @@
         <v>23.9</v>
       </c>
       <c r="D133" s="13" t="n">
-        <v>29631.16949492</v>
+        <v>51770.65398224</v>
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
@@ -44462,11 +44427,11 @@
         <v>11.9</v>
       </c>
       <c r="D134" s="13" t="n">
-        <v>1557.5929303</v>
+        <v>7665.61968209</v>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="F134" s="11" t="n">
@@ -44795,11 +44760,11 @@
         <v>16.4</v>
       </c>
       <c r="D149" s="13" t="n">
-        <v>5205.99404763</v>
+        <v>31551.65838</v>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="F149" s="11" t="n">
@@ -44869,7 +44834,7 @@
         <v>13.4</v>
       </c>
       <c r="D151" s="13" t="n">
-        <v>690679.87641</v>
+        <v>1205407.79598</v>
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
@@ -44943,7 +44908,7 @@
         <v>5.4</v>
       </c>
       <c r="D153" s="13" t="n">
-        <v>2113.06731792</v>
+        <v>2112.96</v>
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
@@ -47007,11 +46972,11 @@
         <v>4.4</v>
       </c>
       <c r="D239" s="13" t="n">
-        <v>9160.919039999999</v>
+        <v>14927.87712</v>
       </c>
       <c r="E239" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="F239" s="11" t="n">
@@ -47269,11 +47234,11 @@
         <v>13.1</v>
       </c>
       <c r="D249" s="13" t="n">
-        <v>9160.919039999999</v>
+        <v>14927.87712</v>
       </c>
       <c r="E249" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="F249" s="11" t="n">
@@ -47308,7 +47273,7 @@
         <v>13.6</v>
       </c>
       <c r="D250" s="13" t="n">
-        <v>1462675.48</v>
+        <v>1479992.08</v>
       </c>
       <c r="E250" s="14" t="inlineStr">
         <is>
@@ -47572,7 +47537,7 @@
         <v>15</v>
       </c>
       <c r="F260" s="13" t="n">
-        <v>20555.491904</v>
+        <v>29490.08752</v>
       </c>
       <c r="G260" s="14" t="inlineStr">
         <is>
@@ -47870,11 +47835,11 @@
         <v>27</v>
       </c>
       <c r="F270" s="13" t="n">
-        <v>4054.238496</v>
+        <v>43043.451936</v>
       </c>
       <c r="G270" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
     </row>
@@ -47963,7 +47928,7 @@
         <v>18</v>
       </c>
       <c r="F273" s="13" t="n">
-        <v>8468.4256</v>
+        <v>9364.928399999999</v>
       </c>
       <c r="G273" s="14" t="inlineStr">
         <is>
@@ -48025,7 +47990,7 @@
         <v>26</v>
       </c>
       <c r="F275" s="13" t="n">
-        <v>97243.60665285001</v>
+        <v>98961.44870745001</v>
       </c>
       <c r="G275" s="14" t="inlineStr">
         <is>
@@ -48267,7 +48232,7 @@
         <v>22</v>
       </c>
       <c r="F283" s="13" t="n">
-        <v>2293.30689399</v>
+        <v>2257.28797143</v>
       </c>
       <c r="G283" s="14" t="inlineStr">
         <is>
@@ -48416,7 +48381,7 @@
         <v>17</v>
       </c>
       <c r="F288" s="13" t="n">
-        <v>18582.248</v>
+        <v>18809.96</v>
       </c>
       <c r="G288" s="14" t="inlineStr">
         <is>
@@ -48478,11 +48443,11 @@
         <v>37</v>
       </c>
       <c r="F290" s="13" t="n">
-        <v>9160.919039999999</v>
+        <v>14927.87712</v>
       </c>
       <c r="G290" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
     </row>
@@ -49302,7 +49267,7 @@
         <v>4</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>1462675.48</v>
+        <v>1479992.08</v>
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
@@ -49310,10 +49275,10 @@
         </is>
       </c>
       <c r="J11" s="18" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="K11" s="20" t="n">
-        <v>6</v>
+        <v>6.07</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>0</v>
@@ -49981,7 +49946,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>52279.51030192</v>
+        <v>52270.95</v>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
@@ -50475,11 +50440,11 @@
         <v>16.4</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>5205.99404763</v>
+        <v>31551.65838</v>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G40" s="12" t="n">
@@ -50539,7 +50504,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>9053.593919999999</v>
+        <v>9107.057699999999</v>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
@@ -50571,7 +50536,7 @@
         <v>3.7</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>8729.92288</v>
+        <v>8781.4753</v>
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
@@ -50887,7 +50852,7 @@
         <v>9.9</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>445.7924025</v>
+        <v>457.09154982</v>
       </c>
       <c r="F53" s="14" t="inlineStr">
         <is>
@@ -51194,7 +51159,7 @@
         <v>2.8</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>40786.32640656</v>
+        <v>41053.37577964</v>
       </c>
       <c r="F65" s="14" t="inlineStr">
         <is>
@@ -51416,7 +51381,7 @@
         <v>2.2</v>
       </c>
       <c r="E72" s="13" t="n">
-        <v>5185.717128</v>
+        <v>4739.499</v>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
@@ -51512,7 +51477,7 @@
         <v>5.5</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>14475.42</v>
+        <v>14845.32</v>
       </c>
       <c r="F75" s="14" t="inlineStr">
         <is>
@@ -51862,7 +51827,7 @@
         <v>31</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>9423.227149599999</v>
+        <v>9429.379999999999</v>
       </c>
       <c r="F89" s="14" t="inlineStr">
         <is>
@@ -52875,7 +52840,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="E124" s="13" t="n">
-        <v>9423.227149599999</v>
+        <v>9429.379999999999</v>
       </c>
       <c r="F124" s="11" t="n">
         <v>0</v>
@@ -53527,7 +53492,7 @@
         <v>6</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>1462675.48</v>
+        <v>1479992.08</v>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
@@ -53535,10 +53500,10 @@
         </is>
       </c>
       <c r="J9" s="18" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="K9" s="20" t="n">
-        <v>6</v>
+        <v>6.07</v>
       </c>
       <c r="L9" s="12" t="n">
         <v>0</v>
@@ -53576,7 +53541,7 @@
         <v>3</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>60014.06322947</v>
+        <v>437382.47</v>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
@@ -53584,10 +53549,10 @@
         </is>
       </c>
       <c r="J10" s="18" t="n">
-        <v>3.5</v>
+        <v>22.4</v>
       </c>
       <c r="K10" s="20" t="n">
-        <v>8.93</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L10" s="12" t="n">
         <v>0</v>
@@ -53674,7 +53639,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>690679.87641</v>
+        <v>1205407.79598</v>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
@@ -53682,10 +53647,10 @@
         </is>
       </c>
       <c r="J12" s="18" t="n">
-        <v>19.6</v>
+        <v>35</v>
       </c>
       <c r="K12" s="20" t="n">
-        <v>0.95</v>
+        <v>1.66</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>0</v>
@@ -54299,7 +54264,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>135131.2920455</v>
+        <v>236913.5</v>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
@@ -54307,10 +54272,10 @@
         </is>
       </c>
       <c r="J25" s="18" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="K25" s="20" t="n">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>0</v>
@@ -54348,7 +54313,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>155881.6932</v>
+        <v>156121.5282</v>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
@@ -55160,7 +55125,7 @@
         <v>5.3</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>4302.405303680001</v>
+        <v>4578.436308159999</v>
       </c>
       <c r="F49" s="14" t="inlineStr">
         <is>
@@ -55691,11 +55656,11 @@
         <v>2.1</v>
       </c>
       <c r="E68" s="13" t="n">
-        <v>1456.70767283</v>
+        <v>4097.47500133</v>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G68" s="12" t="n">
@@ -56035,7 +56000,7 @@
         <v>6.3</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>71897.32291749</v>
+        <v>71894.55</v>
       </c>
       <c r="F79" s="14" t="inlineStr">
         <is>
@@ -56067,7 +56032,7 @@
         <v>7.7</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>54313.77967512</v>
+        <v>58257.37343047999</v>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
@@ -56179,11 +56144,11 @@
         <v>37</v>
       </c>
       <c r="E86" s="13" t="n">
-        <v>9160.919039999999</v>
+        <v>14927.87712</v>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -56210,11 +56175,11 @@
         <v>37</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>9160.919039999999</v>
+        <v>14927.87712</v>
       </c>
       <c r="F87" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G87" s="14" t="inlineStr">
@@ -56272,7 +56237,7 @@
         <v>53</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>690679.87641</v>
+        <v>1205407.79598</v>
       </c>
       <c r="F89" s="14" t="inlineStr">
         <is>
@@ -56444,7 +56409,7 @@
         <v>15</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>2113.29115491</v>
+        <v>2113.29612</v>
       </c>
       <c r="F95" s="14" t="inlineStr">
         <is>
@@ -56585,11 +56550,11 @@
         <v>27</v>
       </c>
       <c r="E100" s="13" t="n">
-        <v>4054.238496</v>
+        <v>43043.451936</v>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G100" s="14" t="inlineStr">
@@ -56817,17 +56782,17 @@
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>SRG</t>
+          <t>MOVAA</t>
         </is>
       </c>
       <c r="C110" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D110" s="12" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="E110" s="13" t="n">
-        <v>0.000266</v>
+        <v>45.652</v>
       </c>
       <c r="F110" s="11" t="n">
         <v>0</v>
@@ -56838,11 +56803,7 @@
       <c r="H110" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I110" s="14" t="inlineStr">
-        <is>
-          <t>Seritage Growth Properties</t>
-        </is>
-      </c>
+      <c r="I110" s="14" t="inlineStr"/>
     </row>
     <row r="111" ht="18" customHeight="1">
       <c r="A111" s="14" t="inlineStr">
@@ -56852,17 +56813,17 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>XRXDW</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E111" s="13" t="n">
-        <v>4.695e-05</v>
+        <v>39.75700174399999</v>
       </c>
       <c r="F111" s="11" t="n">
         <v>0</v>
@@ -56875,7 +56836,7 @@
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Xerox Holdings Corporation</t>
         </is>
       </c>
     </row>
@@ -56887,17 +56848,17 @@
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>MOVAA</t>
+          <t>ARCXF</t>
         </is>
       </c>
       <c r="C112" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D112" s="12" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="E112" s="13" t="n">
-        <v>44.382</v>
+        <v>44.6780855753</v>
       </c>
       <c r="F112" s="11" t="n">
         <v>0</v>
@@ -56908,7 +56869,11 @@
       <c r="H112" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I112" s="14" t="inlineStr"/>
+      <c r="I112" s="14" t="inlineStr">
+        <is>
+          <t>ArcelorMittal South Africa Limit</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="18" customHeight="1">
       <c r="A113" s="14" t="inlineStr">
@@ -56918,17 +56883,17 @@
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>XRXDW</t>
+          <t>SURG</t>
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="E113" s="13" t="n">
-        <v>39.75700174399999</v>
+        <v>10.5511959</v>
       </c>
       <c r="F113" s="11" t="n">
         <v>0</v>
@@ -56941,7 +56906,7 @@
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
-          <t>Xerox Holdings Corporation</t>
+          <t>SurgePays, Inc.</t>
         </is>
       </c>
     </row>
@@ -56953,17 +56918,17 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>ARCXF</t>
+          <t>CULP</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D114" s="12" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="E114" s="13" t="n">
-        <v>44.6780855753</v>
+        <v>40.5209088</v>
       </c>
       <c r="F114" s="11" t="n">
         <v>0</v>
@@ -56972,11 +56937,11 @@
         <v>0</v>
       </c>
       <c r="H114" s="12" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>ArcelorMittal South Africa Limit</t>
+          <t>Culp, Inc.</t>
         </is>
       </c>
     </row>
@@ -57278,7 +57243,7 @@
         <v>12.2</v>
       </c>
       <c r="E123" s="13" t="n">
-        <v>906.9768327999999</v>
+        <v>950.70298466</v>
       </c>
       <c r="F123" s="11" t="n">
         <v>0</v>
@@ -57338,30 +57303,30 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>JOE</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
         <v>5</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>81.7</v>
+        <v>79.7</v>
       </c>
       <c r="E125" s="13" t="n">
-        <v>9160.919039999999</v>
+        <v>3785.59865124</v>
       </c>
       <c r="F125" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G125" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H125" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
-          <t>Carvana Co.</t>
+          <t>The St. Joe Company</t>
         </is>
       </c>
     </row>
@@ -57373,17 +57338,17 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>JOE</t>
+          <t>BRSL</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>79.7</v>
+        <v>42.2</v>
       </c>
       <c r="E126" s="13" t="n">
-        <v>3785.59865124</v>
+        <v>2113.29612</v>
       </c>
       <c r="F126" s="11" t="n">
         <v>0</v>
@@ -57396,7 +57361,7 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>The St. Joe Company</t>
+          <t>Brightstar Lottery PLC</t>
         </is>
       </c>
     </row>
@@ -57408,17 +57373,17 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>BRSL</t>
+          <t>GPI</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>42.2</v>
+        <v>47.7</v>
       </c>
       <c r="E127" s="13" t="n">
-        <v>2113.29115491</v>
+        <v>3726.03811988</v>
       </c>
       <c r="F127" s="11" t="n">
         <v>0</v>
@@ -57431,7 +57396,7 @@
       </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
-          <t>Brightstar Lottery PLC</t>
+          <t>Group 1 Automotive, Inc.</t>
         </is>
       </c>
     </row>
@@ -57443,17 +57408,17 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>GPI</t>
+          <t>TDGMW</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>47.7</v>
+        <v>35.4</v>
       </c>
       <c r="E128" s="13" t="n">
-        <v>3726.03811988</v>
+        <v>3033.569772</v>
       </c>
       <c r="F128" s="11" t="n">
         <v>0</v>
@@ -57462,11 +57427,11 @@
         <v>0</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>Group 1 Automotive, Inc.</t>
+          <t>Tidewater Inc.</t>
         </is>
       </c>
     </row>
@@ -57478,17 +57443,17 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>TDGMW</t>
+          <t>ORLA</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D129" s="12" t="n">
-        <v>35.4</v>
+        <v>25.8</v>
       </c>
       <c r="E129" s="13" t="n">
-        <v>3033.569772</v>
+        <v>3530.61722292</v>
       </c>
       <c r="F129" s="11" t="n">
         <v>0</v>
@@ -57497,11 +57462,11 @@
         <v>0</v>
       </c>
       <c r="H129" s="12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>Tidewater Inc.</t>
+          <t>Orla Mining Ltd.</t>
         </is>
       </c>
     </row>
@@ -57523,7 +57488,7 @@
         <v>72.40000000000001</v>
       </c>
       <c r="E130" s="13" t="n">
-        <v>690679.87641</v>
+        <v>1205407.79598</v>
       </c>
       <c r="F130" s="11" t="n">
         <v>0</v>
@@ -57583,30 +57548,30 @@
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>16.8</v>
+        <v>81.7</v>
       </c>
       <c r="E132" s="13" t="n">
-        <v>2818348.1266976</v>
+        <v>14927.87712</v>
       </c>
       <c r="F132" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G132" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H132" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Carvana Co.</t>
         </is>
       </c>
     </row>
@@ -57618,20 +57583,20 @@
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D133" s="12" t="n">
-        <v>15</v>
+        <v>16.8</v>
       </c>
       <c r="E133" s="13" t="n">
-        <v>4459051.48</v>
+        <v>2818348.1266976</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G133" s="11" t="n">
         <v>0</v>
@@ -57641,7 +57606,7 @@
       </c>
       <c r="I133" s="14" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
     </row>
@@ -57653,17 +57618,17 @@
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>19.6</v>
+        <v>15</v>
       </c>
       <c r="E134" s="13" t="n">
-        <v>1462675.48</v>
+        <v>4459051.48</v>
       </c>
       <c r="F134" s="11" t="n">
         <v>1</v>
@@ -57676,7 +57641,7 @@
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
     </row>
@@ -58004,7 +57969,7 @@
         <v>2</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>60014.06322947</v>
+        <v>437382.47</v>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
@@ -58012,10 +57977,10 @@
         </is>
       </c>
       <c r="J9" s="18" t="n">
-        <v>3.5</v>
+        <v>22.4</v>
       </c>
       <c r="K9" s="20" t="n">
-        <v>8.93</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L9" s="12" t="n">
         <v>0</v>
@@ -58098,7 +58063,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>135131.2920455</v>
+        <v>236913.5</v>
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
@@ -58106,10 +58071,10 @@
         </is>
       </c>
       <c r="J11" s="18" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="K11" s="20" t="n">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>0</v>
@@ -58292,7 +58257,7 @@
         <v>4</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>1462675.48</v>
+        <v>1479992.08</v>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -58300,10 +58265,10 @@
         </is>
       </c>
       <c r="J15" s="18" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="K15" s="20" t="n">
-        <v>6</v>
+        <v>6.07</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>0</v>
@@ -58439,7 +58404,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>690679.87641</v>
+        <v>1205407.79598</v>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
@@ -58447,10 +58412,10 @@
         </is>
       </c>
       <c r="J18" s="18" t="n">
-        <v>19.6</v>
+        <v>35</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>0.95</v>
+        <v>1.66</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>0</v>
@@ -58582,7 +58547,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="13" t="n">
-        <v>155881.6932</v>
+        <v>156121.5282</v>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
@@ -59109,7 +59074,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="13" t="n">
-        <v>81525.32598114001</v>
+        <v>79518.72256991999</v>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
@@ -59117,10 +59082,10 @@
         </is>
       </c>
       <c r="J32" s="18" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="K32" s="20" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>0</v>
@@ -59651,7 +59616,7 @@
         <v>0.1</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>43181.19523440001</v>
+        <v>43181.2467</v>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
@@ -60088,7 +60053,7 @@
         <v>13.2</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>25724.6</v>
+        <v>29736.81909</v>
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
@@ -60530,7 +60495,7 @@
         <v>21.8</v>
       </c>
       <c r="E81" s="13" t="n">
-        <v>1462675.48</v>
+        <v>1479992.08</v>
       </c>
       <c r="F81" s="14" t="inlineStr">
         <is>
@@ -60746,11 +60711,11 @@
         <v>37</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>9160.919039999999</v>
+        <v>14927.87712</v>
       </c>
       <c r="F91" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G91" s="14" t="inlineStr">
@@ -60794,7 +60759,7 @@
         <v>17</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>29631.16949492</v>
+        <v>51770.65398224</v>
       </c>
       <c r="F93" s="14" t="inlineStr">
         <is>
@@ -60856,7 +60821,7 @@
         <v>71</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>1462675.48</v>
+        <v>1479992.08</v>
       </c>
       <c r="F95" s="14" t="inlineStr">
         <is>
@@ -61098,11 +61063,11 @@
         <v>27</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>4054.238496</v>
+        <v>43043.451936</v>
       </c>
       <c r="F103" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G103" s="14" t="inlineStr">
@@ -61268,17 +61233,17 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>VTEX</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="E111" s="13" t="n">
-        <v>4.695e-05</v>
+        <v>0.6682434899999999</v>
       </c>
       <c r="F111" s="11" t="n">
         <v>0</v>
@@ -61291,7 +61256,7 @@
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>VTEX</t>
         </is>
       </c>
     </row>
@@ -61313,7 +61278,7 @@
         <v>0.1</v>
       </c>
       <c r="E112" s="13" t="n">
-        <v>44.382</v>
+        <v>45.652</v>
       </c>
       <c r="F112" s="11" t="n">
         <v>0</v>
@@ -61344,7 +61309,7 @@
         <v>0.1</v>
       </c>
       <c r="E113" s="13" t="n">
-        <v>2.47595712</v>
+        <v>2.48001824</v>
       </c>
       <c r="F113" s="11" t="n">
         <v>0</v>
@@ -61369,7 +61334,7 @@
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>ONEW</t>
+          <t>VPG</t>
         </is>
       </c>
       <c r="C114" s="11" t="n">
@@ -61379,7 +61344,7 @@
         <v>0</v>
       </c>
       <c r="E114" s="13" t="n">
-        <v>0.01133</v>
+        <v>1.87939798</v>
       </c>
       <c r="F114" s="11" t="n">
         <v>0</v>
@@ -61392,7 +61357,7 @@
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>OneWater Marine Inc.</t>
+          <t>Vishay Precision Group, Inc.</t>
         </is>
       </c>
     </row>
@@ -61614,17 +61579,17 @@
       </c>
       <c r="B121" s="10" t="inlineStr">
         <is>
-          <t>ACMR</t>
+          <t>ARLO</t>
         </is>
       </c>
       <c r="C121" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D121" s="12" t="n">
-        <v>11.9</v>
+        <v>0.8</v>
       </c>
       <c r="E121" s="13" t="n">
-        <v>1557.5929303</v>
+        <v>1418.44421002</v>
       </c>
       <c r="F121" s="11" t="n">
         <v>0</v>
@@ -61637,7 +61602,7 @@
       </c>
       <c r="I121" s="14" t="inlineStr">
         <is>
-          <t>ACM Research, Inc.</t>
+          <t>Arlo Technologies, Inc.</t>
         </is>
       </c>
     </row>
@@ -61649,17 +61614,17 @@
       </c>
       <c r="B122" s="10" t="inlineStr">
         <is>
-          <t>ARLO</t>
+          <t>CNXC</t>
         </is>
       </c>
       <c r="C122" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D122" s="12" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="E122" s="13" t="n">
-        <v>1418.44421002</v>
+        <v>1530.00103608</v>
       </c>
       <c r="F122" s="11" t="n">
         <v>0</v>
@@ -61668,11 +61633,11 @@
         <v>0</v>
       </c>
       <c r="H122" s="12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>Arlo Technologies, Inc.</t>
+          <t>Concentrix Corporation</t>
         </is>
       </c>
     </row>
@@ -61684,17 +61649,17 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>UHAL</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="E123" s="13" t="n">
-        <v>1220.19264724</v>
+        <v>1804.5241602</v>
       </c>
       <c r="F123" s="11" t="n">
         <v>0</v>
@@ -61707,7 +61672,7 @@
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
-          <t>U-Haul Holding Company</t>
+          <t>Ivanhoe Electric Inc.</t>
         </is>
       </c>
     </row>
@@ -61719,17 +61684,17 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>CNXC</t>
+          <t>ATRC</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="E124" s="13" t="n">
-        <v>1530.00103608</v>
+        <v>1458.459936</v>
       </c>
       <c r="F124" s="11" t="n">
         <v>0</v>
@@ -61738,11 +61703,11 @@
         <v>0</v>
       </c>
       <c r="H124" s="12" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>Concentrix Corporation</t>
+          <t>AtriCure, Inc.</t>
         </is>
       </c>
     </row>
@@ -61754,17 +61719,17 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>TSN</t>
+          <t>GHM</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="E125" s="13" t="n">
-        <v>1242.304</v>
+        <v>1294.5599322</v>
       </c>
       <c r="F125" s="11" t="n">
         <v>0</v>
@@ -61777,7 +61742,7 @@
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
-          <t>Tyson Foods, Inc.</t>
+          <t>Graham Corporation</t>
         </is>
       </c>
     </row>
@@ -61824,17 +61789,17 @@
       </c>
       <c r="B127" s="10" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>KT</t>
         </is>
       </c>
       <c r="C127" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>31.1</v>
+        <v>13.6</v>
       </c>
       <c r="E127" s="13" t="n">
-        <v>9160.919039999999</v>
+        <v>4416.86155416</v>
       </c>
       <c r="F127" s="11" t="n">
         <v>0</v>
@@ -61843,11 +61808,11 @@
         <v>1</v>
       </c>
       <c r="H127" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
-          <t>Carvana Co.</t>
+          <t>KT Corporation</t>
         </is>
       </c>
     </row>
@@ -61859,30 +61824,30 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>KT</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D128" s="12" t="n">
-        <v>13.6</v>
+        <v>14.5</v>
       </c>
       <c r="E128" s="13" t="n">
-        <v>4416.86155416</v>
+        <v>2725.21804835</v>
       </c>
       <c r="F128" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G128" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H128" s="12" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>KT Corporation</t>
+          <t>Seabridge Gold Inc.</t>
         </is>
       </c>
     </row>
@@ -61894,17 +61859,17 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>CACC</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D129" s="12" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="E129" s="13" t="n">
-        <v>4054.238496</v>
+        <v>6064.016960829999</v>
       </c>
       <c r="F129" s="11" t="n">
         <v>0</v>
@@ -61917,7 +61882,7 @@
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>Interactive Brokers Group, Inc.</t>
+          <t>Credit Acceptance Corporation</t>
         </is>
       </c>
     </row>
@@ -61929,30 +61894,30 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>RRC</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>14.5</v>
+        <v>13.2</v>
       </c>
       <c r="E130" s="13" t="n">
-        <v>2725.21804835</v>
+        <v>8574.2936775</v>
       </c>
       <c r="F130" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G130" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H130" s="12" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>Seabridge Gold Inc.</t>
+          <t>Range Resources Corporation</t>
         </is>
       </c>
     </row>
@@ -62030,30 +61995,30 @@
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="C133" s="11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D133" s="12" t="n">
-        <v>6.5</v>
+        <v>31.1</v>
       </c>
       <c r="E133" s="13" t="n">
-        <v>4459051.48</v>
+        <v>14927.87712</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G133" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H133" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I133" s="14" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Carvana Co.</t>
         </is>
       </c>
     </row>
@@ -62065,30 +62030,30 @@
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C134" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D134" s="12" t="n">
-        <v>21.8</v>
+        <v>6.5</v>
       </c>
       <c r="E134" s="13" t="n">
-        <v>1462675.48</v>
+        <v>4459051.48</v>
       </c>
       <c r="F134" s="11" t="n">
         <v>1</v>
       </c>
       <c r="G134" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H134" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
     </row>
@@ -62100,30 +62065,30 @@
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>META</t>
         </is>
       </c>
       <c r="C135" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D135" s="12" t="n">
-        <v>11.6</v>
+        <v>21.8</v>
       </c>
       <c r="E135" s="13" t="n">
-        <v>153567.46273608</v>
+        <v>1479992.08</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H135" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I135" s="14" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Meta Platforms, Inc.</t>
         </is>
       </c>
     </row>
@@ -62643,7 +62608,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>97986.24000000001</v>
+        <v>98015.51232000001</v>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -62654,7 +62619,7 @@
         <v>37.8</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>8.35</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>0</v>
@@ -62829,7 +62794,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>155881.6932</v>
+        <v>156121.5282</v>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
@@ -63219,18 +63184,18 @@
         <v>1</v>
       </c>
       <c r="H25" s="13" t="n">
-        <v>1973.54693088</v>
+        <v>4507.3215</v>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J25" s="18" t="n">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="K25" s="20" t="n">
-        <v>0.4</v>
+        <v>0.92</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>0</v>
@@ -63411,7 +63376,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="13" t="n">
-        <v>3482.877</v>
+        <v>3510.018</v>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
@@ -63419,10 +63384,10 @@
         </is>
       </c>
       <c r="J29" s="18" t="n">
-        <v>65.3</v>
+        <v>65.8</v>
       </c>
       <c r="K29" s="20" t="n">
-        <v>6.71</v>
+        <v>6.76</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>0</v>
@@ -63511,7 +63476,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="13" t="n">
-        <v>810.3801132900001</v>
+        <v>810.46916231</v>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
@@ -63652,18 +63617,18 @@
         <v>1</v>
       </c>
       <c r="H34" s="13" t="n">
-        <v>9160.919039999999</v>
+        <v>14927.87712</v>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J34" s="18" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="K34" s="20" t="n">
-        <v>2.46</v>
+        <v>4.01</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>5</v>
@@ -64114,11 +64079,11 @@
         <v>1.5</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>0.000266</v>
+        <v>149.82184</v>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>nano</t>
+          <t>micro</t>
         </is>
       </c>
       <c r="G50" s="12" t="n">
@@ -64445,7 +64410,7 @@
         <v>3.4</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>2694.66935616</v>
+        <v>2768.38233423</v>
       </c>
       <c r="F63" s="14" t="inlineStr">
         <is>
@@ -64605,7 +64570,7 @@
         <v>1.3</v>
       </c>
       <c r="E68" s="13" t="n">
-        <v>13045.92289</v>
+        <v>13475.5257</v>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
@@ -64861,11 +64826,11 @@
         <v>13.3</v>
       </c>
       <c r="E76" s="13" t="n">
-        <v>1973.54693088</v>
+        <v>4507.3215</v>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G76" s="12" t="n">
@@ -65198,11 +65163,11 @@
         <v>37</v>
       </c>
       <c r="E90" s="13" t="n">
-        <v>9160.919039999999</v>
+        <v>14927.87712</v>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
@@ -65622,7 +65587,7 @@
         <v>0.2</v>
       </c>
       <c r="E108" s="13" t="n">
-        <v>2.47595712</v>
+        <v>2.48001824</v>
       </c>
       <c r="F108" s="11" t="n">
         <v>0</v>
@@ -65692,7 +65657,7 @@
         <v>0.3</v>
       </c>
       <c r="E110" s="13" t="n">
-        <v>44.382</v>
+        <v>45.652</v>
       </c>
       <c r="F110" s="11" t="n">
         <v>0</v>
@@ -65713,17 +65678,17 @@
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>NPWR</t>
+          <t>VPG</t>
         </is>
       </c>
       <c r="C111" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E111" s="13" t="n">
-        <v>6.886699920000001</v>
+        <v>1.87939798</v>
       </c>
       <c r="F111" s="11" t="n">
         <v>0</v>
@@ -65736,7 +65701,7 @@
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
-          <t>NET Power Inc.</t>
+          <t>Vishay Precision Group, Inc.</t>
         </is>
       </c>
     </row>
@@ -66133,30 +66098,30 @@
       </c>
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>CLBT</t>
         </is>
       </c>
       <c r="C123" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>29.8</v>
+        <v>14.6</v>
       </c>
       <c r="E123" s="13" t="n">
-        <v>9160.919039999999</v>
+        <v>3200.31285211</v>
       </c>
       <c r="F123" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G123" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
-          <t>Carvana Co.</t>
+          <t>Cellebrite DI Ltd.</t>
         </is>
       </c>
     </row>
@@ -66168,30 +66133,30 @@
       </c>
       <c r="B124" s="10" t="inlineStr">
         <is>
-          <t>CLBT</t>
+          <t>NATL</t>
         </is>
       </c>
       <c r="C124" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D124" s="12" t="n">
-        <v>14.6</v>
+        <v>18</v>
       </c>
       <c r="E124" s="13" t="n">
-        <v>3200.31285211</v>
+        <v>3219.01341571</v>
       </c>
       <c r="F124" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G124" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H124" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>Cellebrite DI Ltd.</t>
+          <t>NCR Atleos Corporation</t>
         </is>
       </c>
     </row>
@@ -66203,17 +66168,17 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>NATL</t>
+          <t>HGTY</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>18</v>
+        <v>17.2</v>
       </c>
       <c r="E125" s="13" t="n">
-        <v>3219.01341571</v>
+        <v>3761.479442289999</v>
       </c>
       <c r="F125" s="11" t="n">
         <v>0</v>
@@ -66226,7 +66191,7 @@
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
-          <t>NCR Atleos Corporation</t>
+          <t>Hagerty, Inc.</t>
         </is>
       </c>
     </row>
@@ -66238,17 +66203,17 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>HGTY</t>
+          <t>TDGMW</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>17.2</v>
+        <v>12.5</v>
       </c>
       <c r="E126" s="13" t="n">
-        <v>3761.479442289999</v>
+        <v>3033.569772</v>
       </c>
       <c r="F126" s="11" t="n">
         <v>0</v>
@@ -66257,11 +66222,11 @@
         <v>0</v>
       </c>
       <c r="H126" s="12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>Hagerty, Inc.</t>
+          <t>Tidewater Inc.</t>
         </is>
       </c>
     </row>
@@ -66343,17 +66308,17 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D129" s="12" t="n">
-        <v>10.4</v>
+        <v>29.8</v>
       </c>
       <c r="E129" s="13" t="n">
-        <v>2628929.97506404</v>
+        <v>14927.87712</v>
       </c>
       <c r="F129" s="11" t="n">
         <v>0</v>
@@ -66362,11 +66327,11 @@
         <v>0</v>
       </c>
       <c r="H129" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Carvana Co.</t>
         </is>
       </c>
     </row>
@@ -66378,17 +66343,17 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>20.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" s="13" t="n">
-        <v>19805.38760403</v>
+        <v>2628929.97506404</v>
       </c>
       <c r="F130" s="11" t="n">
         <v>0</v>
@@ -66401,7 +66366,7 @@
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>Talen Energy Corporation</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
     </row>
@@ -66413,17 +66378,17 @@
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>TLN</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D131" s="12" t="n">
-        <v>11.6</v>
+        <v>20.1</v>
       </c>
       <c r="E131" s="13" t="n">
-        <v>4459051.48</v>
+        <v>19805.38760403</v>
       </c>
       <c r="F131" s="11" t="n">
         <v>0</v>
@@ -66436,7 +66401,7 @@
       </c>
       <c r="I131" s="14" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Talen Energy Corporation</t>
         </is>
       </c>
     </row>
@@ -66617,16 +66582,16 @@
         <v>2</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>5205.99404763</v>
+        <v>31551.65838</v>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr"/>
       <c r="K6" s="20" t="n">
-        <v>0.92</v>
+        <v>5.6</v>
       </c>
       <c r="L6" s="12" t="n">
         <v>2</v>
@@ -66764,7 +66729,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>27470</v>
+        <v>27634</v>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
@@ -66772,10 +66737,10 @@
         </is>
       </c>
       <c r="J9" s="18" t="n">
-        <v>52</v>
+        <v>52.3</v>
       </c>
       <c r="K9" s="20" t="n">
-        <v>3.54</v>
+        <v>3.56</v>
       </c>
       <c r="L9" s="12" t="n">
         <v>0</v>
@@ -67052,7 +67017,7 @@
         <v>2</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>198995.8084317</v>
+        <v>1989958.0851738</v>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -67060,10 +67025,10 @@
         </is>
       </c>
       <c r="J15" s="18" t="n">
-        <v>1.7</v>
+        <v>44.1</v>
       </c>
       <c r="K15" s="20" t="n">
-        <v>0.19</v>
+        <v>1.88</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>0</v>
@@ -67199,18 +67164,18 @@
         <v>1</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>1973.54693088</v>
+        <v>4507.3215</v>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="J18" s="18" t="n">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>0.4</v>
+        <v>0.92</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>0</v>
@@ -67387,7 +67352,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>155881.6932</v>
+        <v>156121.5282</v>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
@@ -67914,7 +67879,7 @@
         <v>0</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>135131.2920455</v>
+        <v>236913.5</v>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
@@ -67922,10 +67887,10 @@
         </is>
       </c>
       <c r="J33" s="18" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="K33" s="20" t="n">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>0</v>
@@ -68231,7 +68196,7 @@
         <v>2.2</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>5185.717128</v>
+        <v>4739.499</v>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
@@ -68485,7 +68450,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="13" t="n">
-        <v>530026.5173399999</v>
+        <v>530842.00059</v>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
@@ -68850,11 +68815,11 @@
         <v>13.3</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>1973.54693088</v>
+        <v>4507.3215</v>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G66" s="12" t="n">
@@ -69170,7 +69135,7 @@
         <v>14.2</v>
       </c>
       <c r="E76" s="13" t="n">
-        <v>8468.4256</v>
+        <v>9364.928399999999</v>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
@@ -69928,7 +69893,7 @@
         <v>10.3</v>
       </c>
       <c r="E107" s="13" t="n">
-        <v>0.000305</v>
+        <v>4.939780000000001</v>
       </c>
       <c r="F107" s="11" t="n">
         <v>0</v>
@@ -70233,17 +70198,17 @@
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>UWMC</t>
+          <t>AOMR</t>
         </is>
       </c>
       <c r="C116" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D116" s="12" t="n">
-        <v>8.6</v>
+        <v>0.4</v>
       </c>
       <c r="E116" s="13" t="n">
-        <v>228.8913351</v>
+        <v>210.52876715</v>
       </c>
       <c r="F116" s="11" t="n">
         <v>0</v>
@@ -70256,7 +70221,7 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>UWM Holdings Corporation</t>
+          <t>Angel Oak Mortgage REIT, Inc.</t>
         </is>
       </c>
     </row>
@@ -70548,17 +70513,17 @@
       </c>
       <c r="B125" s="10" t="inlineStr">
         <is>
-          <t>SATS</t>
+          <t>ALV</t>
         </is>
       </c>
       <c r="C125" s="11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D125" s="12" t="n">
-        <v>15.7</v>
+        <v>21.2</v>
       </c>
       <c r="E125" s="13" t="n">
-        <v>5205.99404763</v>
+        <v>8851.841085119999</v>
       </c>
       <c r="F125" s="11" t="n">
         <v>0</v>
@@ -70567,11 +70532,11 @@
         <v>0</v>
       </c>
       <c r="H125" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
-          <t>EchoStar Corporation</t>
+          <t>Autoliv, Inc.</t>
         </is>
       </c>
     </row>
@@ -70583,30 +70548,30 @@
       </c>
       <c r="B126" s="10" t="inlineStr">
         <is>
-          <t>ALV</t>
+          <t>CORZ</t>
         </is>
       </c>
       <c r="C126" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D126" s="12" t="n">
-        <v>21.2</v>
+        <v>15.3</v>
       </c>
       <c r="E126" s="13" t="n">
-        <v>8851.841085119999</v>
+        <v>9269.53511472</v>
       </c>
       <c r="F126" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G126" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H126" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>Autoliv, Inc.</t>
+          <t>Core Scientific, Inc.</t>
         </is>
       </c>
     </row>
@@ -70688,17 +70653,17 @@
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>BA-PA</t>
+          <t>SATS</t>
         </is>
       </c>
       <c r="C129" s="11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D129" s="12" t="n">
         <v>15.7</v>
       </c>
       <c r="E129" s="13" t="n">
-        <v>54511.10618865</v>
+        <v>31551.65838</v>
       </c>
       <c r="F129" s="11" t="n">
         <v>0</v>
@@ -70707,11 +70672,11 @@
         <v>0</v>
       </c>
       <c r="H129" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>EchoStar Corporation</t>
         </is>
       </c>
     </row>
@@ -70723,30 +70688,30 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>BA-PA</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D130" s="12" t="n">
-        <v>18</v>
+        <v>15.7</v>
       </c>
       <c r="E130" s="13" t="n">
-        <v>257212.14661613</v>
+        <v>54511.10618865</v>
       </c>
       <c r="F130" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G130" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H130" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>Western Digital Corporation</t>
+          <t>Boeing Co</t>
         </is>
       </c>
     </row>
@@ -70758,30 +70723,30 @@
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>STT</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="C131" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D131" s="12" t="n">
-        <v>8.6</v>
+        <v>18</v>
       </c>
       <c r="E131" s="13" t="n">
-        <v>46582.65932423001</v>
+        <v>257212.14661613</v>
       </c>
       <c r="F131" s="11" t="n">
         <v>0</v>
       </c>
       <c r="G131" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H131" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I131" s="14" t="inlineStr">
         <is>
-          <t>State Street Corporation</t>
+          <t>Western Digital Corporation</t>
         </is>
       </c>
     </row>
@@ -70813,7 +70778,7 @@
     <col width="33.5" customWidth="1" min="2" max="2"/>
     <col width="9.5" customWidth="1" min="3" max="3"/>
     <col width="9.5" customWidth="1" min="4" max="4"/>
-    <col width="23.5" customWidth="1" min="5" max="5"/>
+    <col width="20.5" customWidth="1" min="5" max="5"/>
     <col width="9.5" customWidth="1" min="6" max="6"/>
     <col width="34.5" customWidth="1" min="7" max="7"/>
     <col width="40.5" customWidth="1" min="8" max="8"/>
@@ -71107,7 +71072,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>1462675.48</v>
+        <v>1479992.08</v>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
@@ -71115,10 +71080,10 @@
         </is>
       </c>
       <c r="J9" s="18" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="K9" s="20" t="n">
-        <v>6</v>
+        <v>6.07</v>
       </c>
       <c r="L9" s="12" t="n">
         <v>0</v>
@@ -71254,7 +71219,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>16419.64597954</v>
+        <v>89487.18704</v>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
@@ -71262,10 +71227,10 @@
         </is>
       </c>
       <c r="J12" s="18" t="n">
-        <v>3.2</v>
+        <v>20.1</v>
       </c>
       <c r="K12" s="20" t="n">
-        <v>0.62</v>
+        <v>3.36</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>0</v>
@@ -71305,7 +71270,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>14821.13635</v>
+        <v>14831.72582</v>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -71313,10 +71278,10 @@
         </is>
       </c>
       <c r="J13" s="18" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>33.2</v>
+        <v>33.22</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>0</v>
@@ -71403,7 +71368,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>690679.87641</v>
+        <v>1205407.79598</v>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -71411,10 +71376,10 @@
         </is>
       </c>
       <c r="J15" s="18" t="n">
-        <v>19.6</v>
+        <v>35</v>
       </c>
       <c r="K15" s="20" t="n">
-        <v>0.95</v>
+        <v>1.66</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>0</v>
@@ -71548,7 +71513,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>1278839.13649349</v>
+        <v>1280720.53930249</v>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
@@ -71556,10 +71521,10 @@
         </is>
       </c>
       <c r="J18" s="18" t="n">
-        <v>69.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K18" s="20" t="n">
-        <v>12.7</v>
+        <v>12.72</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>0</v>
@@ -72263,16 +72228,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="13" t="n">
-        <v>4054.238496</v>
+        <v>43043.451936</v>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>mid</t>
+          <t>large</t>
         </is>
       </c>
       <c r="J33" s="21" t="inlineStr"/>
       <c r="K33" s="20" t="n">
-        <v>0.73</v>
+        <v>7.71</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>0</v>
@@ -72595,7 +72560,7 @@
         <v>6.5</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>1278839.13649349</v>
+        <v>1280720.53930249</v>
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
@@ -72659,7 +72624,7 @@
         <v>2.6</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>40352.94331644</v>
+        <v>82104.48359139</v>
       </c>
       <c r="F49" s="14" t="inlineStr">
         <is>
@@ -72975,7 +72940,7 @@
         <v>19</v>
       </c>
       <c r="E62" s="13" t="n">
-        <v>7342.38496464</v>
+        <v>9754.151779440001</v>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
@@ -73071,11 +73036,11 @@
         <v>17</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>767.4175658399998</v>
+        <v>4912.544519999999</v>
       </c>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -73102,7 +73067,7 @@
         <v>12</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>4406.65361772</v>
+        <v>5524.31176</v>
       </c>
       <c r="F67" s="14" t="inlineStr">
         <is>
@@ -73133,11 +73098,11 @@
         <v>22</v>
       </c>
       <c r="E68" s="13" t="n">
-        <v>65.51875</v>
+        <v>6490.620658159999</v>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>mid</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -73164,7 +73129,7 @@
         <v>49</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>155881.6932</v>
+        <v>156121.5282</v>
       </c>
       <c r="F69" s="14" t="inlineStr">
         <is>
@@ -73354,17 +73319,17 @@
       </c>
       <c r="B79" s="10" t="inlineStr">
         <is>
-          <t>GLXY</t>
+          <t>SVACW</t>
         </is>
       </c>
       <c r="C79" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D79" s="12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>0.00342</v>
+        <v>12.500000625</v>
       </c>
       <c r="F79" s="11" t="n">
         <v>0</v>
@@ -73377,7 +73342,7 @@
       </c>
       <c r="I79" s="14" t="inlineStr">
         <is>
-          <t>Galaxy Digital</t>
+          <t xml:space="preserve">Spring Valley Acquisition Corp. </t>
         </is>
       </c>
     </row>
@@ -73389,17 +73354,17 @@
       </c>
       <c r="B80" s="10" t="inlineStr">
         <is>
-          <t>MWH</t>
+          <t>BBCQW</t>
         </is>
       </c>
       <c r="C80" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D80" s="12" t="n">
         <v>0.1</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>0.003421</v>
+        <v>19.41666589</v>
       </c>
       <c r="F80" s="11" t="n">
         <v>0</v>
@@ -73412,7 +73377,7 @@
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>SOLV Energy, Inc.</t>
+          <t>Bleichroeder Acquisition Corp. I</t>
         </is>
       </c>
     </row>
@@ -73424,17 +73389,17 @@
       </c>
       <c r="B81" s="10" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>XRXDW</t>
         </is>
       </c>
       <c r="C81" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D81" s="12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E81" s="13" t="n">
-        <v>4.695e-05</v>
+        <v>39.75700174399999</v>
       </c>
       <c r="F81" s="11" t="n">
         <v>0</v>
@@ -73447,7 +73412,7 @@
       </c>
       <c r="I81" s="14" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>Xerox Holdings Corporation</t>
         </is>
       </c>
     </row>
@@ -73459,17 +73424,17 @@
       </c>
       <c r="B82" s="10" t="inlineStr">
         <is>
-          <t>SVACW</t>
+          <t>ENHA</t>
         </is>
       </c>
       <c r="C82" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E82" s="13" t="n">
-        <v>12.500000625</v>
+        <v>45.33300069</v>
       </c>
       <c r="F82" s="11" t="n">
         <v>0</v>
@@ -73478,11 +73443,11 @@
         <v>0</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spring Valley Acquisition Corp. </t>
+          <t>Enhanced Group Inc.</t>
         </is>
       </c>
     </row>
@@ -73494,17 +73459,17 @@
       </c>
       <c r="B83" s="10" t="inlineStr">
         <is>
-          <t>CHWY</t>
+          <t>TEM</t>
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E83" s="13" t="n">
-        <v>0.001821</v>
+        <v>9.098529760000002</v>
       </c>
       <c r="F83" s="11" t="n">
         <v>0</v>
@@ -73517,7 +73482,7 @@
       </c>
       <c r="I83" s="14" t="inlineStr">
         <is>
-          <t>Chewy, Inc.</t>
+          <t>Tempus AI, Inc.</t>
         </is>
       </c>
     </row>
@@ -73529,17 +73494,17 @@
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>OWL</t>
+          <t>CIA</t>
         </is>
       </c>
       <c r="C84" s="11" t="n">
         <v>4</v>
       </c>
       <c r="D84" s="12" t="n">
-        <v>11.6</v>
+        <v>0.2</v>
       </c>
       <c r="E84" s="13" t="n">
-        <v>65.51875</v>
+        <v>295.7383494</v>
       </c>
       <c r="F84" s="11" t="n">
         <v>0</v>
@@ -73552,7 +73517,7 @@
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>Blue Owl Capital Inc.</t>
+          <t>Citizens, Inc.</t>
         </is>
       </c>
     </row>
@@ -73564,17 +73529,17 @@
       </c>
       <c r="B85" s="10" t="inlineStr">
         <is>
-          <t>CIA</t>
+          <t>GENI</t>
         </is>
       </c>
       <c r="C85" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D85" s="12" t="n">
-        <v>0.2</v>
+        <v>1.7</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>295.7383494</v>
+        <v>61</v>
       </c>
       <c r="F85" s="11" t="n">
         <v>0</v>
@@ -73583,11 +73548,11 @@
         <v>0</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="I85" s="14" t="inlineStr">
         <is>
-          <t>Citizens, Inc.</t>
+          <t>Genius Sports Limited</t>
         </is>
       </c>
     </row>
@@ -73599,17 +73564,17 @@
       </c>
       <c r="B86" s="10" t="inlineStr">
         <is>
-          <t>GENI</t>
+          <t>CEPV</t>
         </is>
       </c>
       <c r="C86" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D86" s="12" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="E86" s="13" t="n">
-        <v>61</v>
+        <v>56.65000000000001</v>
       </c>
       <c r="F86" s="11" t="n">
         <v>0</v>
@@ -73618,11 +73583,11 @@
         <v>0</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>Genius Sports Limited</t>
+          <t>Cantor Equity Partners V, Inc.</t>
         </is>
       </c>
     </row>
@@ -73634,17 +73599,17 @@
       </c>
       <c r="B87" s="10" t="inlineStr">
         <is>
-          <t>CEPV</t>
+          <t>CNDT</t>
         </is>
       </c>
       <c r="C87" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D87" s="12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>56.65000000000001</v>
+        <v>217.1355396</v>
       </c>
       <c r="F87" s="11" t="n">
         <v>0</v>
@@ -73653,11 +73618,11 @@
         <v>0</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
-          <t>Cantor Equity Partners V, Inc.</t>
+          <t>Conduent Incorporated</t>
         </is>
       </c>
     </row>
@@ -73669,7 +73634,7 @@
       </c>
       <c r="B88" s="10" t="inlineStr">
         <is>
-          <t>CNDT</t>
+          <t>OSG</t>
         </is>
       </c>
       <c r="C88" s="11" t="n">
@@ -73679,7 +73644,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="13" t="n">
-        <v>217.1355396</v>
+        <v>259.27828992</v>
       </c>
       <c r="F88" s="11" t="n">
         <v>0</v>
@@ -73688,11 +73653,11 @@
         <v>0</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>Conduent Incorporated</t>
+          <t>Octave Specialty Group, Inc.</t>
         </is>
       </c>
     </row>
@@ -73704,17 +73669,17 @@
       </c>
       <c r="B89" s="10" t="inlineStr">
         <is>
-          <t>QS</t>
+          <t>GLP</t>
         </is>
       </c>
       <c r="C89" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D89" s="12" t="n">
-        <v>13.1</v>
+        <v>2.4</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>767.4175658399998</v>
+        <v>1447.53107254</v>
       </c>
       <c r="F89" s="11" t="n">
         <v>0</v>
@@ -73727,7 +73692,7 @@
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
-          <t>QuantumScape Corporation</t>
+          <t>Global Partners LP</t>
         </is>
       </c>
     </row>
@@ -73739,17 +73704,17 @@
       </c>
       <c r="B90" s="10" t="inlineStr">
         <is>
-          <t>GLP</t>
+          <t>METC</t>
         </is>
       </c>
       <c r="C90" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D90" s="12" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="E90" s="13" t="n">
-        <v>1447.53107254</v>
+        <v>617.73873265</v>
       </c>
       <c r="F90" s="11" t="n">
         <v>0</v>
@@ -73762,7 +73727,7 @@
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>Global Partners LP</t>
+          <t>Ramaco Resources, Inc.</t>
         </is>
       </c>
     </row>
@@ -73774,17 +73739,17 @@
       </c>
       <c r="B91" s="10" t="inlineStr">
         <is>
-          <t>METC</t>
+          <t>PCT</t>
         </is>
       </c>
       <c r="C91" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D91" s="12" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>621.3530491500001</v>
+        <v>1573.512885</v>
       </c>
       <c r="F91" s="11" t="n">
         <v>0</v>
@@ -73797,7 +73762,7 @@
       </c>
       <c r="I91" s="14" t="inlineStr">
         <is>
-          <t>Ramaco Resources, Inc.</t>
+          <t>PureCycle Technologies, Inc.</t>
         </is>
       </c>
     </row>
@@ -73809,17 +73774,17 @@
       </c>
       <c r="B92" s="10" t="inlineStr">
         <is>
-          <t>PCT</t>
+          <t>HTZ</t>
         </is>
       </c>
       <c r="C92" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D92" s="12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="E92" s="13" t="n">
-        <v>1573.512885</v>
+        <v>1594.61084115</v>
       </c>
       <c r="F92" s="11" t="n">
         <v>0</v>
@@ -73832,7 +73797,7 @@
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>PureCycle Technologies, Inc.</t>
+          <t>Hertz Global Holdings, Inc.</t>
         </is>
       </c>
     </row>
@@ -73844,17 +73809,17 @@
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>HTZ</t>
+          <t>INVA</t>
         </is>
       </c>
       <c r="C93" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D93" s="12" t="n">
-        <v>3.3</v>
+        <v>1.2</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>1594.61084115</v>
+        <v>1659.95876501</v>
       </c>
       <c r="F93" s="11" t="n">
         <v>0</v>
@@ -73867,7 +73832,7 @@
       </c>
       <c r="I93" s="14" t="inlineStr">
         <is>
-          <t>Hertz Global Holdings, Inc.</t>
+          <t>Innoviva, Inc.</t>
         </is>
       </c>
     </row>
@@ -73959,7 +73924,7 @@
         <v>20.8</v>
       </c>
       <c r="E96" s="13" t="n">
-        <v>7342.38496464</v>
+        <v>9754.151779440001</v>
       </c>
       <c r="F96" s="11" t="n">
         <v>0</v>
@@ -73984,17 +73949,17 @@
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>CORZ</t>
+          <t>OWL</t>
         </is>
       </c>
       <c r="C97" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D97" s="12" t="n">
-        <v>0.5</v>
+        <v>11.6</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>9269.53511472</v>
+        <v>6490.620658159999</v>
       </c>
       <c r="F97" s="11" t="n">
         <v>0</v>
@@ -74007,7 +73972,7 @@
       </c>
       <c r="I97" s="14" t="inlineStr">
         <is>
-          <t>Core Scientific, Inc.</t>
+          <t>Blue Owl Capital Inc.</t>
         </is>
       </c>
     </row>
@@ -74019,17 +73984,17 @@
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>QS</t>
         </is>
       </c>
       <c r="C98" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D98" s="12" t="n">
-        <v>0.5</v>
+        <v>13.1</v>
       </c>
       <c r="E98" s="13" t="n">
-        <v>4054.238496</v>
+        <v>4912.544519999999</v>
       </c>
       <c r="F98" s="11" t="n">
         <v>0</v>
@@ -74042,7 +74007,7 @@
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>Interactive Brokers Group, Inc.</t>
+          <t>QuantumScape Corporation</t>
         </is>
       </c>
     </row>

--- a/style_analysis.xlsx
+++ b/style_analysis.xlsx
@@ -19215,7 +19215,7 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>TRUE.B</t>
+          <t>TRUE-B</t>
         </is>
       </c>
       <c r="B42" s="11" t="n">
@@ -34771,7 +34771,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="13" t="n">
         <v>1071439.020032</v>
@@ -53890,10 +53890,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" s="13" t="n">
         <v>1071439.020032</v>
@@ -57765,7 +57765,7 @@
         <v>0</v>
       </c>
       <c r="G130" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H130" s="12" t="n">
         <v>0</v>
@@ -58676,7 +58676,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="13" t="n">
         <v>1071439.020032</v>
@@ -59834,7 +59834,7 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>TISG.MI</t>
+          <t>TIT.MI</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
@@ -59847,11 +59847,11 @@
         <v>0</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>58.406</v>
+        <v>17092.018176</v>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>micro</t>
+          <t>large</t>
         </is>
       </c>
       <c r="G48" s="12" t="n">
@@ -59859,7 +59859,7 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Telecom Italia S.p.A.</t>
         </is>
       </c>
     </row>
